--- a/executive_list_handoff.xlsx
+++ b/executive_list_handoff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FosterDeighton\Downloads\Projects\Geo_intel_visual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FE360F-194E-448C-9419-8A39D8F37C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330A0C0B-2586-49AA-B5B3-23A40359545F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15075" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="1563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3245" uniqueCount="1559">
   <si>
     <t>Name</t>
   </si>
@@ -3775,18 +3775,6 @@
   </si>
   <si>
     <t>6 Park Lane Circle</t>
-  </si>
-  <si>
-    <t>Zhao Wang</t>
-  </si>
-  <si>
-    <t>Technical leader</t>
-  </si>
-  <si>
-    <t>Alphawave Semi</t>
-  </si>
-  <si>
-    <t>37 Park Lane Circle</t>
   </si>
   <si>
     <t>Andrew Curnew</t>
@@ -5256,7 +5244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E42E4E5-A64C-49E6-8DAD-74BEA63F0744}">
-  <dimension ref="A1:K485"/>
+  <dimension ref="A1:K484"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.44140625" bestFit="1" customWidth="1"/>
@@ -5311,19 +5299,19 @@
     </row>
     <row r="2" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F2" s="5">
         <v>41263</v>
@@ -5381,16 +5369,16 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E4" s="16">
         <v>9340000</v>
@@ -5527,7 +5515,7 @@
         <v>419</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>420</v>
@@ -5597,7 +5585,7 @@
         <v>1100</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>1095</v>
@@ -5661,16 +5649,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>209</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E12" s="30">
         <v>3400000</v>
@@ -5840,16 +5828,16 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="E17" s="18">
         <v>1828000</v>
@@ -5910,19 +5898,19 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="25" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="B19" s="25" t="s">
         <v>220</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F19" s="26">
         <v>45716</v>
@@ -5961,7 +5949,7 @@
         <v>945</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F20" s="5">
         <v>27758</v>
@@ -5984,19 +5972,19 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>220</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F21" s="32">
         <v>41696</v>
@@ -6031,7 +6019,7 @@
         <v>142</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F22" s="5">
         <v>46031</v>
@@ -6060,13 +6048,13 @@
         <v>1014</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>1015</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F23" s="32">
         <v>37931</v>
@@ -6089,19 +6077,19 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>220</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F24" s="31">
         <v>41180</v>
@@ -6124,16 +6112,16 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>220</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="E25" s="16">
         <v>9340000</v>
@@ -6264,16 +6252,16 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>220</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E29" s="17">
         <v>4225000</v>
@@ -6474,16 +6462,16 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>220</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="E35" s="18">
         <v>2840670</v>
@@ -6652,7 +6640,7 @@
         <v>1146</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1560</v>
+        <v>1556</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>1147</v>
@@ -6754,16 +6742,16 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="25" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="B43" s="25" t="s">
         <v>220</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="E43" s="30">
         <v>1865000</v>
@@ -6828,16 +6816,16 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="25" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="B45" s="25" t="s">
         <v>220</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="E45" s="30">
         <v>1525000</v>
@@ -6867,16 +6855,16 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="B46" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="E46" s="30">
         <v>1428750</v>
@@ -6912,7 +6900,7 @@
         <v>402</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>879</v>
@@ -7011,19 +6999,19 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="25" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="E50" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F50" s="26">
         <v>42233</v>
@@ -7062,7 +7050,7 @@
         <v>1042</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F51" s="5">
         <v>29951</v>
@@ -7097,7 +7085,7 @@
         <v>44</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F52" s="5">
         <v>32385</v>
@@ -7132,7 +7120,7 @@
         <v>65</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F53" s="5">
         <v>45154</v>
@@ -7155,22 +7143,22 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E54" s="20" t="s">
         <v>1275</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>1279</v>
-      </c>
       <c r="F54" s="33" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="G54" s="3">
         <v>6.26</v>
@@ -7202,7 +7190,7 @@
         <v>1217</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F55" s="5">
         <v>44427</v>
@@ -7237,7 +7225,7 @@
         <v>1225</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F56" s="5">
         <v>46120</v>
@@ -7260,7 +7248,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="25" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="B57" s="25" t="s">
         <v>386</v>
@@ -7269,10 +7257,10 @@
         <v>325</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E57" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F57" s="26">
         <v>45127</v>
@@ -7690,7 +7678,7 @@
         <v>1102</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>1103</v>
@@ -7754,16 +7742,16 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="25" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B71" s="25" t="s">
         <v>917</v>
       </c>
       <c r="C71" s="25" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="E71" s="30">
         <v>3300000</v>
@@ -7834,7 +7822,7 @@
         <v>386</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>560</v>
@@ -8038,16 +8026,16 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="25" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="B79" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="E79" s="30">
         <v>2500000</v>
@@ -8252,16 +8240,16 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="25" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="C85" s="25" t="s">
         <v>467</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="E85" s="30">
         <v>2200000</v>
@@ -8536,16 +8524,16 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="25" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="C93" s="25" t="s">
         <v>294</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="E93" s="30">
         <v>1620000</v>
@@ -8686,7 +8674,7 @@
         <v>386</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>851</v>
@@ -8750,16 +8738,16 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="25" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="D99" s="25" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="E99" s="30">
         <v>1549000</v>
@@ -8795,7 +8783,7 @@
         <v>1195</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>1193</v>
@@ -8859,16 +8847,16 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="25" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B102" s="25" t="s">
         <v>386</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="E102" s="30">
         <v>1390000</v>
@@ -8901,10 +8889,10 @@
         <v>881</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>882</v>
@@ -8933,16 +8921,16 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="25" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>1547</v>
+        <v>1543</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="E104" s="30">
         <v>1305000</v>
@@ -9010,10 +8998,10 @@
         <v>887</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>1561</v>
+        <v>1557</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>1562</v>
+        <v>1558</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>888</v>
@@ -9299,7 +9287,7 @@
         <v>942</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F114" s="5">
         <v>43698</v>
@@ -9334,7 +9322,7 @@
         <v>1214</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F115" s="5">
         <v>44729</v>
@@ -9532,16 +9520,16 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="25" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="B121" s="25" t="s">
         <v>361</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="E121" s="30">
         <v>2300000</v>
@@ -9676,19 +9664,19 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="25" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="B125" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="D125" s="25" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="E125" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F125" s="26">
         <v>46094</v>
@@ -9727,7 +9715,7 @@
         <v>945</v>
       </c>
       <c r="E126" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F126" s="5">
         <v>27758</v>
@@ -9762,7 +9750,7 @@
         <v>1220</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F127" s="5">
         <v>39597</v>
@@ -9785,19 +9773,19 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="25" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="B128" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C128" s="25" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="D128" s="25" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="E128" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F128" s="26">
         <v>40813</v>
@@ -9836,7 +9824,7 @@
         <v>1008</v>
       </c>
       <c r="E129" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F129" s="5">
         <v>35696</v>
@@ -9871,7 +9859,7 @@
         <v>962</v>
       </c>
       <c r="E130" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F130" s="5">
         <v>29966</v>
@@ -9906,7 +9894,7 @@
         <v>1000</v>
       </c>
       <c r="E131" s="21" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F131" s="31">
         <v>41492</v>
@@ -9941,7 +9929,7 @@
         <v>1027</v>
       </c>
       <c r="E132" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F132" s="5">
         <v>42887</v>
@@ -9976,7 +9964,7 @@
         <v>957</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F133" s="5">
         <v>45740</v>
@@ -10139,16 +10127,16 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="25" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="B138" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C138" s="25" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
       <c r="D138" s="25" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="E138" s="30">
         <v>3550000</v>
@@ -10178,16 +10166,16 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="25" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="B139" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C139" s="25" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="D139" s="25" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="E139" s="30">
         <v>3482000</v>
@@ -10217,16 +10205,16 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="25" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="B140" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C140" s="25" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="D140" s="25" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="E140" s="30">
         <v>3175000</v>
@@ -10361,16 +10349,16 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="25" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="B144" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C144" s="25" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="D144" s="25" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="E144" s="30">
         <v>2850000</v>
@@ -10435,16 +10423,16 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="25" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="B146" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C146" s="25" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="E146" s="30">
         <v>2735000</v>
@@ -10655,7 +10643,7 @@
         <v>174</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>648</v>
@@ -10795,7 +10783,7 @@
         <v>174</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>724</v>
@@ -10894,16 +10882,16 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="25" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="B159" s="25" t="s">
         <v>174</v>
       </c>
       <c r="C159" s="25" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="D159" s="25" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="E159" s="30">
         <v>1950000</v>
@@ -11114,7 +11102,7 @@
         <v>174</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>874</v>
@@ -11283,19 +11271,19 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="25" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B170" s="25" t="s">
         <v>156</v>
       </c>
       <c r="C170" s="25" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="D170" s="25" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="E170" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F170" s="26">
         <v>39981</v>
@@ -11334,7 +11322,7 @@
         <v>951</v>
       </c>
       <c r="E171" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F171" s="32">
         <v>43517</v>
@@ -11357,19 +11345,19 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>156</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="E172" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F172" s="5">
         <v>34655</v>
@@ -11392,19 +11380,19 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="25" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="B173" s="25" t="s">
         <v>156</v>
       </c>
       <c r="C173" s="25" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="D173" s="25" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="E173" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F173" s="26">
         <v>46106</v>
@@ -11431,19 +11419,19 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="25" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="B174" s="25" t="s">
         <v>156</v>
       </c>
       <c r="C174" s="25" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="E174" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F174" s="26">
         <v>31253</v>
@@ -11482,7 +11470,7 @@
         <v>954</v>
       </c>
       <c r="E175" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F175" s="5">
         <v>43357</v>
@@ -11505,19 +11493,19 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="25" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B176" s="25" t="s">
         <v>156</v>
       </c>
       <c r="C176" s="25" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="E176" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F176" s="26">
         <v>45798</v>
@@ -11754,16 +11742,16 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="25" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="B183" s="25" t="s">
         <v>156</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="D183" s="25" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="E183" s="30">
         <v>3218018</v>
@@ -12038,7 +12026,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="25" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="B191" s="25" t="s">
         <v>156</v>
@@ -12047,7 +12035,7 @@
         <v>1192</v>
       </c>
       <c r="D191" s="25" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="E191" s="30">
         <v>1500000</v>
@@ -12255,7 +12243,7 @@
         <v>975</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="C197" s="7" t="s">
         <v>976</v>
@@ -12264,7 +12252,7 @@
         <v>977</v>
       </c>
       <c r="E197" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F197" s="32">
         <v>42164</v>
@@ -12290,7 +12278,7 @@
         <v>324</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>325</v>
@@ -12357,7 +12345,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="25" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="B200" s="25" t="s">
         <v>1115</v>
@@ -12366,7 +12354,7 @@
         <v>325</v>
       </c>
       <c r="D200" s="25" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="E200" s="30">
         <v>3480000</v>
@@ -12501,16 +12489,16 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="25" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B204" s="25" t="s">
         <v>1115</v>
       </c>
       <c r="C204" s="25" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
       <c r="D204" s="25" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="E204" s="30">
         <v>1695000</v>
@@ -12575,16 +12563,16 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="25" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="B206" s="25" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="C206" s="25" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="D206" s="25" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="E206" s="30">
         <v>1509000</v>
@@ -12620,7 +12608,7 @@
         <v>1115</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="D207" s="7" t="s">
         <v>207</v>
@@ -12649,19 +12637,19 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="25" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="B208" s="25" t="s">
         <v>158</v>
       </c>
       <c r="C208" s="25" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="D208" s="25" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="E208" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F208" s="26">
         <v>45232</v>
@@ -12700,7 +12688,7 @@
         <v>984</v>
       </c>
       <c r="E209" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F209" s="5">
         <v>37777</v>
@@ -12735,7 +12723,7 @@
         <v>965</v>
       </c>
       <c r="E210" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F210" s="5">
         <v>32295</v>
@@ -12770,7 +12758,7 @@
         <v>115</v>
       </c>
       <c r="E211" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F211" s="5">
         <v>33921</v>
@@ -12904,7 +12892,7 @@
         <v>1112</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>1113</v>
@@ -13120,7 +13108,7 @@
         <v>981</v>
       </c>
       <c r="E221" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F221" s="5">
         <v>44210</v>
@@ -13181,7 +13169,7 @@
         <v>1221</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>948</v>
@@ -13190,7 +13178,7 @@
         <v>1222</v>
       </c>
       <c r="E223" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F223" s="5">
         <v>44600</v>
@@ -13225,7 +13213,7 @@
         <v>1228</v>
       </c>
       <c r="E224" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F224" s="32">
         <v>45456</v>
@@ -13260,7 +13248,7 @@
         <v>949</v>
       </c>
       <c r="E225" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F225" s="5">
         <v>29829</v>
@@ -13283,16 +13271,16 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="25" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B226" s="25" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="C226" s="25" t="s">
         <v>467</v>
       </c>
       <c r="D226" s="25" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="E226" s="30">
         <v>6435000</v>
@@ -13325,7 +13313,7 @@
         <v>462</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>463</v>
@@ -13360,10 +13348,10 @@
         <v>1104</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="D228" s="4" t="s">
         <v>1105</v>
@@ -13395,7 +13383,7 @@
         <v>1106</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>653</v>
@@ -13640,7 +13628,7 @@
         <v>567</v>
       </c>
       <c r="B236" s="11" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="C236" s="11" t="s">
         <v>568</v>
@@ -13713,7 +13701,7 @@
         <v>587</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>588</v>
@@ -13777,16 +13765,16 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" s="25" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="B240" s="25" t="s">
         <v>290</v>
       </c>
       <c r="C240" s="25" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="E240" s="30">
         <v>2530000</v>
@@ -13924,7 +13912,7 @@
         <v>664</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>665</v>
@@ -13994,7 +13982,7 @@
         <v>689</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>467</v>
@@ -14131,16 +14119,16 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" s="25" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="B250" s="25" t="s">
         <v>101</v>
       </c>
       <c r="C250" s="25" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="E250" s="30">
         <v>2160000</v>
@@ -14208,7 +14196,7 @@
         <v>1179</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>829</v>
@@ -14348,7 +14336,7 @@
         <v>276</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>128</v>
@@ -14383,7 +14371,7 @@
         <v>828</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>829</v>
@@ -14418,10 +14406,10 @@
         <v>201</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
       <c r="D258" s="4" t="s">
         <v>202</v>
@@ -14450,16 +14438,16 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="25" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B259" s="25" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="C259" s="25" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
       <c r="D259" s="25" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E259" s="30">
         <v>1340000</v>
@@ -14740,7 +14728,7 @@
         <v>389</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>555</v>
@@ -14775,7 +14763,7 @@
         <v>389</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="D268" s="4" t="s">
         <v>691</v>
@@ -14874,19 +14862,19 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="25" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="B271" s="25" t="s">
         <v>926</v>
       </c>
       <c r="C271" s="25" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="D271" s="25" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="E271" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F271" s="26">
         <v>30806</v>
@@ -15059,7 +15047,7 @@
         <v>509</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>510</v>
@@ -15091,7 +15079,7 @@
         <v>545</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>546</v>
@@ -15228,16 +15216,16 @@
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" s="25" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="B281" s="25" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="C281" s="25" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="D281" s="25" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="E281" s="30">
         <v>2402000</v>
@@ -15340,7 +15328,7 @@
         <v>699</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>1069</v>
@@ -15410,10 +15398,10 @@
         <v>714</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>715</v>
@@ -15547,16 +15535,16 @@
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="25" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="B290" s="25" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="C290" s="25" t="s">
         <v>650</v>
       </c>
       <c r="D290" s="25" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="E290" s="30">
         <v>1525000</v>
@@ -15703,7 +15691,7 @@
         <v>1005</v>
       </c>
       <c r="E294" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F294" s="32">
         <v>45523</v>
@@ -15738,7 +15726,7 @@
         <v>954</v>
       </c>
       <c r="E295" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F295" s="32">
         <v>43357</v>
@@ -15773,7 +15761,7 @@
         <v>1211</v>
       </c>
       <c r="E296" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F296" s="32">
         <v>41851</v>
@@ -15808,7 +15796,7 @@
         <v>92</v>
       </c>
       <c r="E297" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F297" s="32">
         <v>44428</v>
@@ -16012,7 +16000,7 @@
         <v>38</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>656</v>
@@ -16117,7 +16105,7 @@
         <v>58</v>
       </c>
       <c r="C306" s="11" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="D306" s="11" t="s">
         <v>59</v>
@@ -16146,16 +16134,16 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" s="25" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="B307" s="25" t="s">
         <v>38</v>
       </c>
       <c r="C307" s="25" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="D307" s="25" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="E307" s="30">
         <v>1704000</v>
@@ -16220,16 +16208,16 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="25" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="B309" s="25" t="s">
         <v>38</v>
       </c>
       <c r="C309" s="25" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="D309" s="25" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="E309" s="30">
         <v>1600000</v>
@@ -16265,7 +16253,7 @@
         <v>187</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>188</v>
@@ -16399,19 +16387,19 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" s="25" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="B314" s="25" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="C314" s="25" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="D314" s="25" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="E314" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F314" s="26">
         <v>29102</v>
@@ -16450,7 +16438,7 @@
         <v>974</v>
       </c>
       <c r="E315" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F315" s="5">
         <v>36403</v>
@@ -16485,7 +16473,7 @@
         <v>994</v>
       </c>
       <c r="E316" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F316" s="5">
         <v>38506</v>
@@ -16520,7 +16508,7 @@
         <v>1037</v>
       </c>
       <c r="E317" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F317" s="32">
         <v>40899</v>
@@ -16555,7 +16543,7 @@
         <v>1021</v>
       </c>
       <c r="E318" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F318" s="5">
         <v>42150</v>
@@ -16590,7 +16578,7 @@
         <v>968</v>
       </c>
       <c r="E319" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F319" s="5">
         <v>42639</v>
@@ -16625,7 +16613,7 @@
         <v>1003</v>
       </c>
       <c r="E320" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F320" s="5">
         <v>45455</v>
@@ -16651,7 +16639,7 @@
         <v>995</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>996</v>
@@ -16660,7 +16648,7 @@
         <v>997</v>
       </c>
       <c r="E321" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F321" s="5">
         <v>45089</v>
@@ -16721,7 +16709,7 @@
         <v>356</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="C323" s="11" t="s">
         <v>357</v>
@@ -16753,16 +16741,16 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" s="25" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="B324" s="25" t="s">
         <v>124</v>
       </c>
       <c r="C324" s="25" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="D324" s="25" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E324" s="30">
         <v>5500000</v>
@@ -16897,16 +16885,16 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" s="25" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="B328" s="25" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="C328" s="25" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="D328" s="25" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="E328" s="30">
         <v>3550000</v>
@@ -16936,16 +16924,16 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" s="25" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="B329" s="25" t="s">
         <v>124</v>
       </c>
       <c r="C329" s="25" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="D329" s="25" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="E329" s="30">
         <v>3400000</v>
@@ -17016,7 +17004,7 @@
         <v>124</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>588</v>
@@ -17045,16 +17033,16 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" s="25" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="B332" s="25" t="s">
         <v>124</v>
       </c>
       <c r="C332" s="25" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="D332" s="25" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="E332" s="30">
         <v>2530000</v>
@@ -17160,7 +17148,7 @@
         <v>124</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1554</v>
+        <v>1550</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>667</v>
@@ -17192,10 +17180,10 @@
         <v>166</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>167</v>
@@ -17259,16 +17247,16 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" s="7" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="B338" s="7" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="D338" s="7" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="E338" s="16">
         <v>2000000</v>
@@ -17294,7 +17282,7 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="B339" s="4" t="s">
         <v>124</v>
@@ -17303,7 +17291,7 @@
         <v>744</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="E339" s="18">
         <v>2000000</v>
@@ -17475,7 +17463,7 @@
         <v>124</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="D344" s="11" t="s">
         <v>792</v>
@@ -17644,16 +17632,16 @@
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="25" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="B349" s="25" t="s">
         <v>124</v>
       </c>
       <c r="C349" s="25" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="D349" s="25" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="E349" s="30">
         <v>1570000</v>
@@ -17756,7 +17744,7 @@
         <v>1196</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="C352" s="13" t="s">
         <v>996</v>
@@ -17788,7 +17776,7 @@
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" s="25" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="B353" s="25" t="s">
         <v>124</v>
@@ -17797,7 +17785,7 @@
         <v>325</v>
       </c>
       <c r="D353" s="25" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="E353" s="30">
         <v>1410000</v>
@@ -17862,16 +17850,16 @@
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="25" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B355" s="25" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="C355" s="25" t="s">
         <v>294</v>
       </c>
       <c r="D355" s="25" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="E355" s="30">
         <v>1275000</v>
@@ -17901,7 +17889,7 @@
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" s="25" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B356" s="25" t="s">
         <v>124</v>
@@ -17910,7 +17898,7 @@
         <v>325</v>
       </c>
       <c r="D356" s="25" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="E356" s="30">
         <v>1140000</v>
@@ -18092,7 +18080,7 @@
         <v>971</v>
       </c>
       <c r="E361" s="21" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F361" s="31">
         <v>30333</v>
@@ -18115,19 +18103,19 @@
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" s="25" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="B362" s="25" t="s">
         <v>71</v>
       </c>
       <c r="C362" s="25" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="D362" s="25" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="E362" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F362" s="26">
         <v>38454</v>
@@ -18166,7 +18154,7 @@
         <v>1024</v>
       </c>
       <c r="E363" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F363" s="32">
         <v>27256</v>
@@ -18201,7 +18189,7 @@
         <v>1005</v>
       </c>
       <c r="E364" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F364" s="5">
         <v>45523</v>
@@ -18367,7 +18355,7 @@
         <v>506</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>507</v>
@@ -18399,16 +18387,16 @@
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="25" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="B370" s="25" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="C370" s="25" t="s">
         <v>1023</v>
       </c>
       <c r="D370" s="25" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="E370" s="30">
         <v>3400000</v>
@@ -18584,7 +18572,7 @@
         <v>662</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>663</v>
@@ -18724,7 +18712,7 @@
         <v>71</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1553</v>
+        <v>1549</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>726</v>
@@ -18756,7 +18744,7 @@
         <v>727</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>728</v>
@@ -18794,7 +18782,7 @@
         <v>741</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>742</v>
@@ -19179,7 +19167,7 @@
         <v>1177</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>1178</v>
@@ -19386,7 +19374,7 @@
         <v>78</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>79</v>
@@ -19421,7 +19409,7 @@
         <v>1089</v>
       </c>
       <c r="B399" s="11" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="C399" s="13" t="s">
         <v>433</v>
@@ -19570,7 +19558,7 @@
         <v>1012</v>
       </c>
       <c r="E403" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F403" s="32">
         <v>45569</v>
@@ -19593,19 +19581,19 @@
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="25" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="B404" s="25" t="s">
         <v>1010</v>
       </c>
       <c r="C404" s="25" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="D404" s="25" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="E404" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F404" s="26">
         <v>38063</v>
@@ -19631,26 +19619,26 @@
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A405" s="4" t="s">
-        <v>1239</v>
-      </c>
-      <c r="B405" s="4" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C405" s="4" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D405" s="4" t="s">
-        <v>1242</v>
+      <c r="A405" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C405" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="D405" s="7" t="s">
+        <v>499</v>
       </c>
       <c r="E405" s="16">
-        <v>10000000</v>
-      </c>
-      <c r="F405" s="5">
-        <v>41990</v>
-      </c>
-      <c r="G405" s="6">
-        <v>6.3</v>
+        <v>3512000</v>
+      </c>
+      <c r="F405" s="32">
+        <v>45138</v>
+      </c>
+      <c r="G405" s="3">
+        <v>3.76</v>
       </c>
       <c r="H405" s="9">
         <v>62</v>
@@ -19662,30 +19650,30 @@
         <v>1055</v>
       </c>
       <c r="K405" s="10" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A406" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="B406" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="C406" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="D406" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="E406" s="16">
-        <v>3512000</v>
-      </c>
-      <c r="F406" s="32">
-        <v>45138</v>
-      </c>
-      <c r="G406" s="3">
-        <v>3.76</v>
+      <c r="A406" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="E406" s="18">
+        <v>2895000</v>
+      </c>
+      <c r="F406" s="5">
+        <v>42293</v>
+      </c>
+      <c r="G406" s="6">
+        <v>3.84</v>
       </c>
       <c r="H406" s="9">
         <v>62</v>
@@ -19702,25 +19690,25 @@
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
-        <v>571</v>
+        <v>244</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>572</v>
+        <v>289</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>573</v>
+        <v>181</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>574</v>
+        <v>245</v>
       </c>
       <c r="E407" s="18">
-        <v>2895000</v>
+        <v>2330000</v>
       </c>
       <c r="F407" s="5">
-        <v>42293</v>
+        <v>45182</v>
       </c>
       <c r="G407" s="6">
-        <v>3.84</v>
+        <v>4.6630000000000003</v>
       </c>
       <c r="H407" s="9">
         <v>62</v>
@@ -19737,25 +19725,25 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
-        <v>244</v>
+        <v>1181</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>289</v>
+        <v>1229</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>181</v>
+        <v>1182</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>245</v>
+        <v>1183</v>
       </c>
       <c r="E408" s="18">
-        <v>2330000</v>
+        <v>1739800</v>
       </c>
       <c r="F408" s="5">
-        <v>45182</v>
-      </c>
-      <c r="G408" s="6">
-        <v>4.6630000000000003</v>
+        <v>42016</v>
+      </c>
+      <c r="G408" s="3">
+        <v>3.48</v>
       </c>
       <c r="H408" s="9">
         <v>62</v>
@@ -19767,65 +19755,69 @@
         <v>1055</v>
       </c>
       <c r="K408" s="10" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A409" s="4" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B409" s="4" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C409" s="4" t="s">
-        <v>1182</v>
-      </c>
-      <c r="D409" s="4" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E409" s="18">
-        <v>1739800</v>
-      </c>
-      <c r="F409" s="5">
-        <v>42016</v>
-      </c>
-      <c r="G409" s="3">
-        <v>3.48</v>
-      </c>
-      <c r="H409" s="9">
+      <c r="A409" s="25" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B409" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="C409" s="25" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D409" s="25" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E409" s="30">
+        <v>1704000</v>
+      </c>
+      <c r="F409" s="26">
+        <v>40602</v>
+      </c>
+      <c r="G409" s="27">
+        <v>3.27</v>
+      </c>
+      <c r="H409" s="28" cm="1">
+        <f t="array" ref="H409">_xlfn.IFS(I409="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B409)),80,96),I409="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B409)),ISNUMBER(SEARCH("chief executive",B409))),95,91),I409="Managing Director",86,I409="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B409)),ISNUMBER(SEARCH("general partner",B409))),88,85),I409="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B409)),ISNUMBER(SEARCH("executive vice",B409))),91,ISNUMBER(SEARCH("svp",B409)),77,TRUE,73),I409="Director",IF(ISNUMBER(SEARCH("principal",B409)),72,71),I409="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B409)),ISNUMBER(SEARCH("physician",B409)),ISNUMBER(SEARCH("doctor",B409)),ISNUMBER(SEARCH("dentist",B409)),ISNUMBER(SEARCH("psychiat",B409)),ISNUMBER(SEARCH("oncolog",B409)),ISNUMBER(SEARCH("neurolog",B409)),ISNUMBER(SEARCH("patholog",B409)),ISNUMBER(SEARCH("medicine",B409)),ISNUMBER(SEARCH("obgyn",B409))),77,OR(ISNUMBER(SEARCH("portfolio manager",B409)),ISNUMBER(SEARCH("wealth advisor",B409))),81,OR(ISNUMBER(SEARCH("lawyer",B409)),ISNUMBER(SEARCH("attorney",B409))),68,ISNUMBER(SEARCH("counsel",B409)),66,ISNUMBER(SEARCH("professor",B409)),63,OR(ISNUMBER(SEARCH("engineer",B409)),ISNUMBER(SEARCH("consultant",B409))),62,ISNUMBER(SEARCH("senior manager",B409)),64,OR(ISNUMBER(SEARCH("realtor",B409)),ISNUMBER(SEARCH("broker",B409)),ISNUMBER(SEARCH("journalist",B409)),ISNUMBER(SEARCH("columnist",B409)),ISNUMBER(SEARCH("trader",B409)),ISNUMBER(SEARCH("actor",B409))),50,TRUE,60)</f>
         <v>62</v>
       </c>
-      <c r="I409" s="10" t="s">
-        <v>1054</v>
-      </c>
-      <c r="J409" s="10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="K409" s="10" t="s">
-        <v>1061</v>
+      <c r="I409" s="29" t="str" cm="1">
+        <f t="array" ref="I409">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
+        <v>Professional</v>
+      </c>
+      <c r="J409" s="29" t="str" cm="1">
+        <f t="array" ref="J409">_xlfn.IFS(H409&gt;=90,"Very High",H409&gt;=80,"High",H409&gt;=56,"Medium",TRUE,"Low")</f>
+        <v>Medium</v>
+      </c>
+      <c r="K409" s="29" t="str" cm="1">
+        <f t="array" ref="K409">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C409)),ISNUMBER(SEARCH("health",C409)),ISNUMBER(SEARCH("medical",C409)),ISNUMBER(SEARCH("clinic",C409)),ISNUMBER(SEARCH("nursing",C409)),ISNUMBER(SEARCH("care cent",C409)),ISNUMBER(SEARCH("physician",B409)),ISNUMBER(SEARCH("doctor",B409)),ISNUMBER(SEARCH("dentist",B409)),ISNUMBER(SEARCH("surgeon",B409)),ISNUMBER(SEARCH("psychiat",B409)),ISNUMBER(SEARCH("medicine",B409))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C409)),ISNUMBER(SEARCH("lawyer",B409)),ISNUMBER(SEARCH("attorney",B409)),ISNUMBER(SEARCH("legal",C409)),ISNUMBER(SEARCH("tetrault",C409)),ISNUMBER(SEARCH("morley",C409)),ISNUMBER(SEARCH("blg",C409)),ISNUMBER(SEARCH("lowy",C409)),ISNUMBER(SEARCH("riley",C409)),ISNUMBER(SEARCH("toomath",C409))),"Law",OR(ISNUMBER(SEARCH("reit",C409)),ISNUMBER(SEARCH("properties",C409)),ISNUMBER(SEARCH("realty",C409)),ISNUMBER(SEARCH("realtor",B409)),ISNUMBER(SEARCH("colliers",C409)),ISNUMBER(SEARCH("re/max",C409)),ISNUMBER(SEARCH("quadreal",C409)),ISNUMBER(SEARCH("vic management",C409))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C409)),ISNUMBER(SEARCH("kpmg",C409)),ISNUMBER(SEARCH("pwc",C409)),ISNUMBER(SEARCH("consulting",C409)),ISNUMBER(SEARCH("consultant",B409)),ISNUMBER(SEARCH("advisory",C409)),ISNUMBER(SEARCH("philanthropic",C409)),ISNUMBER(SEARCH("argyle",C409)),ISNUMBER(SEARCH("quinn",C409))),"Consulting",OR(ISNUMBER(SEARCH("media",C409)),ISNUMBER(SEARCH("news",C409)),ISNUMBER(SEARCH("radio",C409)),ISNUMBER(SEARCH("film",C409)),ISNUMBER(SEARCH("journalist",B409)),ISNUMBER(SEARCH("columnist",B409)),ISNUMBER(SEARCH("globe",C409)),ISNUMBER(SEARCH("marketing",C409)),ISNUMBER(SEARCH("actor",B409))),"Media",OR(ISNUMBER(SEARCH("rbc",C409)),ISNUMBER(SEARCH("cibc",C409)),ISNUMBER(SEARCH("bmo",C409)),ISNUMBER(SEARCH("scotia",C409)),ISNUMBER(SEARCH("bank",C409)),ISNUMBER(SEARCH("capital",C409)),ISNUMBER(SEARCH("wealth",C409)),ISNUMBER(SEARCH("financial",C409)),ISNUMBER(SEARCH("securities",C409)),ISNUMBER(SEARCH("fidelity",C409)),ISNUMBER(SEARCH("guardian",C409)),ISNUMBER(SEARCH("wealthsimple",C409)),ISNUMBER(SEARCH("credit suisse",C409)),ISNUMBER(SEARCH("tmx",C409)),ISNUMBER(SEARCH("investors",C409)),ISNUMBER(SEARCH("trader",B409))),"Finance",OR(ISNUMBER(SEARCH("ventures",C409)),ISNUMBER(SEARCH("private equity",B409)),ISNUMBER(SEARCH("capital partners",C409))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C409)),ISNUMBER(SEARCH("ministry",C409)),ISNUMBER(SEARCH("tribunal",C409)),ISNUMBER(SEARCH("tdsb",C409)),ISNUMBER(SEARCH("public service",C409))),"Government",OR(ISNUMBER(SEARCH("association",C409)),ISNUMBER(SEARCH("institute",C409)),ISNUMBER(SEARCH("foundation",C409))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C409)),ISNUMBER(SEARCH("tech",C409)),ISNUMBER(SEARCH("systems",C409)),ISNUMBER(SEARCH("digital",C409)),ISNUMBER(SEARCH("engineering",C409)),ISNUMBER(SEARCH("solutions",C409))),"Technology",TRUE,"Other")</f>
+        <v>Consulting</v>
       </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="25" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
       <c r="B410" s="25" t="s">
-        <v>289</v>
+        <v>1010</v>
       </c>
       <c r="C410" s="25" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D410" s="25" t="s">
-        <v>1391</v>
+        <v>1380</v>
       </c>
       <c r="E410" s="30">
-        <v>1704000</v>
+        <v>1570000</v>
       </c>
       <c r="F410" s="26">
-        <v>40602</v>
+        <v>40878</v>
       </c>
       <c r="G410" s="27">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="H410" s="28" cm="1">
         <f t="array" ref="H410">_xlfn.IFS(I410="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B410)),80,96),I410="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B410)),ISNUMBER(SEARCH("chief executive",B410))),95,91),I410="Managing Director",86,I410="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B410)),ISNUMBER(SEARCH("general partner",B410))),88,85),I410="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B410)),ISNUMBER(SEARCH("executive vice",B410))),91,ISNUMBER(SEARCH("svp",B410)),77,TRUE,73),I410="Director",IF(ISNUMBER(SEARCH("principal",B410)),72,71),I410="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B410)),ISNUMBER(SEARCH("physician",B410)),ISNUMBER(SEARCH("doctor",B410)),ISNUMBER(SEARCH("dentist",B410)),ISNUMBER(SEARCH("psychiat",B410)),ISNUMBER(SEARCH("oncolog",B410)),ISNUMBER(SEARCH("neurolog",B410)),ISNUMBER(SEARCH("patholog",B410)),ISNUMBER(SEARCH("medicine",B410)),ISNUMBER(SEARCH("obgyn",B410))),77,OR(ISNUMBER(SEARCH("portfolio manager",B410)),ISNUMBER(SEARCH("wealth advisor",B410))),81,OR(ISNUMBER(SEARCH("lawyer",B410)),ISNUMBER(SEARCH("attorney",B410))),68,ISNUMBER(SEARCH("counsel",B410)),66,ISNUMBER(SEARCH("professor",B410)),63,OR(ISNUMBER(SEARCH("engineer",B410)),ISNUMBER(SEARCH("consultant",B410))),62,ISNUMBER(SEARCH("senior manager",B410)),64,OR(ISNUMBER(SEARCH("realtor",B410)),ISNUMBER(SEARCH("broker",B410)),ISNUMBER(SEARCH("journalist",B410)),ISNUMBER(SEARCH("columnist",B410)),ISNUMBER(SEARCH("trader",B410)),ISNUMBER(SEARCH("actor",B410))),50,TRUE,60)</f>
@@ -19841,69 +19833,65 @@
       </c>
       <c r="K410" s="29" t="str" cm="1">
         <f t="array" ref="K410">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C410)),ISNUMBER(SEARCH("health",C410)),ISNUMBER(SEARCH("medical",C410)),ISNUMBER(SEARCH("clinic",C410)),ISNUMBER(SEARCH("nursing",C410)),ISNUMBER(SEARCH("care cent",C410)),ISNUMBER(SEARCH("physician",B410)),ISNUMBER(SEARCH("doctor",B410)),ISNUMBER(SEARCH("dentist",B410)),ISNUMBER(SEARCH("surgeon",B410)),ISNUMBER(SEARCH("psychiat",B410)),ISNUMBER(SEARCH("medicine",B410))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C410)),ISNUMBER(SEARCH("lawyer",B410)),ISNUMBER(SEARCH("attorney",B410)),ISNUMBER(SEARCH("legal",C410)),ISNUMBER(SEARCH("tetrault",C410)),ISNUMBER(SEARCH("morley",C410)),ISNUMBER(SEARCH("blg",C410)),ISNUMBER(SEARCH("lowy",C410)),ISNUMBER(SEARCH("riley",C410)),ISNUMBER(SEARCH("toomath",C410))),"Law",OR(ISNUMBER(SEARCH("reit",C410)),ISNUMBER(SEARCH("properties",C410)),ISNUMBER(SEARCH("realty",C410)),ISNUMBER(SEARCH("realtor",B410)),ISNUMBER(SEARCH("colliers",C410)),ISNUMBER(SEARCH("re/max",C410)),ISNUMBER(SEARCH("quadreal",C410)),ISNUMBER(SEARCH("vic management",C410))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C410)),ISNUMBER(SEARCH("kpmg",C410)),ISNUMBER(SEARCH("pwc",C410)),ISNUMBER(SEARCH("consulting",C410)),ISNUMBER(SEARCH("consultant",B410)),ISNUMBER(SEARCH("advisory",C410)),ISNUMBER(SEARCH("philanthropic",C410)),ISNUMBER(SEARCH("argyle",C410)),ISNUMBER(SEARCH("quinn",C410))),"Consulting",OR(ISNUMBER(SEARCH("media",C410)),ISNUMBER(SEARCH("news",C410)),ISNUMBER(SEARCH("radio",C410)),ISNUMBER(SEARCH("film",C410)),ISNUMBER(SEARCH("journalist",B410)),ISNUMBER(SEARCH("columnist",B410)),ISNUMBER(SEARCH("globe",C410)),ISNUMBER(SEARCH("marketing",C410)),ISNUMBER(SEARCH("actor",B410))),"Media",OR(ISNUMBER(SEARCH("rbc",C410)),ISNUMBER(SEARCH("cibc",C410)),ISNUMBER(SEARCH("bmo",C410)),ISNUMBER(SEARCH("scotia",C410)),ISNUMBER(SEARCH("bank",C410)),ISNUMBER(SEARCH("capital",C410)),ISNUMBER(SEARCH("wealth",C410)),ISNUMBER(SEARCH("financial",C410)),ISNUMBER(SEARCH("securities",C410)),ISNUMBER(SEARCH("fidelity",C410)),ISNUMBER(SEARCH("guardian",C410)),ISNUMBER(SEARCH("wealthsimple",C410)),ISNUMBER(SEARCH("credit suisse",C410)),ISNUMBER(SEARCH("tmx",C410)),ISNUMBER(SEARCH("investors",C410)),ISNUMBER(SEARCH("trader",B410))),"Finance",OR(ISNUMBER(SEARCH("ventures",C410)),ISNUMBER(SEARCH("private equity",B410)),ISNUMBER(SEARCH("capital partners",C410))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C410)),ISNUMBER(SEARCH("ministry",C410)),ISNUMBER(SEARCH("tribunal",C410)),ISNUMBER(SEARCH("tdsb",C410)),ISNUMBER(SEARCH("public service",C410))),"Government",OR(ISNUMBER(SEARCH("association",C410)),ISNUMBER(SEARCH("institute",C410)),ISNUMBER(SEARCH("foundation",C410))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C410)),ISNUMBER(SEARCH("tech",C410)),ISNUMBER(SEARCH("systems",C410)),ISNUMBER(SEARCH("digital",C410)),ISNUMBER(SEARCH("engineering",C410)),ISNUMBER(SEARCH("solutions",C410))),"Technology",TRUE,"Other")</f>
-        <v>Consulting</v>
+        <v>Other</v>
       </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A411" s="25" t="s">
-        <v>1402</v>
-      </c>
-      <c r="B411" s="25" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C411" s="25" t="s">
-        <v>1463</v>
-      </c>
-      <c r="D411" s="25" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E411" s="30">
-        <v>1570000</v>
-      </c>
-      <c r="F411" s="26">
-        <v>40878</v>
-      </c>
-      <c r="G411" s="27">
-        <v>3.17</v>
-      </c>
-      <c r="H411" s="28" cm="1">
-        <f t="array" ref="H411">_xlfn.IFS(I411="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B411)),80,96),I411="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B411)),ISNUMBER(SEARCH("chief executive",B411))),95,91),I411="Managing Director",86,I411="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B411)),ISNUMBER(SEARCH("general partner",B411))),88,85),I411="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B411)),ISNUMBER(SEARCH("executive vice",B411))),91,ISNUMBER(SEARCH("svp",B411)),77,TRUE,73),I411="Director",IF(ISNUMBER(SEARCH("principal",B411)),72,71),I411="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B411)),ISNUMBER(SEARCH("physician",B411)),ISNUMBER(SEARCH("doctor",B411)),ISNUMBER(SEARCH("dentist",B411)),ISNUMBER(SEARCH("psychiat",B411)),ISNUMBER(SEARCH("oncolog",B411)),ISNUMBER(SEARCH("neurolog",B411)),ISNUMBER(SEARCH("patholog",B411)),ISNUMBER(SEARCH("medicine",B411)),ISNUMBER(SEARCH("obgyn",B411))),77,OR(ISNUMBER(SEARCH("portfolio manager",B411)),ISNUMBER(SEARCH("wealth advisor",B411))),81,OR(ISNUMBER(SEARCH("lawyer",B411)),ISNUMBER(SEARCH("attorney",B411))),68,ISNUMBER(SEARCH("counsel",B411)),66,ISNUMBER(SEARCH("professor",B411)),63,OR(ISNUMBER(SEARCH("engineer",B411)),ISNUMBER(SEARCH("consultant",B411))),62,ISNUMBER(SEARCH("senior manager",B411)),64,OR(ISNUMBER(SEARCH("realtor",B411)),ISNUMBER(SEARCH("broker",B411)),ISNUMBER(SEARCH("journalist",B411)),ISNUMBER(SEARCH("columnist",B411)),ISNUMBER(SEARCH("trader",B411)),ISNUMBER(SEARCH("actor",B411))),50,TRUE,60)</f>
+      <c r="A411" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="C411" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="D411" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="E411" s="16">
+        <v>1252000</v>
+      </c>
+      <c r="F411" s="32">
+        <v>40786</v>
+      </c>
+      <c r="G411" s="3">
+        <v>3.69</v>
+      </c>
+      <c r="H411" s="9">
         <v>62</v>
       </c>
-      <c r="I411" s="29" t="str" cm="1">
-        <f t="array" ref="I411">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
-        <v>Professional</v>
-      </c>
-      <c r="J411" s="29" t="str" cm="1">
-        <f t="array" ref="J411">_xlfn.IFS(H411&gt;=90,"Very High",H411&gt;=80,"High",H411&gt;=56,"Medium",TRUE,"Low")</f>
-        <v>Medium</v>
-      </c>
-      <c r="K411" s="29" t="str" cm="1">
-        <f t="array" ref="K411">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C411)),ISNUMBER(SEARCH("health",C411)),ISNUMBER(SEARCH("medical",C411)),ISNUMBER(SEARCH("clinic",C411)),ISNUMBER(SEARCH("nursing",C411)),ISNUMBER(SEARCH("care cent",C411)),ISNUMBER(SEARCH("physician",B411)),ISNUMBER(SEARCH("doctor",B411)),ISNUMBER(SEARCH("dentist",B411)),ISNUMBER(SEARCH("surgeon",B411)),ISNUMBER(SEARCH("psychiat",B411)),ISNUMBER(SEARCH("medicine",B411))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C411)),ISNUMBER(SEARCH("lawyer",B411)),ISNUMBER(SEARCH("attorney",B411)),ISNUMBER(SEARCH("legal",C411)),ISNUMBER(SEARCH("tetrault",C411)),ISNUMBER(SEARCH("morley",C411)),ISNUMBER(SEARCH("blg",C411)),ISNUMBER(SEARCH("lowy",C411)),ISNUMBER(SEARCH("riley",C411)),ISNUMBER(SEARCH("toomath",C411))),"Law",OR(ISNUMBER(SEARCH("reit",C411)),ISNUMBER(SEARCH("properties",C411)),ISNUMBER(SEARCH("realty",C411)),ISNUMBER(SEARCH("realtor",B411)),ISNUMBER(SEARCH("colliers",C411)),ISNUMBER(SEARCH("re/max",C411)),ISNUMBER(SEARCH("quadreal",C411)),ISNUMBER(SEARCH("vic management",C411))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C411)),ISNUMBER(SEARCH("kpmg",C411)),ISNUMBER(SEARCH("pwc",C411)),ISNUMBER(SEARCH("consulting",C411)),ISNUMBER(SEARCH("consultant",B411)),ISNUMBER(SEARCH("advisory",C411)),ISNUMBER(SEARCH("philanthropic",C411)),ISNUMBER(SEARCH("argyle",C411)),ISNUMBER(SEARCH("quinn",C411))),"Consulting",OR(ISNUMBER(SEARCH("media",C411)),ISNUMBER(SEARCH("news",C411)),ISNUMBER(SEARCH("radio",C411)),ISNUMBER(SEARCH("film",C411)),ISNUMBER(SEARCH("journalist",B411)),ISNUMBER(SEARCH("columnist",B411)),ISNUMBER(SEARCH("globe",C411)),ISNUMBER(SEARCH("marketing",C411)),ISNUMBER(SEARCH("actor",B411))),"Media",OR(ISNUMBER(SEARCH("rbc",C411)),ISNUMBER(SEARCH("cibc",C411)),ISNUMBER(SEARCH("bmo",C411)),ISNUMBER(SEARCH("scotia",C411)),ISNUMBER(SEARCH("bank",C411)),ISNUMBER(SEARCH("capital",C411)),ISNUMBER(SEARCH("wealth",C411)),ISNUMBER(SEARCH("financial",C411)),ISNUMBER(SEARCH("securities",C411)),ISNUMBER(SEARCH("fidelity",C411)),ISNUMBER(SEARCH("guardian",C411)),ISNUMBER(SEARCH("wealthsimple",C411)),ISNUMBER(SEARCH("credit suisse",C411)),ISNUMBER(SEARCH("tmx",C411)),ISNUMBER(SEARCH("investors",C411)),ISNUMBER(SEARCH("trader",B411))),"Finance",OR(ISNUMBER(SEARCH("ventures",C411)),ISNUMBER(SEARCH("private equity",B411)),ISNUMBER(SEARCH("capital partners",C411))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C411)),ISNUMBER(SEARCH("ministry",C411)),ISNUMBER(SEARCH("tribunal",C411)),ISNUMBER(SEARCH("tdsb",C411)),ISNUMBER(SEARCH("public service",C411))),"Government",OR(ISNUMBER(SEARCH("association",C411)),ISNUMBER(SEARCH("institute",C411)),ISNUMBER(SEARCH("foundation",C411))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C411)),ISNUMBER(SEARCH("tech",C411)),ISNUMBER(SEARCH("systems",C411)),ISNUMBER(SEARCH("digital",C411)),ISNUMBER(SEARCH("engineering",C411)),ISNUMBER(SEARCH("solutions",C411))),"Technology",TRUE,"Other")</f>
-        <v>Other</v>
+      <c r="I411" s="10" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J411" s="10" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K411" s="10" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A412" s="7" t="s">
-        <v>891</v>
-      </c>
-      <c r="B412" s="7" t="s">
-        <v>892</v>
-      </c>
-      <c r="C412" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="D412" s="7" t="s">
-        <v>894</v>
-      </c>
-      <c r="E412" s="16">
-        <v>1252000</v>
-      </c>
-      <c r="F412" s="32">
-        <v>40786</v>
-      </c>
-      <c r="G412" s="3">
-        <v>3.69</v>
+      <c r="A412" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="C412" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="D412" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="E412" s="18">
+        <v>1180000</v>
+      </c>
+      <c r="F412" s="5">
+        <v>42521</v>
+      </c>
+      <c r="G412" s="6">
+        <v>4.25</v>
       </c>
       <c r="H412" s="9">
         <v>62</v>
@@ -19915,30 +19903,30 @@
         <v>1055</v>
       </c>
       <c r="K412" s="10" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>912</v>
+        <v>925</v>
       </c>
       <c r="E413" s="18">
-        <v>1180000</v>
+        <v>1100000</v>
       </c>
       <c r="F413" s="5">
-        <v>42521</v>
+        <v>41095</v>
       </c>
       <c r="G413" s="6">
-        <v>4.25</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="H413" s="9">
         <v>62</v>
@@ -19953,62 +19941,66 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A414" s="4" t="s">
-        <v>922</v>
-      </c>
-      <c r="B414" s="4" t="s">
-        <v>923</v>
-      </c>
-      <c r="C414" s="4" t="s">
-        <v>924</v>
-      </c>
-      <c r="D414" s="4" t="s">
-        <v>925</v>
-      </c>
-      <c r="E414" s="18">
-        <v>1100000</v>
-      </c>
-      <c r="F414" s="5">
-        <v>41095</v>
-      </c>
-      <c r="G414" s="6">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="H414" s="9">
-        <v>62</v>
-      </c>
-      <c r="I414" s="10" t="s">
-        <v>1054</v>
-      </c>
-      <c r="J414" s="10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="K414" s="10" t="s">
-        <v>1061</v>
+    <row r="414" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="25" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B414" s="25" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C414" s="25" t="s">
+        <v>697</v>
+      </c>
+      <c r="D414" s="25" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E414" s="30" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F414" s="26">
+        <v>42633</v>
+      </c>
+      <c r="G414" s="27">
+        <v>3.14</v>
+      </c>
+      <c r="H414" s="28" cm="1">
+        <f t="array" ref="H414">_xlfn.IFS(I414="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B414)),80,96),I414="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B414)),ISNUMBER(SEARCH("chief executive",B414))),95,91),I414="Managing Director",86,I414="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B414)),ISNUMBER(SEARCH("general partner",B414))),88,85),I414="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B414)),ISNUMBER(SEARCH("executive vice",B414))),91,ISNUMBER(SEARCH("svp",B414)),77,TRUE,73),I414="Director",IF(ISNUMBER(SEARCH("principal",B414)),72,71),I414="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B414)),ISNUMBER(SEARCH("physician",B414)),ISNUMBER(SEARCH("doctor",B414)),ISNUMBER(SEARCH("dentist",B414)),ISNUMBER(SEARCH("psychiat",B414)),ISNUMBER(SEARCH("oncolog",B414)),ISNUMBER(SEARCH("neurolog",B414)),ISNUMBER(SEARCH("patholog",B414)),ISNUMBER(SEARCH("medicine",B414)),ISNUMBER(SEARCH("obgyn",B414))),77,OR(ISNUMBER(SEARCH("portfolio manager",B414)),ISNUMBER(SEARCH("wealth advisor",B414))),81,OR(ISNUMBER(SEARCH("lawyer",B414)),ISNUMBER(SEARCH("attorney",B414))),68,ISNUMBER(SEARCH("counsel",B414)),66,ISNUMBER(SEARCH("professor",B414)),63,OR(ISNUMBER(SEARCH("engineer",B414)),ISNUMBER(SEARCH("consultant",B414))),62,ISNUMBER(SEARCH("senior manager",B414)),64,OR(ISNUMBER(SEARCH("realtor",B414)),ISNUMBER(SEARCH("broker",B414)),ISNUMBER(SEARCH("journalist",B414)),ISNUMBER(SEARCH("columnist",B414)),ISNUMBER(SEARCH("trader",B414)),ISNUMBER(SEARCH("actor",B414))),50,TRUE,60)</f>
+        <v>60</v>
+      </c>
+      <c r="I414" s="29" t="str" cm="1">
+        <f t="array" ref="I414">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B414,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
+        <v>Professional</v>
+      </c>
+      <c r="J414" s="29" t="str" cm="1">
+        <f t="array" ref="J414">_xlfn.IFS(H414&gt;=90,"Very High",H414&gt;=80,"High",H414&gt;=56,"Medium",TRUE,"Low")</f>
+        <v>Medium</v>
+      </c>
+      <c r="K414" s="29" t="str" cm="1">
+        <f t="array" ref="K414">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C414)),ISNUMBER(SEARCH("health",C414)),ISNUMBER(SEARCH("medical",C414)),ISNUMBER(SEARCH("clinic",C414)),ISNUMBER(SEARCH("nursing",C414)),ISNUMBER(SEARCH("care cent",C414)),ISNUMBER(SEARCH("physician",B414)),ISNUMBER(SEARCH("doctor",B414)),ISNUMBER(SEARCH("dentist",B414)),ISNUMBER(SEARCH("surgeon",B414)),ISNUMBER(SEARCH("psychiat",B414)),ISNUMBER(SEARCH("medicine",B414))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C414)),ISNUMBER(SEARCH("lawyer",B414)),ISNUMBER(SEARCH("attorney",B414)),ISNUMBER(SEARCH("legal",C414)),ISNUMBER(SEARCH("tetrault",C414)),ISNUMBER(SEARCH("morley",C414)),ISNUMBER(SEARCH("blg",C414)),ISNUMBER(SEARCH("lowy",C414)),ISNUMBER(SEARCH("riley",C414)),ISNUMBER(SEARCH("toomath",C414))),"Law",OR(ISNUMBER(SEARCH("reit",C414)),ISNUMBER(SEARCH("properties",C414)),ISNUMBER(SEARCH("realty",C414)),ISNUMBER(SEARCH("realtor",B414)),ISNUMBER(SEARCH("colliers",C414)),ISNUMBER(SEARCH("re/max",C414)),ISNUMBER(SEARCH("quadreal",C414)),ISNUMBER(SEARCH("vic management",C414))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C414)),ISNUMBER(SEARCH("kpmg",C414)),ISNUMBER(SEARCH("pwc",C414)),ISNUMBER(SEARCH("consulting",C414)),ISNUMBER(SEARCH("consultant",B414)),ISNUMBER(SEARCH("advisory",C414)),ISNUMBER(SEARCH("philanthropic",C414)),ISNUMBER(SEARCH("argyle",C414)),ISNUMBER(SEARCH("quinn",C414))),"Consulting",OR(ISNUMBER(SEARCH("media",C414)),ISNUMBER(SEARCH("news",C414)),ISNUMBER(SEARCH("radio",C414)),ISNUMBER(SEARCH("film",C414)),ISNUMBER(SEARCH("journalist",B414)),ISNUMBER(SEARCH("columnist",B414)),ISNUMBER(SEARCH("globe",C414)),ISNUMBER(SEARCH("marketing",C414)),ISNUMBER(SEARCH("actor",B414))),"Media",OR(ISNUMBER(SEARCH("rbc",C414)),ISNUMBER(SEARCH("cibc",C414)),ISNUMBER(SEARCH("bmo",C414)),ISNUMBER(SEARCH("scotia",C414)),ISNUMBER(SEARCH("bank",C414)),ISNUMBER(SEARCH("capital",C414)),ISNUMBER(SEARCH("wealth",C414)),ISNUMBER(SEARCH("financial",C414)),ISNUMBER(SEARCH("securities",C414)),ISNUMBER(SEARCH("fidelity",C414)),ISNUMBER(SEARCH("guardian",C414)),ISNUMBER(SEARCH("wealthsimple",C414)),ISNUMBER(SEARCH("credit suisse",C414)),ISNUMBER(SEARCH("tmx",C414)),ISNUMBER(SEARCH("investors",C414)),ISNUMBER(SEARCH("trader",B414))),"Finance",OR(ISNUMBER(SEARCH("ventures",C414)),ISNUMBER(SEARCH("private equity",B414)),ISNUMBER(SEARCH("capital partners",C414))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C414)),ISNUMBER(SEARCH("ministry",C414)),ISNUMBER(SEARCH("tribunal",C414)),ISNUMBER(SEARCH("tdsb",C414)),ISNUMBER(SEARCH("public service",C414))),"Government",OR(ISNUMBER(SEARCH("association",C414)),ISNUMBER(SEARCH("institute",C414)),ISNUMBER(SEARCH("foundation",C414))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C414)),ISNUMBER(SEARCH("tech",C414)),ISNUMBER(SEARCH("systems",C414)),ISNUMBER(SEARCH("digital",C414)),ISNUMBER(SEARCH("engineering",C414)),ISNUMBER(SEARCH("solutions",C414))),"Technology",TRUE,"Other")</f>
+        <v>Finance</v>
       </c>
     </row>
     <row r="415" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A415" s="25" t="s">
-        <v>1440</v>
+        <v>1376</v>
       </c>
       <c r="B415" s="25" t="s">
-        <v>1477</v>
+        <v>1541</v>
       </c>
       <c r="C415" s="25" t="s">
-        <v>697</v>
+        <v>1467</v>
       </c>
       <c r="D415" s="25" t="s">
-        <v>1427</v>
+        <v>1377</v>
       </c>
       <c r="E415" s="30" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F415" s="26">
-        <v>42633</v>
+        <v>45716</v>
       </c>
       <c r="G415" s="27">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="H415" s="28" cm="1">
         <f t="array" ref="H415">_xlfn.IFS(I415="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B415)),80,96),I415="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B415)),ISNUMBER(SEARCH("chief executive",B415))),95,91),I415="Managing Director",86,I415="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B415)),ISNUMBER(SEARCH("general partner",B415))),88,85),I415="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B415)),ISNUMBER(SEARCH("executive vice",B415))),91,ISNUMBER(SEARCH("svp",B415)),77,TRUE,73),I415="Director",IF(ISNUMBER(SEARCH("principal",B415)),72,71),I415="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B415)),ISNUMBER(SEARCH("physician",B415)),ISNUMBER(SEARCH("doctor",B415)),ISNUMBER(SEARCH("dentist",B415)),ISNUMBER(SEARCH("psychiat",B415)),ISNUMBER(SEARCH("oncolog",B415)),ISNUMBER(SEARCH("neurolog",B415)),ISNUMBER(SEARCH("patholog",B415)),ISNUMBER(SEARCH("medicine",B415)),ISNUMBER(SEARCH("obgyn",B415))),77,OR(ISNUMBER(SEARCH("portfolio manager",B415)),ISNUMBER(SEARCH("wealth advisor",B415))),81,OR(ISNUMBER(SEARCH("lawyer",B415)),ISNUMBER(SEARCH("attorney",B415))),68,ISNUMBER(SEARCH("counsel",B415)),66,ISNUMBER(SEARCH("professor",B415)),63,OR(ISNUMBER(SEARCH("engineer",B415)),ISNUMBER(SEARCH("consultant",B415))),62,ISNUMBER(SEARCH("senior manager",B415)),64,OR(ISNUMBER(SEARCH("realtor",B415)),ISNUMBER(SEARCH("broker",B415)),ISNUMBER(SEARCH("journalist",B415)),ISNUMBER(SEARCH("columnist",B415)),ISNUMBER(SEARCH("trader",B415)),ISNUMBER(SEARCH("actor",B415))),50,TRUE,60)</f>
@@ -20024,69 +20016,65 @@
       </c>
       <c r="K415" s="29" t="str" cm="1">
         <f t="array" ref="K415">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C415)),ISNUMBER(SEARCH("health",C415)),ISNUMBER(SEARCH("medical",C415)),ISNUMBER(SEARCH("clinic",C415)),ISNUMBER(SEARCH("nursing",C415)),ISNUMBER(SEARCH("care cent",C415)),ISNUMBER(SEARCH("physician",B415)),ISNUMBER(SEARCH("doctor",B415)),ISNUMBER(SEARCH("dentist",B415)),ISNUMBER(SEARCH("surgeon",B415)),ISNUMBER(SEARCH("psychiat",B415)),ISNUMBER(SEARCH("medicine",B415))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C415)),ISNUMBER(SEARCH("lawyer",B415)),ISNUMBER(SEARCH("attorney",B415)),ISNUMBER(SEARCH("legal",C415)),ISNUMBER(SEARCH("tetrault",C415)),ISNUMBER(SEARCH("morley",C415)),ISNUMBER(SEARCH("blg",C415)),ISNUMBER(SEARCH("lowy",C415)),ISNUMBER(SEARCH("riley",C415)),ISNUMBER(SEARCH("toomath",C415))),"Law",OR(ISNUMBER(SEARCH("reit",C415)),ISNUMBER(SEARCH("properties",C415)),ISNUMBER(SEARCH("realty",C415)),ISNUMBER(SEARCH("realtor",B415)),ISNUMBER(SEARCH("colliers",C415)),ISNUMBER(SEARCH("re/max",C415)),ISNUMBER(SEARCH("quadreal",C415)),ISNUMBER(SEARCH("vic management",C415))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C415)),ISNUMBER(SEARCH("kpmg",C415)),ISNUMBER(SEARCH("pwc",C415)),ISNUMBER(SEARCH("consulting",C415)),ISNUMBER(SEARCH("consultant",B415)),ISNUMBER(SEARCH("advisory",C415)),ISNUMBER(SEARCH("philanthropic",C415)),ISNUMBER(SEARCH("argyle",C415)),ISNUMBER(SEARCH("quinn",C415))),"Consulting",OR(ISNUMBER(SEARCH("media",C415)),ISNUMBER(SEARCH("news",C415)),ISNUMBER(SEARCH("radio",C415)),ISNUMBER(SEARCH("film",C415)),ISNUMBER(SEARCH("journalist",B415)),ISNUMBER(SEARCH("columnist",B415)),ISNUMBER(SEARCH("globe",C415)),ISNUMBER(SEARCH("marketing",C415)),ISNUMBER(SEARCH("actor",B415))),"Media",OR(ISNUMBER(SEARCH("rbc",C415)),ISNUMBER(SEARCH("cibc",C415)),ISNUMBER(SEARCH("bmo",C415)),ISNUMBER(SEARCH("scotia",C415)),ISNUMBER(SEARCH("bank",C415)),ISNUMBER(SEARCH("capital",C415)),ISNUMBER(SEARCH("wealth",C415)),ISNUMBER(SEARCH("financial",C415)),ISNUMBER(SEARCH("securities",C415)),ISNUMBER(SEARCH("fidelity",C415)),ISNUMBER(SEARCH("guardian",C415)),ISNUMBER(SEARCH("wealthsimple",C415)),ISNUMBER(SEARCH("credit suisse",C415)),ISNUMBER(SEARCH("tmx",C415)),ISNUMBER(SEARCH("investors",C415)),ISNUMBER(SEARCH("trader",B415))),"Finance",OR(ISNUMBER(SEARCH("ventures",C415)),ISNUMBER(SEARCH("private equity",B415)),ISNUMBER(SEARCH("capital partners",C415))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C415)),ISNUMBER(SEARCH("ministry",C415)),ISNUMBER(SEARCH("tribunal",C415)),ISNUMBER(SEARCH("tdsb",C415)),ISNUMBER(SEARCH("public service",C415))),"Government",OR(ISNUMBER(SEARCH("association",C415)),ISNUMBER(SEARCH("institute",C415)),ISNUMBER(SEARCH("foundation",C415))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C415)),ISNUMBER(SEARCH("tech",C415)),ISNUMBER(SEARCH("systems",C415)),ISNUMBER(SEARCH("digital",C415)),ISNUMBER(SEARCH("engineering",C415)),ISNUMBER(SEARCH("solutions",C415))),"Technology",TRUE,"Other")</f>
-        <v>Finance</v>
+        <v>Healthcare</v>
       </c>
     </row>
     <row r="416" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="25" t="s">
-        <v>1380</v>
-      </c>
-      <c r="B416" s="25" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C416" s="25" t="s">
-        <v>1471</v>
-      </c>
-      <c r="D416" s="25" t="s">
-        <v>1381</v>
-      </c>
-      <c r="E416" s="30" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F416" s="26">
-        <v>45716</v>
-      </c>
-      <c r="G416" s="27">
-        <v>3.24</v>
-      </c>
-      <c r="H416" s="28" cm="1">
-        <f t="array" ref="H416">_xlfn.IFS(I416="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B416)),80,96),I416="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B416)),ISNUMBER(SEARCH("chief executive",B416))),95,91),I416="Managing Director",86,I416="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B416)),ISNUMBER(SEARCH("general partner",B416))),88,85),I416="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B416)),ISNUMBER(SEARCH("executive vice",B416))),91,ISNUMBER(SEARCH("svp",B416)),77,TRUE,73),I416="Director",IF(ISNUMBER(SEARCH("principal",B416)),72,71),I416="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B416)),ISNUMBER(SEARCH("physician",B416)),ISNUMBER(SEARCH("doctor",B416)),ISNUMBER(SEARCH("dentist",B416)),ISNUMBER(SEARCH("psychiat",B416)),ISNUMBER(SEARCH("oncolog",B416)),ISNUMBER(SEARCH("neurolog",B416)),ISNUMBER(SEARCH("patholog",B416)),ISNUMBER(SEARCH("medicine",B416)),ISNUMBER(SEARCH("obgyn",B416))),77,OR(ISNUMBER(SEARCH("portfolio manager",B416)),ISNUMBER(SEARCH("wealth advisor",B416))),81,OR(ISNUMBER(SEARCH("lawyer",B416)),ISNUMBER(SEARCH("attorney",B416))),68,ISNUMBER(SEARCH("counsel",B416)),66,ISNUMBER(SEARCH("professor",B416)),63,OR(ISNUMBER(SEARCH("engineer",B416)),ISNUMBER(SEARCH("consultant",B416))),62,ISNUMBER(SEARCH("senior manager",B416)),64,OR(ISNUMBER(SEARCH("realtor",B416)),ISNUMBER(SEARCH("broker",B416)),ISNUMBER(SEARCH("journalist",B416)),ISNUMBER(SEARCH("columnist",B416)),ISNUMBER(SEARCH("trader",B416)),ISNUMBER(SEARCH("actor",B416))),50,TRUE,60)</f>
+      <c r="A416" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="E416" s="20" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F416" s="5">
+        <v>43808</v>
+      </c>
+      <c r="G416" s="6">
+        <v>3.94</v>
+      </c>
+      <c r="H416" s="9">
         <v>60</v>
       </c>
-      <c r="I416" s="29" t="str" cm="1">
-        <f t="array" ref="I416">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B416,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
-        <v>Professional</v>
-      </c>
-      <c r="J416" s="29" t="str" cm="1">
-        <f t="array" ref="J416">_xlfn.IFS(H416&gt;=90,"Very High",H416&gt;=80,"High",H416&gt;=56,"Medium",TRUE,"Low")</f>
-        <v>Medium</v>
-      </c>
-      <c r="K416" s="29" t="str" cm="1">
-        <f t="array" ref="K416">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C416)),ISNUMBER(SEARCH("health",C416)),ISNUMBER(SEARCH("medical",C416)),ISNUMBER(SEARCH("clinic",C416)),ISNUMBER(SEARCH("nursing",C416)),ISNUMBER(SEARCH("care cent",C416)),ISNUMBER(SEARCH("physician",B416)),ISNUMBER(SEARCH("doctor",B416)),ISNUMBER(SEARCH("dentist",B416)),ISNUMBER(SEARCH("surgeon",B416)),ISNUMBER(SEARCH("psychiat",B416)),ISNUMBER(SEARCH("medicine",B416))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C416)),ISNUMBER(SEARCH("lawyer",B416)),ISNUMBER(SEARCH("attorney",B416)),ISNUMBER(SEARCH("legal",C416)),ISNUMBER(SEARCH("tetrault",C416)),ISNUMBER(SEARCH("morley",C416)),ISNUMBER(SEARCH("blg",C416)),ISNUMBER(SEARCH("lowy",C416)),ISNUMBER(SEARCH("riley",C416)),ISNUMBER(SEARCH("toomath",C416))),"Law",OR(ISNUMBER(SEARCH("reit",C416)),ISNUMBER(SEARCH("properties",C416)),ISNUMBER(SEARCH("realty",C416)),ISNUMBER(SEARCH("realtor",B416)),ISNUMBER(SEARCH("colliers",C416)),ISNUMBER(SEARCH("re/max",C416)),ISNUMBER(SEARCH("quadreal",C416)),ISNUMBER(SEARCH("vic management",C416))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C416)),ISNUMBER(SEARCH("kpmg",C416)),ISNUMBER(SEARCH("pwc",C416)),ISNUMBER(SEARCH("consulting",C416)),ISNUMBER(SEARCH("consultant",B416)),ISNUMBER(SEARCH("advisory",C416)),ISNUMBER(SEARCH("philanthropic",C416)),ISNUMBER(SEARCH("argyle",C416)),ISNUMBER(SEARCH("quinn",C416))),"Consulting",OR(ISNUMBER(SEARCH("media",C416)),ISNUMBER(SEARCH("news",C416)),ISNUMBER(SEARCH("radio",C416)),ISNUMBER(SEARCH("film",C416)),ISNUMBER(SEARCH("journalist",B416)),ISNUMBER(SEARCH("columnist",B416)),ISNUMBER(SEARCH("globe",C416)),ISNUMBER(SEARCH("marketing",C416)),ISNUMBER(SEARCH("actor",B416))),"Media",OR(ISNUMBER(SEARCH("rbc",C416)),ISNUMBER(SEARCH("cibc",C416)),ISNUMBER(SEARCH("bmo",C416)),ISNUMBER(SEARCH("scotia",C416)),ISNUMBER(SEARCH("bank",C416)),ISNUMBER(SEARCH("capital",C416)),ISNUMBER(SEARCH("wealth",C416)),ISNUMBER(SEARCH("financial",C416)),ISNUMBER(SEARCH("securities",C416)),ISNUMBER(SEARCH("fidelity",C416)),ISNUMBER(SEARCH("guardian",C416)),ISNUMBER(SEARCH("wealthsimple",C416)),ISNUMBER(SEARCH("credit suisse",C416)),ISNUMBER(SEARCH("tmx",C416)),ISNUMBER(SEARCH("investors",C416)),ISNUMBER(SEARCH("trader",B416))),"Finance",OR(ISNUMBER(SEARCH("ventures",C416)),ISNUMBER(SEARCH("private equity",B416)),ISNUMBER(SEARCH("capital partners",C416))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C416)),ISNUMBER(SEARCH("ministry",C416)),ISNUMBER(SEARCH("tribunal",C416)),ISNUMBER(SEARCH("tdsb",C416)),ISNUMBER(SEARCH("public service",C416))),"Government",OR(ISNUMBER(SEARCH("association",C416)),ISNUMBER(SEARCH("institute",C416)),ISNUMBER(SEARCH("foundation",C416))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C416)),ISNUMBER(SEARCH("tech",C416)),ISNUMBER(SEARCH("systems",C416)),ISNUMBER(SEARCH("digital",C416)),ISNUMBER(SEARCH("engineering",C416)),ISNUMBER(SEARCH("solutions",C416))),"Technology",TRUE,"Other")</f>
-        <v>Healthcare</v>
+      <c r="I416" s="29" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J416" s="10" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K416" s="10" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="417" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
-        <v>988</v>
+        <v>1032</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1515</v>
+        <v>1552</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>989</v>
+        <v>1033</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>990</v>
+        <v>1034</v>
       </c>
       <c r="E417" s="20" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F417" s="5">
-        <v>43808</v>
-      </c>
-      <c r="G417" s="6">
-        <v>3.94</v>
+        <v>40854</v>
+      </c>
+      <c r="G417" s="3">
+        <v>4.08</v>
       </c>
       <c r="H417" s="9">
         <v>60</v>
@@ -20098,65 +20086,69 @@
         <v>1055</v>
       </c>
       <c r="K417" s="10" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="418" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="4" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B418" s="4" t="s">
-        <v>1556</v>
-      </c>
-      <c r="C418" s="4" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D418" s="4" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E418" s="20" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F418" s="5">
-        <v>40854</v>
-      </c>
-      <c r="G418" s="3">
-        <v>4.08</v>
-      </c>
-      <c r="H418" s="9">
+      <c r="A418" s="25" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B418" s="25" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C418" s="25" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D418" s="25" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E418" s="30" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F418" s="26">
+        <v>46001</v>
+      </c>
+      <c r="G418" s="27">
+        <v>3.27</v>
+      </c>
+      <c r="H418" s="28" cm="1">
+        <f t="array" ref="H418">_xlfn.IFS(I418="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B418)),80,96),I418="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B418)),ISNUMBER(SEARCH("chief executive",B418))),95,91),I418="Managing Director",86,I418="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B418)),ISNUMBER(SEARCH("general partner",B418))),88,85),I418="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B418)),ISNUMBER(SEARCH("executive vice",B418))),91,ISNUMBER(SEARCH("svp",B418)),77,TRUE,73),I418="Director",IF(ISNUMBER(SEARCH("principal",B418)),72,71),I418="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B418)),ISNUMBER(SEARCH("physician",B418)),ISNUMBER(SEARCH("doctor",B418)),ISNUMBER(SEARCH("dentist",B418)),ISNUMBER(SEARCH("psychiat",B418)),ISNUMBER(SEARCH("oncolog",B418)),ISNUMBER(SEARCH("neurolog",B418)),ISNUMBER(SEARCH("patholog",B418)),ISNUMBER(SEARCH("medicine",B418)),ISNUMBER(SEARCH("obgyn",B418))),77,OR(ISNUMBER(SEARCH("portfolio manager",B418)),ISNUMBER(SEARCH("wealth advisor",B418))),81,OR(ISNUMBER(SEARCH("lawyer",B418)),ISNUMBER(SEARCH("attorney",B418))),68,ISNUMBER(SEARCH("counsel",B418)),66,ISNUMBER(SEARCH("professor",B418)),63,OR(ISNUMBER(SEARCH("engineer",B418)),ISNUMBER(SEARCH("consultant",B418))),62,ISNUMBER(SEARCH("senior manager",B418)),64,OR(ISNUMBER(SEARCH("realtor",B418)),ISNUMBER(SEARCH("broker",B418)),ISNUMBER(SEARCH("journalist",B418)),ISNUMBER(SEARCH("columnist",B418)),ISNUMBER(SEARCH("trader",B418)),ISNUMBER(SEARCH("actor",B418))),50,TRUE,60)</f>
         <v>60</v>
       </c>
-      <c r="I418" s="29" t="s">
-        <v>1054</v>
-      </c>
-      <c r="J418" s="10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="K418" s="10" t="s">
-        <v>1057</v>
+      <c r="I418" s="29" t="str" cm="1">
+        <f t="array" ref="I418">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
+        <v>Professional</v>
+      </c>
+      <c r="J418" s="29" t="str" cm="1">
+        <f t="array" ref="J418">_xlfn.IFS(H418&gt;=90,"Very High",H418&gt;=80,"High",H418&gt;=56,"Medium",TRUE,"Low")</f>
+        <v>Medium</v>
+      </c>
+      <c r="K418" s="29" t="str" cm="1">
+        <f t="array" ref="K418">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C418)),ISNUMBER(SEARCH("health",C418)),ISNUMBER(SEARCH("medical",C418)),ISNUMBER(SEARCH("clinic",C418)),ISNUMBER(SEARCH("nursing",C418)),ISNUMBER(SEARCH("care cent",C418)),ISNUMBER(SEARCH("physician",B418)),ISNUMBER(SEARCH("doctor",B418)),ISNUMBER(SEARCH("dentist",B418)),ISNUMBER(SEARCH("surgeon",B418)),ISNUMBER(SEARCH("psychiat",B418)),ISNUMBER(SEARCH("medicine",B418))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C418)),ISNUMBER(SEARCH("lawyer",B418)),ISNUMBER(SEARCH("attorney",B418)),ISNUMBER(SEARCH("legal",C418)),ISNUMBER(SEARCH("tetrault",C418)),ISNUMBER(SEARCH("morley",C418)),ISNUMBER(SEARCH("blg",C418)),ISNUMBER(SEARCH("lowy",C418)),ISNUMBER(SEARCH("riley",C418)),ISNUMBER(SEARCH("toomath",C418))),"Law",OR(ISNUMBER(SEARCH("reit",C418)),ISNUMBER(SEARCH("properties",C418)),ISNUMBER(SEARCH("realty",C418)),ISNUMBER(SEARCH("realtor",B418)),ISNUMBER(SEARCH("colliers",C418)),ISNUMBER(SEARCH("re/max",C418)),ISNUMBER(SEARCH("quadreal",C418)),ISNUMBER(SEARCH("vic management",C418))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C418)),ISNUMBER(SEARCH("kpmg",C418)),ISNUMBER(SEARCH("pwc",C418)),ISNUMBER(SEARCH("consulting",C418)),ISNUMBER(SEARCH("consultant",B418)),ISNUMBER(SEARCH("advisory",C418)),ISNUMBER(SEARCH("philanthropic",C418)),ISNUMBER(SEARCH("argyle",C418)),ISNUMBER(SEARCH("quinn",C418))),"Consulting",OR(ISNUMBER(SEARCH("media",C418)),ISNUMBER(SEARCH("news",C418)),ISNUMBER(SEARCH("radio",C418)),ISNUMBER(SEARCH("film",C418)),ISNUMBER(SEARCH("journalist",B418)),ISNUMBER(SEARCH("columnist",B418)),ISNUMBER(SEARCH("globe",C418)),ISNUMBER(SEARCH("marketing",C418)),ISNUMBER(SEARCH("actor",B418))),"Media",OR(ISNUMBER(SEARCH("rbc",C418)),ISNUMBER(SEARCH("cibc",C418)),ISNUMBER(SEARCH("bmo",C418)),ISNUMBER(SEARCH("scotia",C418)),ISNUMBER(SEARCH("bank",C418)),ISNUMBER(SEARCH("capital",C418)),ISNUMBER(SEARCH("wealth",C418)),ISNUMBER(SEARCH("financial",C418)),ISNUMBER(SEARCH("securities",C418)),ISNUMBER(SEARCH("fidelity",C418)),ISNUMBER(SEARCH("guardian",C418)),ISNUMBER(SEARCH("wealthsimple",C418)),ISNUMBER(SEARCH("credit suisse",C418)),ISNUMBER(SEARCH("tmx",C418)),ISNUMBER(SEARCH("investors",C418)),ISNUMBER(SEARCH("trader",B418))),"Finance",OR(ISNUMBER(SEARCH("ventures",C418)),ISNUMBER(SEARCH("private equity",B418)),ISNUMBER(SEARCH("capital partners",C418))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C418)),ISNUMBER(SEARCH("ministry",C418)),ISNUMBER(SEARCH("tribunal",C418)),ISNUMBER(SEARCH("tdsb",C418)),ISNUMBER(SEARCH("public service",C418))),"Government",OR(ISNUMBER(SEARCH("association",C418)),ISNUMBER(SEARCH("institute",C418)),ISNUMBER(SEARCH("foundation",C418))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C418)),ISNUMBER(SEARCH("tech",C418)),ISNUMBER(SEARCH("systems",C418)),ISNUMBER(SEARCH("digital",C418)),ISNUMBER(SEARCH("engineering",C418)),ISNUMBER(SEARCH("solutions",C418))),"Technology",TRUE,"Other")</f>
+        <v>Government</v>
       </c>
     </row>
     <row r="419" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A419" s="25" t="s">
-        <v>1428</v>
+        <v>1362</v>
       </c>
       <c r="B419" s="25" t="s">
-        <v>1429</v>
+        <v>1363</v>
       </c>
       <c r="C419" s="25" t="s">
-        <v>1426</v>
+        <v>1364</v>
       </c>
       <c r="D419" s="25" t="s">
-        <v>1430</v>
-      </c>
-      <c r="E419" s="30" t="s">
-        <v>1279</v>
+        <v>1365</v>
+      </c>
+      <c r="E419" s="30">
+        <v>3480000</v>
       </c>
       <c r="F419" s="26">
-        <v>46001</v>
+        <v>44734</v>
       </c>
       <c r="G419" s="27">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="H419" s="28" cm="1">
         <f t="array" ref="H419">_xlfn.IFS(I419="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B419)),80,96),I419="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B419)),ISNUMBER(SEARCH("chief executive",B419))),95,91),I419="Managing Director",86,I419="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B419)),ISNUMBER(SEARCH("general partner",B419))),88,85),I419="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B419)),ISNUMBER(SEARCH("executive vice",B419))),91,ISNUMBER(SEARCH("svp",B419)),77,TRUE,73),I419="Director",IF(ISNUMBER(SEARCH("principal",B419)),72,71),I419="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B419)),ISNUMBER(SEARCH("physician",B419)),ISNUMBER(SEARCH("doctor",B419)),ISNUMBER(SEARCH("dentist",B419)),ISNUMBER(SEARCH("psychiat",B419)),ISNUMBER(SEARCH("oncolog",B419)),ISNUMBER(SEARCH("neurolog",B419)),ISNUMBER(SEARCH("patholog",B419)),ISNUMBER(SEARCH("medicine",B419)),ISNUMBER(SEARCH("obgyn",B419))),77,OR(ISNUMBER(SEARCH("portfolio manager",B419)),ISNUMBER(SEARCH("wealth advisor",B419))),81,OR(ISNUMBER(SEARCH("lawyer",B419)),ISNUMBER(SEARCH("attorney",B419))),68,ISNUMBER(SEARCH("counsel",B419)),66,ISNUMBER(SEARCH("professor",B419)),63,OR(ISNUMBER(SEARCH("engineer",B419)),ISNUMBER(SEARCH("consultant",B419))),62,ISNUMBER(SEARCH("senior manager",B419)),64,OR(ISNUMBER(SEARCH("realtor",B419)),ISNUMBER(SEARCH("broker",B419)),ISNUMBER(SEARCH("journalist",B419)),ISNUMBER(SEARCH("columnist",B419)),ISNUMBER(SEARCH("trader",B419)),ISNUMBER(SEARCH("actor",B419))),50,TRUE,60)</f>
@@ -20172,30 +20164,30 @@
       </c>
       <c r="K419" s="29" t="str" cm="1">
         <f t="array" ref="K419">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C419)),ISNUMBER(SEARCH("health",C419)),ISNUMBER(SEARCH("medical",C419)),ISNUMBER(SEARCH("clinic",C419)),ISNUMBER(SEARCH("nursing",C419)),ISNUMBER(SEARCH("care cent",C419)),ISNUMBER(SEARCH("physician",B419)),ISNUMBER(SEARCH("doctor",B419)),ISNUMBER(SEARCH("dentist",B419)),ISNUMBER(SEARCH("surgeon",B419)),ISNUMBER(SEARCH("psychiat",B419)),ISNUMBER(SEARCH("medicine",B419))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C419)),ISNUMBER(SEARCH("lawyer",B419)),ISNUMBER(SEARCH("attorney",B419)),ISNUMBER(SEARCH("legal",C419)),ISNUMBER(SEARCH("tetrault",C419)),ISNUMBER(SEARCH("morley",C419)),ISNUMBER(SEARCH("blg",C419)),ISNUMBER(SEARCH("lowy",C419)),ISNUMBER(SEARCH("riley",C419)),ISNUMBER(SEARCH("toomath",C419))),"Law",OR(ISNUMBER(SEARCH("reit",C419)),ISNUMBER(SEARCH("properties",C419)),ISNUMBER(SEARCH("realty",C419)),ISNUMBER(SEARCH("realtor",B419)),ISNUMBER(SEARCH("colliers",C419)),ISNUMBER(SEARCH("re/max",C419)),ISNUMBER(SEARCH("quadreal",C419)),ISNUMBER(SEARCH("vic management",C419))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C419)),ISNUMBER(SEARCH("kpmg",C419)),ISNUMBER(SEARCH("pwc",C419)),ISNUMBER(SEARCH("consulting",C419)),ISNUMBER(SEARCH("consultant",B419)),ISNUMBER(SEARCH("advisory",C419)),ISNUMBER(SEARCH("philanthropic",C419)),ISNUMBER(SEARCH("argyle",C419)),ISNUMBER(SEARCH("quinn",C419))),"Consulting",OR(ISNUMBER(SEARCH("media",C419)),ISNUMBER(SEARCH("news",C419)),ISNUMBER(SEARCH("radio",C419)),ISNUMBER(SEARCH("film",C419)),ISNUMBER(SEARCH("journalist",B419)),ISNUMBER(SEARCH("columnist",B419)),ISNUMBER(SEARCH("globe",C419)),ISNUMBER(SEARCH("marketing",C419)),ISNUMBER(SEARCH("actor",B419))),"Media",OR(ISNUMBER(SEARCH("rbc",C419)),ISNUMBER(SEARCH("cibc",C419)),ISNUMBER(SEARCH("bmo",C419)),ISNUMBER(SEARCH("scotia",C419)),ISNUMBER(SEARCH("bank",C419)),ISNUMBER(SEARCH("capital",C419)),ISNUMBER(SEARCH("wealth",C419)),ISNUMBER(SEARCH("financial",C419)),ISNUMBER(SEARCH("securities",C419)),ISNUMBER(SEARCH("fidelity",C419)),ISNUMBER(SEARCH("guardian",C419)),ISNUMBER(SEARCH("wealthsimple",C419)),ISNUMBER(SEARCH("credit suisse",C419)),ISNUMBER(SEARCH("tmx",C419)),ISNUMBER(SEARCH("investors",C419)),ISNUMBER(SEARCH("trader",B419))),"Finance",OR(ISNUMBER(SEARCH("ventures",C419)),ISNUMBER(SEARCH("private equity",B419)),ISNUMBER(SEARCH("capital partners",C419))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C419)),ISNUMBER(SEARCH("ministry",C419)),ISNUMBER(SEARCH("tribunal",C419)),ISNUMBER(SEARCH("tdsb",C419)),ISNUMBER(SEARCH("public service",C419))),"Government",OR(ISNUMBER(SEARCH("association",C419)),ISNUMBER(SEARCH("institute",C419)),ISNUMBER(SEARCH("foundation",C419))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C419)),ISNUMBER(SEARCH("tech",C419)),ISNUMBER(SEARCH("systems",C419)),ISNUMBER(SEARCH("digital",C419)),ISNUMBER(SEARCH("engineering",C419)),ISNUMBER(SEARCH("solutions",C419))),"Technology",TRUE,"Other")</f>
-        <v>Government</v>
+        <v>Media</v>
       </c>
     </row>
     <row r="420" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A420" s="25" t="s">
-        <v>1366</v>
+        <v>1286</v>
       </c>
       <c r="B420" s="25" t="s">
-        <v>1367</v>
+        <v>684</v>
       </c>
       <c r="C420" s="25" t="s">
-        <v>1368</v>
+        <v>1507</v>
       </c>
       <c r="D420" s="25" t="s">
-        <v>1369</v>
+        <v>1287</v>
       </c>
       <c r="E420" s="30">
-        <v>3480000</v>
+        <v>2772000</v>
       </c>
       <c r="F420" s="26">
-        <v>44734</v>
+        <v>45125</v>
       </c>
       <c r="G420" s="27">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="H420" s="28" cm="1">
         <f t="array" ref="H420">_xlfn.IFS(I420="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B420)),80,96),I420="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B420)),ISNUMBER(SEARCH("chief executive",B420))),95,91),I420="Managing Director",86,I420="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B420)),ISNUMBER(SEARCH("general partner",B420))),88,85),I420="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B420)),ISNUMBER(SEARCH("executive vice",B420))),91,ISNUMBER(SEARCH("svp",B420)),77,TRUE,73),I420="Director",IF(ISNUMBER(SEARCH("principal",B420)),72,71),I420="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B420)),ISNUMBER(SEARCH("physician",B420)),ISNUMBER(SEARCH("doctor",B420)),ISNUMBER(SEARCH("dentist",B420)),ISNUMBER(SEARCH("psychiat",B420)),ISNUMBER(SEARCH("oncolog",B420)),ISNUMBER(SEARCH("neurolog",B420)),ISNUMBER(SEARCH("patholog",B420)),ISNUMBER(SEARCH("medicine",B420)),ISNUMBER(SEARCH("obgyn",B420))),77,OR(ISNUMBER(SEARCH("portfolio manager",B420)),ISNUMBER(SEARCH("wealth advisor",B420))),81,OR(ISNUMBER(SEARCH("lawyer",B420)),ISNUMBER(SEARCH("attorney",B420))),68,ISNUMBER(SEARCH("counsel",B420)),66,ISNUMBER(SEARCH("professor",B420)),63,OR(ISNUMBER(SEARCH("engineer",B420)),ISNUMBER(SEARCH("consultant",B420))),62,ISNUMBER(SEARCH("senior manager",B420)),64,OR(ISNUMBER(SEARCH("realtor",B420)),ISNUMBER(SEARCH("broker",B420)),ISNUMBER(SEARCH("journalist",B420)),ISNUMBER(SEARCH("columnist",B420)),ISNUMBER(SEARCH("trader",B420)),ISNUMBER(SEARCH("actor",B420))),50,TRUE,60)</f>
@@ -20211,69 +20203,65 @@
       </c>
       <c r="K420" s="29" t="str" cm="1">
         <f t="array" ref="K420">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C420)),ISNUMBER(SEARCH("health",C420)),ISNUMBER(SEARCH("medical",C420)),ISNUMBER(SEARCH("clinic",C420)),ISNUMBER(SEARCH("nursing",C420)),ISNUMBER(SEARCH("care cent",C420)),ISNUMBER(SEARCH("physician",B420)),ISNUMBER(SEARCH("doctor",B420)),ISNUMBER(SEARCH("dentist",B420)),ISNUMBER(SEARCH("surgeon",B420)),ISNUMBER(SEARCH("psychiat",B420)),ISNUMBER(SEARCH("medicine",B420))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C420)),ISNUMBER(SEARCH("lawyer",B420)),ISNUMBER(SEARCH("attorney",B420)),ISNUMBER(SEARCH("legal",C420)),ISNUMBER(SEARCH("tetrault",C420)),ISNUMBER(SEARCH("morley",C420)),ISNUMBER(SEARCH("blg",C420)),ISNUMBER(SEARCH("lowy",C420)),ISNUMBER(SEARCH("riley",C420)),ISNUMBER(SEARCH("toomath",C420))),"Law",OR(ISNUMBER(SEARCH("reit",C420)),ISNUMBER(SEARCH("properties",C420)),ISNUMBER(SEARCH("realty",C420)),ISNUMBER(SEARCH("realtor",B420)),ISNUMBER(SEARCH("colliers",C420)),ISNUMBER(SEARCH("re/max",C420)),ISNUMBER(SEARCH("quadreal",C420)),ISNUMBER(SEARCH("vic management",C420))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C420)),ISNUMBER(SEARCH("kpmg",C420)),ISNUMBER(SEARCH("pwc",C420)),ISNUMBER(SEARCH("consulting",C420)),ISNUMBER(SEARCH("consultant",B420)),ISNUMBER(SEARCH("advisory",C420)),ISNUMBER(SEARCH("philanthropic",C420)),ISNUMBER(SEARCH("argyle",C420)),ISNUMBER(SEARCH("quinn",C420))),"Consulting",OR(ISNUMBER(SEARCH("media",C420)),ISNUMBER(SEARCH("news",C420)),ISNUMBER(SEARCH("radio",C420)),ISNUMBER(SEARCH("film",C420)),ISNUMBER(SEARCH("journalist",B420)),ISNUMBER(SEARCH("columnist",B420)),ISNUMBER(SEARCH("globe",C420)),ISNUMBER(SEARCH("marketing",C420)),ISNUMBER(SEARCH("actor",B420))),"Media",OR(ISNUMBER(SEARCH("rbc",C420)),ISNUMBER(SEARCH("cibc",C420)),ISNUMBER(SEARCH("bmo",C420)),ISNUMBER(SEARCH("scotia",C420)),ISNUMBER(SEARCH("bank",C420)),ISNUMBER(SEARCH("capital",C420)),ISNUMBER(SEARCH("wealth",C420)),ISNUMBER(SEARCH("financial",C420)),ISNUMBER(SEARCH("securities",C420)),ISNUMBER(SEARCH("fidelity",C420)),ISNUMBER(SEARCH("guardian",C420)),ISNUMBER(SEARCH("wealthsimple",C420)),ISNUMBER(SEARCH("credit suisse",C420)),ISNUMBER(SEARCH("tmx",C420)),ISNUMBER(SEARCH("investors",C420)),ISNUMBER(SEARCH("trader",B420))),"Finance",OR(ISNUMBER(SEARCH("ventures",C420)),ISNUMBER(SEARCH("private equity",B420)),ISNUMBER(SEARCH("capital partners",C420))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C420)),ISNUMBER(SEARCH("ministry",C420)),ISNUMBER(SEARCH("tribunal",C420)),ISNUMBER(SEARCH("tdsb",C420)),ISNUMBER(SEARCH("public service",C420))),"Government",OR(ISNUMBER(SEARCH("association",C420)),ISNUMBER(SEARCH("institute",C420)),ISNUMBER(SEARCH("foundation",C420))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C420)),ISNUMBER(SEARCH("tech",C420)),ISNUMBER(SEARCH("systems",C420)),ISNUMBER(SEARCH("digital",C420)),ISNUMBER(SEARCH("engineering",C420)),ISNUMBER(SEARCH("solutions",C420))),"Technology",TRUE,"Other")</f>
-        <v>Media</v>
+        <v>Finance</v>
       </c>
     </row>
     <row r="421" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="25" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B421" s="25" t="s">
-        <v>684</v>
-      </c>
-      <c r="C421" s="25" t="s">
-        <v>1511</v>
-      </c>
-      <c r="D421" s="25" t="s">
-        <v>1291</v>
-      </c>
-      <c r="E421" s="30">
-        <v>2772000</v>
-      </c>
-      <c r="F421" s="26">
-        <v>45125</v>
-      </c>
-      <c r="G421" s="27">
-        <v>2.94</v>
-      </c>
-      <c r="H421" s="28" cm="1">
-        <f t="array" ref="H421">_xlfn.IFS(I421="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B421)),80,96),I421="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B421)),ISNUMBER(SEARCH("chief executive",B421))),95,91),I421="Managing Director",86,I421="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B421)),ISNUMBER(SEARCH("general partner",B421))),88,85),I421="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B421)),ISNUMBER(SEARCH("executive vice",B421))),91,ISNUMBER(SEARCH("svp",B421)),77,TRUE,73),I421="Director",IF(ISNUMBER(SEARCH("principal",B421)),72,71),I421="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B421)),ISNUMBER(SEARCH("physician",B421)),ISNUMBER(SEARCH("doctor",B421)),ISNUMBER(SEARCH("dentist",B421)),ISNUMBER(SEARCH("psychiat",B421)),ISNUMBER(SEARCH("oncolog",B421)),ISNUMBER(SEARCH("neurolog",B421)),ISNUMBER(SEARCH("patholog",B421)),ISNUMBER(SEARCH("medicine",B421)),ISNUMBER(SEARCH("obgyn",B421))),77,OR(ISNUMBER(SEARCH("portfolio manager",B421)),ISNUMBER(SEARCH("wealth advisor",B421))),81,OR(ISNUMBER(SEARCH("lawyer",B421)),ISNUMBER(SEARCH("attorney",B421))),68,ISNUMBER(SEARCH("counsel",B421)),66,ISNUMBER(SEARCH("professor",B421)),63,OR(ISNUMBER(SEARCH("engineer",B421)),ISNUMBER(SEARCH("consultant",B421))),62,ISNUMBER(SEARCH("senior manager",B421)),64,OR(ISNUMBER(SEARCH("realtor",B421)),ISNUMBER(SEARCH("broker",B421)),ISNUMBER(SEARCH("journalist",B421)),ISNUMBER(SEARCH("columnist",B421)),ISNUMBER(SEARCH("trader",B421)),ISNUMBER(SEARCH("actor",B421))),50,TRUE,60)</f>
+      <c r="A421" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="E421" s="18">
+        <v>1955000</v>
+      </c>
+      <c r="F421" s="5">
+        <v>38537</v>
+      </c>
+      <c r="G421" s="6">
+        <v>4.07</v>
+      </c>
+      <c r="H421" s="9">
         <v>60</v>
       </c>
-      <c r="I421" s="29" t="str" cm="1">
-        <f t="array" ref="I421">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B421,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
-        <v>Professional</v>
-      </c>
-      <c r="J421" s="29" t="str" cm="1">
-        <f t="array" ref="J421">_xlfn.IFS(H421&gt;=90,"Very High",H421&gt;=80,"High",H421&gt;=56,"Medium",TRUE,"Low")</f>
-        <v>Medium</v>
-      </c>
-      <c r="K421" s="29" t="str" cm="1">
-        <f t="array" ref="K421">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C421)),ISNUMBER(SEARCH("health",C421)),ISNUMBER(SEARCH("medical",C421)),ISNUMBER(SEARCH("clinic",C421)),ISNUMBER(SEARCH("nursing",C421)),ISNUMBER(SEARCH("care cent",C421)),ISNUMBER(SEARCH("physician",B421)),ISNUMBER(SEARCH("doctor",B421)),ISNUMBER(SEARCH("dentist",B421)),ISNUMBER(SEARCH("surgeon",B421)),ISNUMBER(SEARCH("psychiat",B421)),ISNUMBER(SEARCH("medicine",B421))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C421)),ISNUMBER(SEARCH("lawyer",B421)),ISNUMBER(SEARCH("attorney",B421)),ISNUMBER(SEARCH("legal",C421)),ISNUMBER(SEARCH("tetrault",C421)),ISNUMBER(SEARCH("morley",C421)),ISNUMBER(SEARCH("blg",C421)),ISNUMBER(SEARCH("lowy",C421)),ISNUMBER(SEARCH("riley",C421)),ISNUMBER(SEARCH("toomath",C421))),"Law",OR(ISNUMBER(SEARCH("reit",C421)),ISNUMBER(SEARCH("properties",C421)),ISNUMBER(SEARCH("realty",C421)),ISNUMBER(SEARCH("realtor",B421)),ISNUMBER(SEARCH("colliers",C421)),ISNUMBER(SEARCH("re/max",C421)),ISNUMBER(SEARCH("quadreal",C421)),ISNUMBER(SEARCH("vic management",C421))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C421)),ISNUMBER(SEARCH("kpmg",C421)),ISNUMBER(SEARCH("pwc",C421)),ISNUMBER(SEARCH("consulting",C421)),ISNUMBER(SEARCH("consultant",B421)),ISNUMBER(SEARCH("advisory",C421)),ISNUMBER(SEARCH("philanthropic",C421)),ISNUMBER(SEARCH("argyle",C421)),ISNUMBER(SEARCH("quinn",C421))),"Consulting",OR(ISNUMBER(SEARCH("media",C421)),ISNUMBER(SEARCH("news",C421)),ISNUMBER(SEARCH("radio",C421)),ISNUMBER(SEARCH("film",C421)),ISNUMBER(SEARCH("journalist",B421)),ISNUMBER(SEARCH("columnist",B421)),ISNUMBER(SEARCH("globe",C421)),ISNUMBER(SEARCH("marketing",C421)),ISNUMBER(SEARCH("actor",B421))),"Media",OR(ISNUMBER(SEARCH("rbc",C421)),ISNUMBER(SEARCH("cibc",C421)),ISNUMBER(SEARCH("bmo",C421)),ISNUMBER(SEARCH("scotia",C421)),ISNUMBER(SEARCH("bank",C421)),ISNUMBER(SEARCH("capital",C421)),ISNUMBER(SEARCH("wealth",C421)),ISNUMBER(SEARCH("financial",C421)),ISNUMBER(SEARCH("securities",C421)),ISNUMBER(SEARCH("fidelity",C421)),ISNUMBER(SEARCH("guardian",C421)),ISNUMBER(SEARCH("wealthsimple",C421)),ISNUMBER(SEARCH("credit suisse",C421)),ISNUMBER(SEARCH("tmx",C421)),ISNUMBER(SEARCH("investors",C421)),ISNUMBER(SEARCH("trader",B421))),"Finance",OR(ISNUMBER(SEARCH("ventures",C421)),ISNUMBER(SEARCH("private equity",B421)),ISNUMBER(SEARCH("capital partners",C421))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C421)),ISNUMBER(SEARCH("ministry",C421)),ISNUMBER(SEARCH("tribunal",C421)),ISNUMBER(SEARCH("tdsb",C421)),ISNUMBER(SEARCH("public service",C421))),"Government",OR(ISNUMBER(SEARCH("association",C421)),ISNUMBER(SEARCH("institute",C421)),ISNUMBER(SEARCH("foundation",C421))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C421)),ISNUMBER(SEARCH("tech",C421)),ISNUMBER(SEARCH("systems",C421)),ISNUMBER(SEARCH("digital",C421)),ISNUMBER(SEARCH("engineering",C421)),ISNUMBER(SEARCH("solutions",C421))),"Technology",TRUE,"Other")</f>
-        <v>Finance</v>
+      <c r="I421" s="29" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J421" s="10" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K421" s="10" t="s">
+        <v>1063</v>
       </c>
     </row>
     <row r="422" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
-        <v>762</v>
+        <v>867</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>763</v>
+        <v>868</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>764</v>
+        <v>294</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>765</v>
+        <v>869</v>
       </c>
       <c r="E422" s="18">
-        <v>1955000</v>
+        <v>1530000</v>
       </c>
       <c r="F422" s="5">
-        <v>38537</v>
+        <v>41502</v>
       </c>
       <c r="G422" s="6">
-        <v>4.07</v>
+        <v>3.92</v>
       </c>
       <c r="H422" s="9">
         <v>60</v>
@@ -20285,65 +20273,69 @@
         <v>1055</v>
       </c>
       <c r="K422" s="10" t="s">
-        <v>1063</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="423" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="4" t="s">
-        <v>867</v>
-      </c>
-      <c r="B423" s="4" t="s">
-        <v>868</v>
-      </c>
-      <c r="C423" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="D423" s="4" t="s">
-        <v>869</v>
-      </c>
-      <c r="E423" s="18">
-        <v>1530000</v>
-      </c>
-      <c r="F423" s="5">
-        <v>41502</v>
-      </c>
-      <c r="G423" s="6">
-        <v>3.92</v>
-      </c>
-      <c r="H423" s="9">
+      <c r="A423" s="25" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B423" s="25" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C423" s="25" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D423" s="25" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E423" s="30">
+        <v>1350000</v>
+      </c>
+      <c r="F423" s="26">
+        <v>45866</v>
+      </c>
+      <c r="G423" s="27">
+        <v>3.24</v>
+      </c>
+      <c r="H423" s="28" cm="1">
+        <f t="array" ref="H423">_xlfn.IFS(I423="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B423)),80,96),I423="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B423)),ISNUMBER(SEARCH("chief executive",B423))),95,91),I423="Managing Director",86,I423="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B423)),ISNUMBER(SEARCH("general partner",B423))),88,85),I423="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B423)),ISNUMBER(SEARCH("executive vice",B423))),91,ISNUMBER(SEARCH("svp",B423)),77,TRUE,73),I423="Director",IF(ISNUMBER(SEARCH("principal",B423)),72,71),I423="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B423)),ISNUMBER(SEARCH("physician",B423)),ISNUMBER(SEARCH("doctor",B423)),ISNUMBER(SEARCH("dentist",B423)),ISNUMBER(SEARCH("psychiat",B423)),ISNUMBER(SEARCH("oncolog",B423)),ISNUMBER(SEARCH("neurolog",B423)),ISNUMBER(SEARCH("patholog",B423)),ISNUMBER(SEARCH("medicine",B423)),ISNUMBER(SEARCH("obgyn",B423))),77,OR(ISNUMBER(SEARCH("portfolio manager",B423)),ISNUMBER(SEARCH("wealth advisor",B423))),81,OR(ISNUMBER(SEARCH("lawyer",B423)),ISNUMBER(SEARCH("attorney",B423))),68,ISNUMBER(SEARCH("counsel",B423)),66,ISNUMBER(SEARCH("professor",B423)),63,OR(ISNUMBER(SEARCH("engineer",B423)),ISNUMBER(SEARCH("consultant",B423))),62,ISNUMBER(SEARCH("senior manager",B423)),64,OR(ISNUMBER(SEARCH("realtor",B423)),ISNUMBER(SEARCH("broker",B423)),ISNUMBER(SEARCH("journalist",B423)),ISNUMBER(SEARCH("columnist",B423)),ISNUMBER(SEARCH("trader",B423)),ISNUMBER(SEARCH("actor",B423))),50,TRUE,60)</f>
         <v>60</v>
       </c>
-      <c r="I423" s="29" t="s">
-        <v>1054</v>
-      </c>
-      <c r="J423" s="10" t="s">
-        <v>1055</v>
-      </c>
-      <c r="K423" s="10" t="s">
-        <v>1053</v>
+      <c r="I423" s="29" t="str" cm="1">
+        <f t="array" ref="I423">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B423,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
+        <v>Professional</v>
+      </c>
+      <c r="J423" s="29" t="str" cm="1">
+        <f t="array" ref="J423">_xlfn.IFS(H423&gt;=90,"Very High",H423&gt;=80,"High",H423&gt;=56,"Medium",TRUE,"Low")</f>
+        <v>Medium</v>
+      </c>
+      <c r="K423" s="29" t="str" cm="1">
+        <f t="array" ref="K423">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C423)),ISNUMBER(SEARCH("health",C423)),ISNUMBER(SEARCH("medical",C423)),ISNUMBER(SEARCH("clinic",C423)),ISNUMBER(SEARCH("nursing",C423)),ISNUMBER(SEARCH("care cent",C423)),ISNUMBER(SEARCH("physician",B423)),ISNUMBER(SEARCH("doctor",B423)),ISNUMBER(SEARCH("dentist",B423)),ISNUMBER(SEARCH("surgeon",B423)),ISNUMBER(SEARCH("psychiat",B423)),ISNUMBER(SEARCH("medicine",B423))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C423)),ISNUMBER(SEARCH("lawyer",B423)),ISNUMBER(SEARCH("attorney",B423)),ISNUMBER(SEARCH("legal",C423)),ISNUMBER(SEARCH("tetrault",C423)),ISNUMBER(SEARCH("morley",C423)),ISNUMBER(SEARCH("blg",C423)),ISNUMBER(SEARCH("lowy",C423)),ISNUMBER(SEARCH("riley",C423)),ISNUMBER(SEARCH("toomath",C423))),"Law",OR(ISNUMBER(SEARCH("reit",C423)),ISNUMBER(SEARCH("properties",C423)),ISNUMBER(SEARCH("realty",C423)),ISNUMBER(SEARCH("realtor",B423)),ISNUMBER(SEARCH("colliers",C423)),ISNUMBER(SEARCH("re/max",C423)),ISNUMBER(SEARCH("quadreal",C423)),ISNUMBER(SEARCH("vic management",C423))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C423)),ISNUMBER(SEARCH("kpmg",C423)),ISNUMBER(SEARCH("pwc",C423)),ISNUMBER(SEARCH("consulting",C423)),ISNUMBER(SEARCH("consultant",B423)),ISNUMBER(SEARCH("advisory",C423)),ISNUMBER(SEARCH("philanthropic",C423)),ISNUMBER(SEARCH("argyle",C423)),ISNUMBER(SEARCH("quinn",C423))),"Consulting",OR(ISNUMBER(SEARCH("media",C423)),ISNUMBER(SEARCH("news",C423)),ISNUMBER(SEARCH("radio",C423)),ISNUMBER(SEARCH("film",C423)),ISNUMBER(SEARCH("journalist",B423)),ISNUMBER(SEARCH("columnist",B423)),ISNUMBER(SEARCH("globe",C423)),ISNUMBER(SEARCH("marketing",C423)),ISNUMBER(SEARCH("actor",B423))),"Media",OR(ISNUMBER(SEARCH("rbc",C423)),ISNUMBER(SEARCH("cibc",C423)),ISNUMBER(SEARCH("bmo",C423)),ISNUMBER(SEARCH("scotia",C423)),ISNUMBER(SEARCH("bank",C423)),ISNUMBER(SEARCH("capital",C423)),ISNUMBER(SEARCH("wealth",C423)),ISNUMBER(SEARCH("financial",C423)),ISNUMBER(SEARCH("securities",C423)),ISNUMBER(SEARCH("fidelity",C423)),ISNUMBER(SEARCH("guardian",C423)),ISNUMBER(SEARCH("wealthsimple",C423)),ISNUMBER(SEARCH("credit suisse",C423)),ISNUMBER(SEARCH("tmx",C423)),ISNUMBER(SEARCH("investors",C423)),ISNUMBER(SEARCH("trader",B423))),"Finance",OR(ISNUMBER(SEARCH("ventures",C423)),ISNUMBER(SEARCH("private equity",B423)),ISNUMBER(SEARCH("capital partners",C423))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C423)),ISNUMBER(SEARCH("ministry",C423)),ISNUMBER(SEARCH("tribunal",C423)),ISNUMBER(SEARCH("tdsb",C423)),ISNUMBER(SEARCH("public service",C423))),"Government",OR(ISNUMBER(SEARCH("association",C423)),ISNUMBER(SEARCH("institute",C423)),ISNUMBER(SEARCH("foundation",C423))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C423)),ISNUMBER(SEARCH("tech",C423)),ISNUMBER(SEARCH("systems",C423)),ISNUMBER(SEARCH("digital",C423)),ISNUMBER(SEARCH("engineering",C423)),ISNUMBER(SEARCH("solutions",C423))),"Technology",TRUE,"Other")</f>
+        <v>Other</v>
       </c>
     </row>
     <row r="424" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A424" s="25" t="s">
-        <v>1358</v>
+        <v>1351</v>
       </c>
       <c r="B424" s="25" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C424" s="25" t="s">
         <v>1466</v>
       </c>
-      <c r="C424" s="25" t="s">
-        <v>1467</v>
-      </c>
       <c r="D424" s="25" t="s">
-        <v>1314</v>
+        <v>1330</v>
       </c>
       <c r="E424" s="30">
-        <v>1350000</v>
+        <v>1165000</v>
       </c>
       <c r="F424" s="26">
-        <v>45866</v>
+        <v>39478</v>
       </c>
       <c r="G424" s="27">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="H424" s="28" cm="1">
         <f t="array" ref="H424">_xlfn.IFS(I424="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B424)),80,96),I424="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B424)),ISNUMBER(SEARCH("chief executive",B424))),95,91),I424="Managing Director",86,I424="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B424)),ISNUMBER(SEARCH("general partner",B424))),88,85),I424="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B424)),ISNUMBER(SEARCH("executive vice",B424))),91,ISNUMBER(SEARCH("svp",B424)),77,TRUE,73),I424="Director",IF(ISNUMBER(SEARCH("principal",B424)),72,71),I424="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B424)),ISNUMBER(SEARCH("physician",B424)),ISNUMBER(SEARCH("doctor",B424)),ISNUMBER(SEARCH("dentist",B424)),ISNUMBER(SEARCH("psychiat",B424)),ISNUMBER(SEARCH("oncolog",B424)),ISNUMBER(SEARCH("neurolog",B424)),ISNUMBER(SEARCH("patholog",B424)),ISNUMBER(SEARCH("medicine",B424)),ISNUMBER(SEARCH("obgyn",B424))),77,OR(ISNUMBER(SEARCH("portfolio manager",B424)),ISNUMBER(SEARCH("wealth advisor",B424))),81,OR(ISNUMBER(SEARCH("lawyer",B424)),ISNUMBER(SEARCH("attorney",B424))),68,ISNUMBER(SEARCH("counsel",B424)),66,ISNUMBER(SEARCH("professor",B424)),63,OR(ISNUMBER(SEARCH("engineer",B424)),ISNUMBER(SEARCH("consultant",B424))),62,ISNUMBER(SEARCH("senior manager",B424)),64,OR(ISNUMBER(SEARCH("realtor",B424)),ISNUMBER(SEARCH("broker",B424)),ISNUMBER(SEARCH("journalist",B424)),ISNUMBER(SEARCH("columnist",B424)),ISNUMBER(SEARCH("trader",B424)),ISNUMBER(SEARCH("actor",B424))),50,TRUE,60)</f>
@@ -20364,16 +20356,16 @@
     </row>
     <row r="425" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A425" s="25" t="s">
-        <v>1355</v>
+        <v>1329</v>
       </c>
       <c r="B425" s="25" t="s">
-        <v>1469</v>
+        <v>1029</v>
       </c>
       <c r="C425" s="25" t="s">
-        <v>1470</v>
+        <v>294</v>
       </c>
       <c r="D425" s="25" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="E425" s="30">
         <v>1165000</v>
@@ -20398,72 +20390,68 @@
       </c>
       <c r="K425" s="29" t="str" cm="1">
         <f t="array" ref="K425">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C425)),ISNUMBER(SEARCH("health",C425)),ISNUMBER(SEARCH("medical",C425)),ISNUMBER(SEARCH("clinic",C425)),ISNUMBER(SEARCH("nursing",C425)),ISNUMBER(SEARCH("care cent",C425)),ISNUMBER(SEARCH("physician",B425)),ISNUMBER(SEARCH("doctor",B425)),ISNUMBER(SEARCH("dentist",B425)),ISNUMBER(SEARCH("surgeon",B425)),ISNUMBER(SEARCH("psychiat",B425)),ISNUMBER(SEARCH("medicine",B425))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C425)),ISNUMBER(SEARCH("lawyer",B425)),ISNUMBER(SEARCH("attorney",B425)),ISNUMBER(SEARCH("legal",C425)),ISNUMBER(SEARCH("tetrault",C425)),ISNUMBER(SEARCH("morley",C425)),ISNUMBER(SEARCH("blg",C425)),ISNUMBER(SEARCH("lowy",C425)),ISNUMBER(SEARCH("riley",C425)),ISNUMBER(SEARCH("toomath",C425))),"Law",OR(ISNUMBER(SEARCH("reit",C425)),ISNUMBER(SEARCH("properties",C425)),ISNUMBER(SEARCH("realty",C425)),ISNUMBER(SEARCH("realtor",B425)),ISNUMBER(SEARCH("colliers",C425)),ISNUMBER(SEARCH("re/max",C425)),ISNUMBER(SEARCH("quadreal",C425)),ISNUMBER(SEARCH("vic management",C425))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C425)),ISNUMBER(SEARCH("kpmg",C425)),ISNUMBER(SEARCH("pwc",C425)),ISNUMBER(SEARCH("consulting",C425)),ISNUMBER(SEARCH("consultant",B425)),ISNUMBER(SEARCH("advisory",C425)),ISNUMBER(SEARCH("philanthropic",C425)),ISNUMBER(SEARCH("argyle",C425)),ISNUMBER(SEARCH("quinn",C425))),"Consulting",OR(ISNUMBER(SEARCH("media",C425)),ISNUMBER(SEARCH("news",C425)),ISNUMBER(SEARCH("radio",C425)),ISNUMBER(SEARCH("film",C425)),ISNUMBER(SEARCH("journalist",B425)),ISNUMBER(SEARCH("columnist",B425)),ISNUMBER(SEARCH("globe",C425)),ISNUMBER(SEARCH("marketing",C425)),ISNUMBER(SEARCH("actor",B425))),"Media",OR(ISNUMBER(SEARCH("rbc",C425)),ISNUMBER(SEARCH("cibc",C425)),ISNUMBER(SEARCH("bmo",C425)),ISNUMBER(SEARCH("scotia",C425)),ISNUMBER(SEARCH("bank",C425)),ISNUMBER(SEARCH("capital",C425)),ISNUMBER(SEARCH("wealth",C425)),ISNUMBER(SEARCH("financial",C425)),ISNUMBER(SEARCH("securities",C425)),ISNUMBER(SEARCH("fidelity",C425)),ISNUMBER(SEARCH("guardian",C425)),ISNUMBER(SEARCH("wealthsimple",C425)),ISNUMBER(SEARCH("credit suisse",C425)),ISNUMBER(SEARCH("tmx",C425)),ISNUMBER(SEARCH("investors",C425)),ISNUMBER(SEARCH("trader",B425))),"Finance",OR(ISNUMBER(SEARCH("ventures",C425)),ISNUMBER(SEARCH("private equity",B425)),ISNUMBER(SEARCH("capital partners",C425))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C425)),ISNUMBER(SEARCH("ministry",C425)),ISNUMBER(SEARCH("tribunal",C425)),ISNUMBER(SEARCH("tdsb",C425)),ISNUMBER(SEARCH("public service",C425))),"Government",OR(ISNUMBER(SEARCH("association",C425)),ISNUMBER(SEARCH("institute",C425)),ISNUMBER(SEARCH("foundation",C425))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C425)),ISNUMBER(SEARCH("tech",C425)),ISNUMBER(SEARCH("systems",C425)),ISNUMBER(SEARCH("digital",C425)),ISNUMBER(SEARCH("engineering",C425)),ISNUMBER(SEARCH("solutions",C425))),"Technology",TRUE,"Other")</f>
-        <v>Other</v>
+        <v>Finance</v>
       </c>
     </row>
     <row r="426" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="25" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B426" s="25" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C426" s="25" t="s">
-        <v>294</v>
-      </c>
-      <c r="D426" s="25" t="s">
-        <v>1334</v>
-      </c>
-      <c r="E426" s="30">
-        <v>1165000</v>
-      </c>
-      <c r="F426" s="26">
-        <v>39478</v>
-      </c>
-      <c r="G426" s="27">
-        <v>3.05</v>
-      </c>
-      <c r="H426" s="28" cm="1">
-        <f t="array" ref="H426">_xlfn.IFS(I426="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B426)),80,96),I426="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B426)),ISNUMBER(SEARCH("chief executive",B426))),95,91),I426="Managing Director",86,I426="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B426)),ISNUMBER(SEARCH("general partner",B426))),88,85),I426="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B426)),ISNUMBER(SEARCH("executive vice",B426))),91,ISNUMBER(SEARCH("svp",B426)),77,TRUE,73),I426="Director",IF(ISNUMBER(SEARCH("principal",B426)),72,71),I426="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B426)),ISNUMBER(SEARCH("physician",B426)),ISNUMBER(SEARCH("doctor",B426)),ISNUMBER(SEARCH("dentist",B426)),ISNUMBER(SEARCH("psychiat",B426)),ISNUMBER(SEARCH("oncolog",B426)),ISNUMBER(SEARCH("neurolog",B426)),ISNUMBER(SEARCH("patholog",B426)),ISNUMBER(SEARCH("medicine",B426)),ISNUMBER(SEARCH("obgyn",B426))),77,OR(ISNUMBER(SEARCH("portfolio manager",B426)),ISNUMBER(SEARCH("wealth advisor",B426))),81,OR(ISNUMBER(SEARCH("lawyer",B426)),ISNUMBER(SEARCH("attorney",B426))),68,ISNUMBER(SEARCH("counsel",B426)),66,ISNUMBER(SEARCH("professor",B426)),63,OR(ISNUMBER(SEARCH("engineer",B426)),ISNUMBER(SEARCH("consultant",B426))),62,ISNUMBER(SEARCH("senior manager",B426)),64,OR(ISNUMBER(SEARCH("realtor",B426)),ISNUMBER(SEARCH("broker",B426)),ISNUMBER(SEARCH("journalist",B426)),ISNUMBER(SEARCH("columnist",B426)),ISNUMBER(SEARCH("trader",B426)),ISNUMBER(SEARCH("actor",B426))),50,TRUE,60)</f>
-        <v>60</v>
-      </c>
-      <c r="I426" s="29" t="str" cm="1">
-        <f t="array" ref="I426">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B426,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
-        <v>Professional</v>
-      </c>
-      <c r="J426" s="29" t="str" cm="1">
-        <f t="array" ref="J426">_xlfn.IFS(H426&gt;=90,"Very High",H426&gt;=80,"High",H426&gt;=56,"Medium",TRUE,"Low")</f>
-        <v>Medium</v>
-      </c>
-      <c r="K426" s="29" t="str" cm="1">
-        <f t="array" ref="K426">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C426)),ISNUMBER(SEARCH("health",C426)),ISNUMBER(SEARCH("medical",C426)),ISNUMBER(SEARCH("clinic",C426)),ISNUMBER(SEARCH("nursing",C426)),ISNUMBER(SEARCH("care cent",C426)),ISNUMBER(SEARCH("physician",B426)),ISNUMBER(SEARCH("doctor",B426)),ISNUMBER(SEARCH("dentist",B426)),ISNUMBER(SEARCH("surgeon",B426)),ISNUMBER(SEARCH("psychiat",B426)),ISNUMBER(SEARCH("medicine",B426))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C426)),ISNUMBER(SEARCH("lawyer",B426)),ISNUMBER(SEARCH("attorney",B426)),ISNUMBER(SEARCH("legal",C426)),ISNUMBER(SEARCH("tetrault",C426)),ISNUMBER(SEARCH("morley",C426)),ISNUMBER(SEARCH("blg",C426)),ISNUMBER(SEARCH("lowy",C426)),ISNUMBER(SEARCH("riley",C426)),ISNUMBER(SEARCH("toomath",C426))),"Law",OR(ISNUMBER(SEARCH("reit",C426)),ISNUMBER(SEARCH("properties",C426)),ISNUMBER(SEARCH("realty",C426)),ISNUMBER(SEARCH("realtor",B426)),ISNUMBER(SEARCH("colliers",C426)),ISNUMBER(SEARCH("re/max",C426)),ISNUMBER(SEARCH("quadreal",C426)),ISNUMBER(SEARCH("vic management",C426))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C426)),ISNUMBER(SEARCH("kpmg",C426)),ISNUMBER(SEARCH("pwc",C426)),ISNUMBER(SEARCH("consulting",C426)),ISNUMBER(SEARCH("consultant",B426)),ISNUMBER(SEARCH("advisory",C426)),ISNUMBER(SEARCH("philanthropic",C426)),ISNUMBER(SEARCH("argyle",C426)),ISNUMBER(SEARCH("quinn",C426))),"Consulting",OR(ISNUMBER(SEARCH("media",C426)),ISNUMBER(SEARCH("news",C426)),ISNUMBER(SEARCH("radio",C426)),ISNUMBER(SEARCH("film",C426)),ISNUMBER(SEARCH("journalist",B426)),ISNUMBER(SEARCH("columnist",B426)),ISNUMBER(SEARCH("globe",C426)),ISNUMBER(SEARCH("marketing",C426)),ISNUMBER(SEARCH("actor",B426))),"Media",OR(ISNUMBER(SEARCH("rbc",C426)),ISNUMBER(SEARCH("cibc",C426)),ISNUMBER(SEARCH("bmo",C426)),ISNUMBER(SEARCH("scotia",C426)),ISNUMBER(SEARCH("bank",C426)),ISNUMBER(SEARCH("capital",C426)),ISNUMBER(SEARCH("wealth",C426)),ISNUMBER(SEARCH("financial",C426)),ISNUMBER(SEARCH("securities",C426)),ISNUMBER(SEARCH("fidelity",C426)),ISNUMBER(SEARCH("guardian",C426)),ISNUMBER(SEARCH("wealthsimple",C426)),ISNUMBER(SEARCH("credit suisse",C426)),ISNUMBER(SEARCH("tmx",C426)),ISNUMBER(SEARCH("investors",C426)),ISNUMBER(SEARCH("trader",B426))),"Finance",OR(ISNUMBER(SEARCH("ventures",C426)),ISNUMBER(SEARCH("private equity",B426)),ISNUMBER(SEARCH("capital partners",C426))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C426)),ISNUMBER(SEARCH("ministry",C426)),ISNUMBER(SEARCH("tribunal",C426)),ISNUMBER(SEARCH("tdsb",C426)),ISNUMBER(SEARCH("public service",C426))),"Government",OR(ISNUMBER(SEARCH("association",C426)),ISNUMBER(SEARCH("institute",C426)),ISNUMBER(SEARCH("foundation",C426))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C426)),ISNUMBER(SEARCH("tech",C426)),ISNUMBER(SEARCH("systems",C426)),ISNUMBER(SEARCH("digital",C426)),ISNUMBER(SEARCH("engineering",C426)),ISNUMBER(SEARCH("solutions",C426))),"Technology",TRUE,"Other")</f>
-        <v>Finance</v>
+      <c r="A426" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="B426" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="C426" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="D426" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="E426" s="17">
+        <v>4000000</v>
+      </c>
+      <c r="F426" s="31">
+        <v>43544</v>
+      </c>
+      <c r="G426" s="14">
+        <v>3.88</v>
+      </c>
+      <c r="H426" s="9">
+        <v>55</v>
+      </c>
+      <c r="I426" s="29" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J426" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K426" s="10" t="s">
+        <v>1056</v>
       </c>
     </row>
     <row r="427" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="11" t="s">
-        <v>435</v>
-      </c>
-      <c r="B427" s="11" t="s">
-        <v>436</v>
-      </c>
-      <c r="C427" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="D427" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="E427" s="17">
-        <v>4000000</v>
-      </c>
-      <c r="F427" s="31">
-        <v>43544</v>
-      </c>
-      <c r="G427" s="14">
-        <v>3.88</v>
+      <c r="A427" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E427" s="16">
+        <v>5525000</v>
+      </c>
+      <c r="F427" s="5">
+        <v>44377</v>
+      </c>
+      <c r="G427" s="6">
+        <v>3.75</v>
       </c>
       <c r="H427" s="9">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I427" s="29" t="s">
         <v>1054</v>
@@ -20472,30 +20460,30 @@
         <v>1060</v>
       </c>
       <c r="K427" s="10" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="428" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
-        <v>358</v>
+        <v>548</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1453</v>
+        <v>549</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>359</v>
+        <v>550</v>
       </c>
       <c r="D428" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E428" s="16">
-        <v>5525000</v>
+        <v>551</v>
+      </c>
+      <c r="E428" s="18">
+        <v>3050000</v>
       </c>
       <c r="F428" s="5">
-        <v>44377</v>
+        <v>43656</v>
       </c>
       <c r="G428" s="6">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="H428" s="9">
         <v>52</v>
@@ -20510,27 +20498,27 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="429" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
-        <v>548</v>
+        <v>223</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>549</v>
+        <v>224</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>550</v>
+        <v>225</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>551</v>
+        <v>226</v>
       </c>
       <c r="E429" s="18">
-        <v>3050000</v>
+        <v>2199000</v>
       </c>
       <c r="F429" s="5">
-        <v>43656</v>
+        <v>43069</v>
       </c>
       <c r="G429" s="6">
-        <v>3.79</v>
+        <v>4.7130000000000001</v>
       </c>
       <c r="H429" s="9">
         <v>52</v>
@@ -20546,29 +20534,29 @@
       </c>
     </row>
     <row r="430" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B430" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C430" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D430" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E430" s="18">
-        <v>2199000</v>
-      </c>
-      <c r="F430" s="5">
-        <v>43069</v>
-      </c>
-      <c r="G430" s="6">
-        <v>4.7130000000000001</v>
+      <c r="A430" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B430" s="11" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C430" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D430" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E430" s="17">
+        <v>4700000</v>
+      </c>
+      <c r="F430" s="31">
+        <v>44411</v>
+      </c>
+      <c r="G430" s="12">
+        <v>3.23</v>
       </c>
       <c r="H430" s="9">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I430" s="29" t="s">
         <v>1054</v>
@@ -20577,29 +20565,29 @@
         <v>1060</v>
       </c>
       <c r="K430" s="10" t="s">
-        <v>1050</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="431" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A431" s="11" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B431" s="11" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C431" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D431" s="11" t="s">
+      <c r="A431" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D431" s="4" t="s">
         <v>1080</v>
       </c>
-      <c r="E431" s="17">
+      <c r="E431" s="16">
         <v>4700000</v>
       </c>
-      <c r="F431" s="31">
+      <c r="F431" s="5">
         <v>44411</v>
       </c>
-      <c r="G431" s="12">
+      <c r="G431" s="6">
         <v>3.23</v>
       </c>
       <c r="H431" s="9">
@@ -20616,100 +20604,100 @@
       </c>
     </row>
     <row r="432" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A432" s="4" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>1527</v>
-      </c>
-      <c r="D432" s="4" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E432" s="16">
-        <v>4700000</v>
-      </c>
-      <c r="F432" s="5">
-        <v>44411</v>
-      </c>
-      <c r="G432" s="6">
-        <v>3.23</v>
-      </c>
-      <c r="H432" s="9">
+      <c r="A432" s="25" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B432" s="25" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C432" s="25" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D432" s="25" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E432" s="30">
+        <v>4385000</v>
+      </c>
+      <c r="F432" s="26">
+        <v>45460</v>
+      </c>
+      <c r="G432" s="27">
+        <v>2.97</v>
+      </c>
+      <c r="H432" s="28" cm="1">
+        <f t="array" ref="H432">_xlfn.IFS(I432="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B432)),80,96),I432="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B432)),ISNUMBER(SEARCH("chief executive",B432))),95,91),I432="Managing Director",86,I432="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B432)),ISNUMBER(SEARCH("general partner",B432))),88,85),I432="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B432)),ISNUMBER(SEARCH("executive vice",B432))),91,ISNUMBER(SEARCH("svp",B432)),77,TRUE,73),I432="Director",IF(ISNUMBER(SEARCH("principal",B432)),72,71),I432="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B432)),ISNUMBER(SEARCH("physician",B432)),ISNUMBER(SEARCH("doctor",B432)),ISNUMBER(SEARCH("dentist",B432)),ISNUMBER(SEARCH("psychiat",B432)),ISNUMBER(SEARCH("oncolog",B432)),ISNUMBER(SEARCH("neurolog",B432)),ISNUMBER(SEARCH("patholog",B432)),ISNUMBER(SEARCH("medicine",B432)),ISNUMBER(SEARCH("obgyn",B432))),77,OR(ISNUMBER(SEARCH("portfolio manager",B432)),ISNUMBER(SEARCH("wealth advisor",B432))),81,OR(ISNUMBER(SEARCH("lawyer",B432)),ISNUMBER(SEARCH("attorney",B432))),68,ISNUMBER(SEARCH("counsel",B432)),66,ISNUMBER(SEARCH("professor",B432)),63,OR(ISNUMBER(SEARCH("engineer",B432)),ISNUMBER(SEARCH("consultant",B432))),62,ISNUMBER(SEARCH("senior manager",B432)),64,OR(ISNUMBER(SEARCH("realtor",B432)),ISNUMBER(SEARCH("broker",B432)),ISNUMBER(SEARCH("journalist",B432)),ISNUMBER(SEARCH("columnist",B432)),ISNUMBER(SEARCH("trader",B432)),ISNUMBER(SEARCH("actor",B432))),50,TRUE,60)</f>
         <v>50</v>
       </c>
-      <c r="I432" s="29" t="s">
+      <c r="I432" s="29" t="str" cm="1">
+        <f t="array" ref="I432">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B432,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
+        <v>Professional</v>
+      </c>
+      <c r="J432" s="29" t="str" cm="1">
+        <f t="array" ref="J432">_xlfn.IFS(H432&gt;=90,"Very High",H432&gt;=80,"High",H432&gt;=56,"Medium",TRUE,"Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="K432" s="29" t="str" cm="1">
+        <f t="array" ref="K432">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C432)),ISNUMBER(SEARCH("health",C432)),ISNUMBER(SEARCH("medical",C432)),ISNUMBER(SEARCH("clinic",C432)),ISNUMBER(SEARCH("nursing",C432)),ISNUMBER(SEARCH("care cent",C432)),ISNUMBER(SEARCH("physician",B432)),ISNUMBER(SEARCH("doctor",B432)),ISNUMBER(SEARCH("dentist",B432)),ISNUMBER(SEARCH("surgeon",B432)),ISNUMBER(SEARCH("psychiat",B432)),ISNUMBER(SEARCH("medicine",B432))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C432)),ISNUMBER(SEARCH("lawyer",B432)),ISNUMBER(SEARCH("attorney",B432)),ISNUMBER(SEARCH("legal",C432)),ISNUMBER(SEARCH("tetrault",C432)),ISNUMBER(SEARCH("morley",C432)),ISNUMBER(SEARCH("blg",C432)),ISNUMBER(SEARCH("lowy",C432)),ISNUMBER(SEARCH("riley",C432)),ISNUMBER(SEARCH("toomath",C432))),"Law",OR(ISNUMBER(SEARCH("reit",C432)),ISNUMBER(SEARCH("properties",C432)),ISNUMBER(SEARCH("realty",C432)),ISNUMBER(SEARCH("realtor",B432)),ISNUMBER(SEARCH("colliers",C432)),ISNUMBER(SEARCH("re/max",C432)),ISNUMBER(SEARCH("quadreal",C432)),ISNUMBER(SEARCH("vic management",C432))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C432)),ISNUMBER(SEARCH("kpmg",C432)),ISNUMBER(SEARCH("pwc",C432)),ISNUMBER(SEARCH("consulting",C432)),ISNUMBER(SEARCH("consultant",B432)),ISNUMBER(SEARCH("advisory",C432)),ISNUMBER(SEARCH("philanthropic",C432)),ISNUMBER(SEARCH("argyle",C432)),ISNUMBER(SEARCH("quinn",C432))),"Consulting",OR(ISNUMBER(SEARCH("media",C432)),ISNUMBER(SEARCH("news",C432)),ISNUMBER(SEARCH("radio",C432)),ISNUMBER(SEARCH("film",C432)),ISNUMBER(SEARCH("journalist",B432)),ISNUMBER(SEARCH("columnist",B432)),ISNUMBER(SEARCH("globe",C432)),ISNUMBER(SEARCH("marketing",C432)),ISNUMBER(SEARCH("actor",B432))),"Media",OR(ISNUMBER(SEARCH("rbc",C432)),ISNUMBER(SEARCH("cibc",C432)),ISNUMBER(SEARCH("bmo",C432)),ISNUMBER(SEARCH("scotia",C432)),ISNUMBER(SEARCH("bank",C432)),ISNUMBER(SEARCH("capital",C432)),ISNUMBER(SEARCH("wealth",C432)),ISNUMBER(SEARCH("financial",C432)),ISNUMBER(SEARCH("securities",C432)),ISNUMBER(SEARCH("fidelity",C432)),ISNUMBER(SEARCH("guardian",C432)),ISNUMBER(SEARCH("wealthsimple",C432)),ISNUMBER(SEARCH("credit suisse",C432)),ISNUMBER(SEARCH("tmx",C432)),ISNUMBER(SEARCH("investors",C432)),ISNUMBER(SEARCH("trader",B432))),"Finance",OR(ISNUMBER(SEARCH("ventures",C432)),ISNUMBER(SEARCH("private equity",B432)),ISNUMBER(SEARCH("capital partners",C432))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C432)),ISNUMBER(SEARCH("ministry",C432)),ISNUMBER(SEARCH("tribunal",C432)),ISNUMBER(SEARCH("tdsb",C432)),ISNUMBER(SEARCH("public service",C432))),"Government",OR(ISNUMBER(SEARCH("association",C432)),ISNUMBER(SEARCH("institute",C432)),ISNUMBER(SEARCH("foundation",C432))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C432)),ISNUMBER(SEARCH("tech",C432)),ISNUMBER(SEARCH("systems",C432)),ISNUMBER(SEARCH("digital",C432)),ISNUMBER(SEARCH("engineering",C432)),ISNUMBER(SEARCH("solutions",C432))),"Technology",TRUE,"Other")</f>
+        <v>Finance</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A433" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E433" s="18">
+        <v>3775000</v>
+      </c>
+      <c r="F433" s="5">
+        <v>43735</v>
+      </c>
+      <c r="G433" s="6">
+        <v>3.28</v>
+      </c>
+      <c r="H433" s="9">
+        <v>50</v>
+      </c>
+      <c r="I433" s="29" t="s">
         <v>1054</v>
       </c>
-      <c r="J432" s="10" t="s">
+      <c r="J433" s="10" t="s">
         <v>1060</v>
       </c>
-      <c r="K432" s="10" t="s">
+      <c r="K433" s="10" t="s">
         <v>1065</v>
-      </c>
-    </row>
-    <row r="433" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A433" s="25" t="s">
-        <v>1335</v>
-      </c>
-      <c r="B433" s="25" t="s">
-        <v>1549</v>
-      </c>
-      <c r="C433" s="25" t="s">
-        <v>1446</v>
-      </c>
-      <c r="D433" s="25" t="s">
-        <v>1336</v>
-      </c>
-      <c r="E433" s="30">
-        <v>4385000</v>
-      </c>
-      <c r="F433" s="26">
-        <v>45460</v>
-      </c>
-      <c r="G433" s="27">
-        <v>2.97</v>
-      </c>
-      <c r="H433" s="28" cm="1">
-        <f t="array" ref="H433">_xlfn.IFS(I433="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B433)),80,96),I433="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B433)),ISNUMBER(SEARCH("chief executive",B433))),95,91),I433="Managing Director",86,I433="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B433)),ISNUMBER(SEARCH("general partner",B433))),88,85),I433="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B433)),ISNUMBER(SEARCH("executive vice",B433))),91,ISNUMBER(SEARCH("svp",B433)),77,TRUE,73),I433="Director",IF(ISNUMBER(SEARCH("principal",B433)),72,71),I433="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B433)),ISNUMBER(SEARCH("physician",B433)),ISNUMBER(SEARCH("doctor",B433)),ISNUMBER(SEARCH("dentist",B433)),ISNUMBER(SEARCH("psychiat",B433)),ISNUMBER(SEARCH("oncolog",B433)),ISNUMBER(SEARCH("neurolog",B433)),ISNUMBER(SEARCH("patholog",B433)),ISNUMBER(SEARCH("medicine",B433)),ISNUMBER(SEARCH("obgyn",B433))),77,OR(ISNUMBER(SEARCH("portfolio manager",B433)),ISNUMBER(SEARCH("wealth advisor",B433))),81,OR(ISNUMBER(SEARCH("lawyer",B433)),ISNUMBER(SEARCH("attorney",B433))),68,ISNUMBER(SEARCH("counsel",B433)),66,ISNUMBER(SEARCH("professor",B433)),63,OR(ISNUMBER(SEARCH("engineer",B433)),ISNUMBER(SEARCH("consultant",B433))),62,ISNUMBER(SEARCH("senior manager",B433)),64,OR(ISNUMBER(SEARCH("realtor",B433)),ISNUMBER(SEARCH("broker",B433)),ISNUMBER(SEARCH("journalist",B433)),ISNUMBER(SEARCH("columnist",B433)),ISNUMBER(SEARCH("trader",B433)),ISNUMBER(SEARCH("actor",B433))),50,TRUE,60)</f>
-        <v>50</v>
-      </c>
-      <c r="I433" s="29" t="str" cm="1">
-        <f t="array" ref="I433">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B433,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
-        <v>Professional</v>
-      </c>
-      <c r="J433" s="29" t="str" cm="1">
-        <f t="array" ref="J433">_xlfn.IFS(H433&gt;=90,"Very High",H433&gt;=80,"High",H433&gt;=56,"Medium",TRUE,"Low")</f>
-        <v>Low</v>
-      </c>
-      <c r="K433" s="29" t="str" cm="1">
-        <f t="array" ref="K433">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C433)),ISNUMBER(SEARCH("health",C433)),ISNUMBER(SEARCH("medical",C433)),ISNUMBER(SEARCH("clinic",C433)),ISNUMBER(SEARCH("nursing",C433)),ISNUMBER(SEARCH("care cent",C433)),ISNUMBER(SEARCH("physician",B433)),ISNUMBER(SEARCH("doctor",B433)),ISNUMBER(SEARCH("dentist",B433)),ISNUMBER(SEARCH("surgeon",B433)),ISNUMBER(SEARCH("psychiat",B433)),ISNUMBER(SEARCH("medicine",B433))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C433)),ISNUMBER(SEARCH("lawyer",B433)),ISNUMBER(SEARCH("attorney",B433)),ISNUMBER(SEARCH("legal",C433)),ISNUMBER(SEARCH("tetrault",C433)),ISNUMBER(SEARCH("morley",C433)),ISNUMBER(SEARCH("blg",C433)),ISNUMBER(SEARCH("lowy",C433)),ISNUMBER(SEARCH("riley",C433)),ISNUMBER(SEARCH("toomath",C433))),"Law",OR(ISNUMBER(SEARCH("reit",C433)),ISNUMBER(SEARCH("properties",C433)),ISNUMBER(SEARCH("realty",C433)),ISNUMBER(SEARCH("realtor",B433)),ISNUMBER(SEARCH("colliers",C433)),ISNUMBER(SEARCH("re/max",C433)),ISNUMBER(SEARCH("quadreal",C433)),ISNUMBER(SEARCH("vic management",C433))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C433)),ISNUMBER(SEARCH("kpmg",C433)),ISNUMBER(SEARCH("pwc",C433)),ISNUMBER(SEARCH("consulting",C433)),ISNUMBER(SEARCH("consultant",B433)),ISNUMBER(SEARCH("advisory",C433)),ISNUMBER(SEARCH("philanthropic",C433)),ISNUMBER(SEARCH("argyle",C433)),ISNUMBER(SEARCH("quinn",C433))),"Consulting",OR(ISNUMBER(SEARCH("media",C433)),ISNUMBER(SEARCH("news",C433)),ISNUMBER(SEARCH("radio",C433)),ISNUMBER(SEARCH("film",C433)),ISNUMBER(SEARCH("journalist",B433)),ISNUMBER(SEARCH("columnist",B433)),ISNUMBER(SEARCH("globe",C433)),ISNUMBER(SEARCH("marketing",C433)),ISNUMBER(SEARCH("actor",B433))),"Media",OR(ISNUMBER(SEARCH("rbc",C433)),ISNUMBER(SEARCH("cibc",C433)),ISNUMBER(SEARCH("bmo",C433)),ISNUMBER(SEARCH("scotia",C433)),ISNUMBER(SEARCH("bank",C433)),ISNUMBER(SEARCH("capital",C433)),ISNUMBER(SEARCH("wealth",C433)),ISNUMBER(SEARCH("financial",C433)),ISNUMBER(SEARCH("securities",C433)),ISNUMBER(SEARCH("fidelity",C433)),ISNUMBER(SEARCH("guardian",C433)),ISNUMBER(SEARCH("wealthsimple",C433)),ISNUMBER(SEARCH("credit suisse",C433)),ISNUMBER(SEARCH("tmx",C433)),ISNUMBER(SEARCH("investors",C433)),ISNUMBER(SEARCH("trader",B433))),"Finance",OR(ISNUMBER(SEARCH("ventures",C433)),ISNUMBER(SEARCH("private equity",B433)),ISNUMBER(SEARCH("capital partners",C433))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C433)),ISNUMBER(SEARCH("ministry",C433)),ISNUMBER(SEARCH("tribunal",C433)),ISNUMBER(SEARCH("tdsb",C433)),ISNUMBER(SEARCH("public service",C433))),"Government",OR(ISNUMBER(SEARCH("association",C433)),ISNUMBER(SEARCH("institute",C433)),ISNUMBER(SEARCH("foundation",C433))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C433)),ISNUMBER(SEARCH("tech",C433)),ISNUMBER(SEARCH("systems",C433)),ISNUMBER(SEARCH("digital",C433)),ISNUMBER(SEARCH("engineering",C433)),ISNUMBER(SEARCH("solutions",C433))),"Technology",TRUE,"Other")</f>
-        <v>Finance</v>
       </c>
     </row>
     <row r="434" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
-        <v>1094</v>
+        <v>273</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>646</v>
+        <v>274</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>354</v>
+        <v>275</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>1095</v>
+        <v>182</v>
       </c>
       <c r="E434" s="18">
-        <v>3775000</v>
+        <v>3600100</v>
       </c>
       <c r="F434" s="5">
-        <v>43735</v>
+        <v>44778</v>
       </c>
       <c r="G434" s="6">
-        <v>3.28</v>
+        <v>4.633</v>
       </c>
       <c r="H434" s="9">
         <v>50</v>
@@ -20725,61 +20713,65 @@
       </c>
     </row>
     <row r="435" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="B435" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="C435" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D435" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="E435" s="18">
-        <v>3600100</v>
-      </c>
-      <c r="F435" s="5">
-        <v>44778</v>
-      </c>
-      <c r="G435" s="6">
-        <v>4.633</v>
-      </c>
-      <c r="H435" s="9">
+      <c r="A435" s="25" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B435" s="25" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C435" s="25" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D435" s="25" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E435" s="30">
+        <v>3000000</v>
+      </c>
+      <c r="F435" s="26">
+        <v>45505</v>
+      </c>
+      <c r="G435" s="27">
+        <v>3.16</v>
+      </c>
+      <c r="H435" s="28" cm="1">
+        <f t="array" ref="H435">_xlfn.IFS(I435="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B435)),80,96),I435="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B435)),ISNUMBER(SEARCH("chief executive",B435))),95,91),I435="Managing Director",86,I435="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B435)),ISNUMBER(SEARCH("general partner",B435))),88,85),I435="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B435)),ISNUMBER(SEARCH("executive vice",B435))),91,ISNUMBER(SEARCH("svp",B435)),77,TRUE,73),I435="Director",IF(ISNUMBER(SEARCH("principal",B435)),72,71),I435="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B435)),ISNUMBER(SEARCH("physician",B435)),ISNUMBER(SEARCH("doctor",B435)),ISNUMBER(SEARCH("dentist",B435)),ISNUMBER(SEARCH("psychiat",B435)),ISNUMBER(SEARCH("oncolog",B435)),ISNUMBER(SEARCH("neurolog",B435)),ISNUMBER(SEARCH("patholog",B435)),ISNUMBER(SEARCH("medicine",B435)),ISNUMBER(SEARCH("obgyn",B435))),77,OR(ISNUMBER(SEARCH("portfolio manager",B435)),ISNUMBER(SEARCH("wealth advisor",B435))),81,OR(ISNUMBER(SEARCH("lawyer",B435)),ISNUMBER(SEARCH("attorney",B435))),68,ISNUMBER(SEARCH("counsel",B435)),66,ISNUMBER(SEARCH("professor",B435)),63,OR(ISNUMBER(SEARCH("engineer",B435)),ISNUMBER(SEARCH("consultant",B435))),62,ISNUMBER(SEARCH("senior manager",B435)),64,OR(ISNUMBER(SEARCH("realtor",B435)),ISNUMBER(SEARCH("broker",B435)),ISNUMBER(SEARCH("journalist",B435)),ISNUMBER(SEARCH("columnist",B435)),ISNUMBER(SEARCH("trader",B435)),ISNUMBER(SEARCH("actor",B435))),50,TRUE,60)</f>
         <v>50</v>
       </c>
-      <c r="I435" s="29" t="s">
-        <v>1054</v>
-      </c>
-      <c r="J435" s="10" t="s">
-        <v>1060</v>
-      </c>
-      <c r="K435" s="10" t="s">
-        <v>1065</v>
+      <c r="I435" s="29" t="str" cm="1">
+        <f t="array" ref="I435">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
+        <v>Professional</v>
+      </c>
+      <c r="J435" s="29" t="str" cm="1">
+        <f t="array" ref="J435">_xlfn.IFS(H435&gt;=90,"Very High",H435&gt;=80,"High",H435&gt;=56,"Medium",TRUE,"Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="K435" s="29" t="str" cm="1">
+        <f t="array" ref="K435">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C435)),ISNUMBER(SEARCH("health",C435)),ISNUMBER(SEARCH("medical",C435)),ISNUMBER(SEARCH("clinic",C435)),ISNUMBER(SEARCH("nursing",C435)),ISNUMBER(SEARCH("care cent",C435)),ISNUMBER(SEARCH("physician",B435)),ISNUMBER(SEARCH("doctor",B435)),ISNUMBER(SEARCH("dentist",B435)),ISNUMBER(SEARCH("surgeon",B435)),ISNUMBER(SEARCH("psychiat",B435)),ISNUMBER(SEARCH("medicine",B435))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C435)),ISNUMBER(SEARCH("lawyer",B435)),ISNUMBER(SEARCH("attorney",B435)),ISNUMBER(SEARCH("legal",C435)),ISNUMBER(SEARCH("tetrault",C435)),ISNUMBER(SEARCH("morley",C435)),ISNUMBER(SEARCH("blg",C435)),ISNUMBER(SEARCH("lowy",C435)),ISNUMBER(SEARCH("riley",C435)),ISNUMBER(SEARCH("toomath",C435))),"Law",OR(ISNUMBER(SEARCH("reit",C435)),ISNUMBER(SEARCH("properties",C435)),ISNUMBER(SEARCH("realty",C435)),ISNUMBER(SEARCH("realtor",B435)),ISNUMBER(SEARCH("colliers",C435)),ISNUMBER(SEARCH("re/max",C435)),ISNUMBER(SEARCH("quadreal",C435)),ISNUMBER(SEARCH("vic management",C435))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C435)),ISNUMBER(SEARCH("kpmg",C435)),ISNUMBER(SEARCH("pwc",C435)),ISNUMBER(SEARCH("consulting",C435)),ISNUMBER(SEARCH("consultant",B435)),ISNUMBER(SEARCH("advisory",C435)),ISNUMBER(SEARCH("philanthropic",C435)),ISNUMBER(SEARCH("argyle",C435)),ISNUMBER(SEARCH("quinn",C435))),"Consulting",OR(ISNUMBER(SEARCH("media",C435)),ISNUMBER(SEARCH("news",C435)),ISNUMBER(SEARCH("radio",C435)),ISNUMBER(SEARCH("film",C435)),ISNUMBER(SEARCH("journalist",B435)),ISNUMBER(SEARCH("columnist",B435)),ISNUMBER(SEARCH("globe",C435)),ISNUMBER(SEARCH("marketing",C435)),ISNUMBER(SEARCH("actor",B435))),"Media",OR(ISNUMBER(SEARCH("rbc",C435)),ISNUMBER(SEARCH("cibc",C435)),ISNUMBER(SEARCH("bmo",C435)),ISNUMBER(SEARCH("scotia",C435)),ISNUMBER(SEARCH("bank",C435)),ISNUMBER(SEARCH("capital",C435)),ISNUMBER(SEARCH("wealth",C435)),ISNUMBER(SEARCH("financial",C435)),ISNUMBER(SEARCH("securities",C435)),ISNUMBER(SEARCH("fidelity",C435)),ISNUMBER(SEARCH("guardian",C435)),ISNUMBER(SEARCH("wealthsimple",C435)),ISNUMBER(SEARCH("credit suisse",C435)),ISNUMBER(SEARCH("tmx",C435)),ISNUMBER(SEARCH("investors",C435)),ISNUMBER(SEARCH("trader",B435))),"Finance",OR(ISNUMBER(SEARCH("ventures",C435)),ISNUMBER(SEARCH("private equity",B435)),ISNUMBER(SEARCH("capital partners",C435))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C435)),ISNUMBER(SEARCH("ministry",C435)),ISNUMBER(SEARCH("tribunal",C435)),ISNUMBER(SEARCH("tdsb",C435)),ISNUMBER(SEARCH("public service",C435))),"Government",OR(ISNUMBER(SEARCH("association",C435)),ISNUMBER(SEARCH("institute",C435)),ISNUMBER(SEARCH("foundation",C435))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C435)),ISNUMBER(SEARCH("tech",C435)),ISNUMBER(SEARCH("systems",C435)),ISNUMBER(SEARCH("digital",C435)),ISNUMBER(SEARCH("engineering",C435)),ISNUMBER(SEARCH("solutions",C435))),"Technology",TRUE,"Other")</f>
+        <v>Media</v>
       </c>
     </row>
     <row r="436" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A436" s="25" t="s">
-        <v>1374</v>
+        <v>1432</v>
       </c>
       <c r="B436" s="25" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="C436" s="25" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="D436" s="25" t="s">
-        <v>1375</v>
+        <v>1431</v>
       </c>
       <c r="E436" s="30">
-        <v>3000000</v>
+        <v>2975000</v>
       </c>
       <c r="F436" s="26">
-        <v>45505</v>
+        <v>44176</v>
       </c>
       <c r="G436" s="27">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="H436" s="28" cm="1">
         <f t="array" ref="H436">_xlfn.IFS(I436="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B436)),80,96),I436="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B436)),ISNUMBER(SEARCH("chief executive",B436))),95,91),I436="Managing Director",86,I436="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B436)),ISNUMBER(SEARCH("general partner",B436))),88,85),I436="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B436)),ISNUMBER(SEARCH("executive vice",B436))),91,ISNUMBER(SEARCH("svp",B436)),77,TRUE,73),I436="Director",IF(ISNUMBER(SEARCH("principal",B436)),72,71),I436="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B436)),ISNUMBER(SEARCH("physician",B436)),ISNUMBER(SEARCH("doctor",B436)),ISNUMBER(SEARCH("dentist",B436)),ISNUMBER(SEARCH("psychiat",B436)),ISNUMBER(SEARCH("oncolog",B436)),ISNUMBER(SEARCH("neurolog",B436)),ISNUMBER(SEARCH("patholog",B436)),ISNUMBER(SEARCH("medicine",B436)),ISNUMBER(SEARCH("obgyn",B436))),77,OR(ISNUMBER(SEARCH("portfolio manager",B436)),ISNUMBER(SEARCH("wealth advisor",B436))),81,OR(ISNUMBER(SEARCH("lawyer",B436)),ISNUMBER(SEARCH("attorney",B436))),68,ISNUMBER(SEARCH("counsel",B436)),66,ISNUMBER(SEARCH("professor",B436)),63,OR(ISNUMBER(SEARCH("engineer",B436)),ISNUMBER(SEARCH("consultant",B436))),62,ISNUMBER(SEARCH("senior manager",B436)),64,OR(ISNUMBER(SEARCH("realtor",B436)),ISNUMBER(SEARCH("broker",B436)),ISNUMBER(SEARCH("journalist",B436)),ISNUMBER(SEARCH("columnist",B436)),ISNUMBER(SEARCH("trader",B436)),ISNUMBER(SEARCH("actor",B436))),50,TRUE,60)</f>
@@ -20795,30 +20787,30 @@
       </c>
       <c r="K436" s="29" t="str" cm="1">
         <f t="array" ref="K436">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C436)),ISNUMBER(SEARCH("health",C436)),ISNUMBER(SEARCH("medical",C436)),ISNUMBER(SEARCH("clinic",C436)),ISNUMBER(SEARCH("nursing",C436)),ISNUMBER(SEARCH("care cent",C436)),ISNUMBER(SEARCH("physician",B436)),ISNUMBER(SEARCH("doctor",B436)),ISNUMBER(SEARCH("dentist",B436)),ISNUMBER(SEARCH("surgeon",B436)),ISNUMBER(SEARCH("psychiat",B436)),ISNUMBER(SEARCH("medicine",B436))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C436)),ISNUMBER(SEARCH("lawyer",B436)),ISNUMBER(SEARCH("attorney",B436)),ISNUMBER(SEARCH("legal",C436)),ISNUMBER(SEARCH("tetrault",C436)),ISNUMBER(SEARCH("morley",C436)),ISNUMBER(SEARCH("blg",C436)),ISNUMBER(SEARCH("lowy",C436)),ISNUMBER(SEARCH("riley",C436)),ISNUMBER(SEARCH("toomath",C436))),"Law",OR(ISNUMBER(SEARCH("reit",C436)),ISNUMBER(SEARCH("properties",C436)),ISNUMBER(SEARCH("realty",C436)),ISNUMBER(SEARCH("realtor",B436)),ISNUMBER(SEARCH("colliers",C436)),ISNUMBER(SEARCH("re/max",C436)),ISNUMBER(SEARCH("quadreal",C436)),ISNUMBER(SEARCH("vic management",C436))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C436)),ISNUMBER(SEARCH("kpmg",C436)),ISNUMBER(SEARCH("pwc",C436)),ISNUMBER(SEARCH("consulting",C436)),ISNUMBER(SEARCH("consultant",B436)),ISNUMBER(SEARCH("advisory",C436)),ISNUMBER(SEARCH("philanthropic",C436)),ISNUMBER(SEARCH("argyle",C436)),ISNUMBER(SEARCH("quinn",C436))),"Consulting",OR(ISNUMBER(SEARCH("media",C436)),ISNUMBER(SEARCH("news",C436)),ISNUMBER(SEARCH("radio",C436)),ISNUMBER(SEARCH("film",C436)),ISNUMBER(SEARCH("journalist",B436)),ISNUMBER(SEARCH("columnist",B436)),ISNUMBER(SEARCH("globe",C436)),ISNUMBER(SEARCH("marketing",C436)),ISNUMBER(SEARCH("actor",B436))),"Media",OR(ISNUMBER(SEARCH("rbc",C436)),ISNUMBER(SEARCH("cibc",C436)),ISNUMBER(SEARCH("bmo",C436)),ISNUMBER(SEARCH("scotia",C436)),ISNUMBER(SEARCH("bank",C436)),ISNUMBER(SEARCH("capital",C436)),ISNUMBER(SEARCH("wealth",C436)),ISNUMBER(SEARCH("financial",C436)),ISNUMBER(SEARCH("securities",C436)),ISNUMBER(SEARCH("fidelity",C436)),ISNUMBER(SEARCH("guardian",C436)),ISNUMBER(SEARCH("wealthsimple",C436)),ISNUMBER(SEARCH("credit suisse",C436)),ISNUMBER(SEARCH("tmx",C436)),ISNUMBER(SEARCH("investors",C436)),ISNUMBER(SEARCH("trader",B436))),"Finance",OR(ISNUMBER(SEARCH("ventures",C436)),ISNUMBER(SEARCH("private equity",B436)),ISNUMBER(SEARCH("capital partners",C436))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C436)),ISNUMBER(SEARCH("ministry",C436)),ISNUMBER(SEARCH("tribunal",C436)),ISNUMBER(SEARCH("tdsb",C436)),ISNUMBER(SEARCH("public service",C436))),"Government",OR(ISNUMBER(SEARCH("association",C436)),ISNUMBER(SEARCH("institute",C436)),ISNUMBER(SEARCH("foundation",C436))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C436)),ISNUMBER(SEARCH("tech",C436)),ISNUMBER(SEARCH("systems",C436)),ISNUMBER(SEARCH("digital",C436)),ISNUMBER(SEARCH("engineering",C436)),ISNUMBER(SEARCH("solutions",C436))),"Technology",TRUE,"Other")</f>
-        <v>Media</v>
+        <v>Real Estate</v>
       </c>
     </row>
     <row r="437" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A437" s="25" t="s">
-        <v>1436</v>
+        <v>1416</v>
       </c>
       <c r="B437" s="25" t="s">
-        <v>1453</v>
+        <v>1417</v>
       </c>
       <c r="C437" s="25" t="s">
-        <v>1454</v>
+        <v>1418</v>
       </c>
       <c r="D437" s="25" t="s">
-        <v>1435</v>
+        <v>1419</v>
       </c>
       <c r="E437" s="30">
-        <v>2975000</v>
+        <v>2847000</v>
       </c>
       <c r="F437" s="26">
-        <v>44176</v>
+        <v>45596</v>
       </c>
       <c r="G437" s="27">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="H437" s="28" cm="1">
         <f t="array" ref="H437">_xlfn.IFS(I437="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B437)),80,96),I437="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B437)),ISNUMBER(SEARCH("chief executive",B437))),95,91),I437="Managing Director",86,I437="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B437)),ISNUMBER(SEARCH("general partner",B437))),88,85),I437="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B437)),ISNUMBER(SEARCH("executive vice",B437))),91,ISNUMBER(SEARCH("svp",B437)),77,TRUE,73),I437="Director",IF(ISNUMBER(SEARCH("principal",B437)),72,71),I437="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B437)),ISNUMBER(SEARCH("physician",B437)),ISNUMBER(SEARCH("doctor",B437)),ISNUMBER(SEARCH("dentist",B437)),ISNUMBER(SEARCH("psychiat",B437)),ISNUMBER(SEARCH("oncolog",B437)),ISNUMBER(SEARCH("neurolog",B437)),ISNUMBER(SEARCH("patholog",B437)),ISNUMBER(SEARCH("medicine",B437)),ISNUMBER(SEARCH("obgyn",B437))),77,OR(ISNUMBER(SEARCH("portfolio manager",B437)),ISNUMBER(SEARCH("wealth advisor",B437))),81,OR(ISNUMBER(SEARCH("lawyer",B437)),ISNUMBER(SEARCH("attorney",B437))),68,ISNUMBER(SEARCH("counsel",B437)),66,ISNUMBER(SEARCH("professor",B437)),63,OR(ISNUMBER(SEARCH("engineer",B437)),ISNUMBER(SEARCH("consultant",B437))),62,ISNUMBER(SEARCH("senior manager",B437)),64,OR(ISNUMBER(SEARCH("realtor",B437)),ISNUMBER(SEARCH("broker",B437)),ISNUMBER(SEARCH("journalist",B437)),ISNUMBER(SEARCH("columnist",B437)),ISNUMBER(SEARCH("trader",B437)),ISNUMBER(SEARCH("actor",B437))),50,TRUE,60)</f>
@@ -20838,65 +20830,61 @@
       </c>
     </row>
     <row r="438" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A438" s="25" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B438" s="25" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C438" s="25" t="s">
-        <v>1422</v>
-      </c>
-      <c r="D438" s="25" t="s">
-        <v>1423</v>
-      </c>
-      <c r="E438" s="30">
-        <v>2847000</v>
-      </c>
-      <c r="F438" s="26">
-        <v>45596</v>
-      </c>
-      <c r="G438" s="27">
-        <v>3.22</v>
-      </c>
-      <c r="H438" s="28" cm="1">
-        <f t="array" ref="H438">_xlfn.IFS(I438="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B438)),80,96),I438="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B438)),ISNUMBER(SEARCH("chief executive",B438))),95,91),I438="Managing Director",86,I438="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B438)),ISNUMBER(SEARCH("general partner",B438))),88,85),I438="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B438)),ISNUMBER(SEARCH("executive vice",B438))),91,ISNUMBER(SEARCH("svp",B438)),77,TRUE,73),I438="Director",IF(ISNUMBER(SEARCH("principal",B438)),72,71),I438="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B438)),ISNUMBER(SEARCH("physician",B438)),ISNUMBER(SEARCH("doctor",B438)),ISNUMBER(SEARCH("dentist",B438)),ISNUMBER(SEARCH("psychiat",B438)),ISNUMBER(SEARCH("oncolog",B438)),ISNUMBER(SEARCH("neurolog",B438)),ISNUMBER(SEARCH("patholog",B438)),ISNUMBER(SEARCH("medicine",B438)),ISNUMBER(SEARCH("obgyn",B438))),77,OR(ISNUMBER(SEARCH("portfolio manager",B438)),ISNUMBER(SEARCH("wealth advisor",B438))),81,OR(ISNUMBER(SEARCH("lawyer",B438)),ISNUMBER(SEARCH("attorney",B438))),68,ISNUMBER(SEARCH("counsel",B438)),66,ISNUMBER(SEARCH("professor",B438)),63,OR(ISNUMBER(SEARCH("engineer",B438)),ISNUMBER(SEARCH("consultant",B438))),62,ISNUMBER(SEARCH("senior manager",B438)),64,OR(ISNUMBER(SEARCH("realtor",B438)),ISNUMBER(SEARCH("broker",B438)),ISNUMBER(SEARCH("journalist",B438)),ISNUMBER(SEARCH("columnist",B438)),ISNUMBER(SEARCH("trader",B438)),ISNUMBER(SEARCH("actor",B438))),50,TRUE,60)</f>
+      <c r="A438" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="E438" s="18">
+        <v>2420000</v>
+      </c>
+      <c r="F438" s="5">
+        <v>40717</v>
+      </c>
+      <c r="G438" s="6">
+        <v>3.72</v>
+      </c>
+      <c r="H438" s="9">
         <v>50</v>
       </c>
-      <c r="I438" s="29" t="str" cm="1">
-        <f t="array" ref="I438">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
-        <v>Professional</v>
-      </c>
-      <c r="J438" s="29" t="str" cm="1">
-        <f t="array" ref="J438">_xlfn.IFS(H438&gt;=90,"Very High",H438&gt;=80,"High",H438&gt;=56,"Medium",TRUE,"Low")</f>
-        <v>Low</v>
-      </c>
-      <c r="K438" s="29" t="str" cm="1">
-        <f t="array" ref="K438">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C438)),ISNUMBER(SEARCH("health",C438)),ISNUMBER(SEARCH("medical",C438)),ISNUMBER(SEARCH("clinic",C438)),ISNUMBER(SEARCH("nursing",C438)),ISNUMBER(SEARCH("care cent",C438)),ISNUMBER(SEARCH("physician",B438)),ISNUMBER(SEARCH("doctor",B438)),ISNUMBER(SEARCH("dentist",B438)),ISNUMBER(SEARCH("surgeon",B438)),ISNUMBER(SEARCH("psychiat",B438)),ISNUMBER(SEARCH("medicine",B438))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C438)),ISNUMBER(SEARCH("lawyer",B438)),ISNUMBER(SEARCH("attorney",B438)),ISNUMBER(SEARCH("legal",C438)),ISNUMBER(SEARCH("tetrault",C438)),ISNUMBER(SEARCH("morley",C438)),ISNUMBER(SEARCH("blg",C438)),ISNUMBER(SEARCH("lowy",C438)),ISNUMBER(SEARCH("riley",C438)),ISNUMBER(SEARCH("toomath",C438))),"Law",OR(ISNUMBER(SEARCH("reit",C438)),ISNUMBER(SEARCH("properties",C438)),ISNUMBER(SEARCH("realty",C438)),ISNUMBER(SEARCH("realtor",B438)),ISNUMBER(SEARCH("colliers",C438)),ISNUMBER(SEARCH("re/max",C438)),ISNUMBER(SEARCH("quadreal",C438)),ISNUMBER(SEARCH("vic management",C438))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C438)),ISNUMBER(SEARCH("kpmg",C438)),ISNUMBER(SEARCH("pwc",C438)),ISNUMBER(SEARCH("consulting",C438)),ISNUMBER(SEARCH("consultant",B438)),ISNUMBER(SEARCH("advisory",C438)),ISNUMBER(SEARCH("philanthropic",C438)),ISNUMBER(SEARCH("argyle",C438)),ISNUMBER(SEARCH("quinn",C438))),"Consulting",OR(ISNUMBER(SEARCH("media",C438)),ISNUMBER(SEARCH("news",C438)),ISNUMBER(SEARCH("radio",C438)),ISNUMBER(SEARCH("film",C438)),ISNUMBER(SEARCH("journalist",B438)),ISNUMBER(SEARCH("columnist",B438)),ISNUMBER(SEARCH("globe",C438)),ISNUMBER(SEARCH("marketing",C438)),ISNUMBER(SEARCH("actor",B438))),"Media",OR(ISNUMBER(SEARCH("rbc",C438)),ISNUMBER(SEARCH("cibc",C438)),ISNUMBER(SEARCH("bmo",C438)),ISNUMBER(SEARCH("scotia",C438)),ISNUMBER(SEARCH("bank",C438)),ISNUMBER(SEARCH("capital",C438)),ISNUMBER(SEARCH("wealth",C438)),ISNUMBER(SEARCH("financial",C438)),ISNUMBER(SEARCH("securities",C438)),ISNUMBER(SEARCH("fidelity",C438)),ISNUMBER(SEARCH("guardian",C438)),ISNUMBER(SEARCH("wealthsimple",C438)),ISNUMBER(SEARCH("credit suisse",C438)),ISNUMBER(SEARCH("tmx",C438)),ISNUMBER(SEARCH("investors",C438)),ISNUMBER(SEARCH("trader",B438))),"Finance",OR(ISNUMBER(SEARCH("ventures",C438)),ISNUMBER(SEARCH("private equity",B438)),ISNUMBER(SEARCH("capital partners",C438))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C438)),ISNUMBER(SEARCH("ministry",C438)),ISNUMBER(SEARCH("tribunal",C438)),ISNUMBER(SEARCH("tdsb",C438)),ISNUMBER(SEARCH("public service",C438))),"Government",OR(ISNUMBER(SEARCH("association",C438)),ISNUMBER(SEARCH("institute",C438)),ISNUMBER(SEARCH("foundation",C438))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C438)),ISNUMBER(SEARCH("tech",C438)),ISNUMBER(SEARCH("systems",C438)),ISNUMBER(SEARCH("digital",C438)),ISNUMBER(SEARCH("engineering",C438)),ISNUMBER(SEARCH("solutions",C438))),"Technology",TRUE,"Other")</f>
-        <v>Real Estate</v>
+      <c r="I438" s="29" t="s">
+        <v>1054</v>
+      </c>
+      <c r="J438" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="K438" s="10" t="s">
+        <v>1065</v>
       </c>
     </row>
     <row r="439" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
-        <v>645</v>
+        <v>732</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>646</v>
+        <v>733</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1482</v>
+        <v>734</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>644</v>
+        <v>735</v>
       </c>
       <c r="E439" s="18">
-        <v>2420000</v>
+        <v>2100000</v>
       </c>
       <c r="F439" s="5">
-        <v>40717</v>
+        <v>41467</v>
       </c>
       <c r="G439" s="6">
-        <v>3.72</v>
+        <v>4.17</v>
       </c>
       <c r="H439" s="9">
         <v>50</v>
@@ -20913,25 +20901,25 @@
     </row>
     <row r="440" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
-        <v>732</v>
+        <v>807</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>733</v>
+        <v>808</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>734</v>
+        <v>809</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>735</v>
+        <v>810</v>
       </c>
       <c r="E440" s="18">
-        <v>2100000</v>
+        <v>1700000</v>
       </c>
       <c r="F440" s="5">
-        <v>41467</v>
-      </c>
-      <c r="G440" s="6">
-        <v>4.17</v>
+        <v>42037</v>
+      </c>
+      <c r="G440" s="3">
+        <v>3.73</v>
       </c>
       <c r="H440" s="9">
         <v>50</v>
@@ -20948,25 +20936,25 @@
     </row>
     <row r="441" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
-        <v>807</v>
+        <v>838</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>808</v>
+        <v>646</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>809</v>
+        <v>298</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>810</v>
+        <v>839</v>
       </c>
       <c r="E441" s="18">
-        <v>1700000</v>
+        <v>1600000</v>
       </c>
       <c r="F441" s="5">
-        <v>42037</v>
+        <v>38868</v>
       </c>
       <c r="G441" s="3">
-        <v>3.73</v>
+        <v>4.09</v>
       </c>
       <c r="H441" s="9">
         <v>50</v>
@@ -20982,26 +20970,26 @@
       </c>
     </row>
     <row r="442" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="4" t="s">
-        <v>838</v>
-      </c>
-      <c r="B442" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="C442" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D442" s="4" t="s">
-        <v>839</v>
-      </c>
-      <c r="E442" s="18">
-        <v>1600000</v>
-      </c>
-      <c r="F442" s="5">
-        <v>38868</v>
+      <c r="A442" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B442" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C442" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D442" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E442" s="16">
+        <v>1200000</v>
+      </c>
+      <c r="F442" s="32">
+        <v>45960</v>
       </c>
       <c r="G442" s="3">
-        <v>4.09</v>
+        <v>4.7510000000000003</v>
       </c>
       <c r="H442" s="9">
         <v>50</v>
@@ -21017,103 +21005,103 @@
       </c>
     </row>
     <row r="443" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A443" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B443" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C443" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D443" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E443" s="16">
-        <v>1200000</v>
-      </c>
-      <c r="F443" s="32">
-        <v>45960</v>
-      </c>
-      <c r="G443" s="3">
-        <v>4.7510000000000003</v>
-      </c>
-      <c r="H443" s="9">
+      <c r="A443" s="25" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B443" s="25" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C443" s="25" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D443" s="25" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E443" s="30">
+        <v>1140000</v>
+      </c>
+      <c r="F443" s="26">
+        <v>37994</v>
+      </c>
+      <c r="G443" s="27">
+        <v>3.23</v>
+      </c>
+      <c r="H443" s="28" cm="1">
+        <f t="array" ref="H443">_xlfn.IFS(I443="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B443)),80,96),I443="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B443)),ISNUMBER(SEARCH("chief executive",B443))),95,91),I443="Managing Director",86,I443="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B443)),ISNUMBER(SEARCH("general partner",B443))),88,85),I443="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B443)),ISNUMBER(SEARCH("executive vice",B443))),91,ISNUMBER(SEARCH("svp",B443)),77,TRUE,73),I443="Director",IF(ISNUMBER(SEARCH("principal",B443)),72,71),I443="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B443)),ISNUMBER(SEARCH("physician",B443)),ISNUMBER(SEARCH("doctor",B443)),ISNUMBER(SEARCH("dentist",B443)),ISNUMBER(SEARCH("psychiat",B443)),ISNUMBER(SEARCH("oncolog",B443)),ISNUMBER(SEARCH("neurolog",B443)),ISNUMBER(SEARCH("patholog",B443)),ISNUMBER(SEARCH("medicine",B443)),ISNUMBER(SEARCH("obgyn",B443))),77,OR(ISNUMBER(SEARCH("portfolio manager",B443)),ISNUMBER(SEARCH("wealth advisor",B443))),81,OR(ISNUMBER(SEARCH("lawyer",B443)),ISNUMBER(SEARCH("attorney",B443))),68,ISNUMBER(SEARCH("counsel",B443)),66,ISNUMBER(SEARCH("professor",B443)),63,OR(ISNUMBER(SEARCH("engineer",B443)),ISNUMBER(SEARCH("consultant",B443))),62,ISNUMBER(SEARCH("senior manager",B443)),64,OR(ISNUMBER(SEARCH("realtor",B443)),ISNUMBER(SEARCH("broker",B443)),ISNUMBER(SEARCH("journalist",B443)),ISNUMBER(SEARCH("columnist",B443)),ISNUMBER(SEARCH("trader",B443)),ISNUMBER(SEARCH("actor",B443))),50,TRUE,60)</f>
         <v>50</v>
       </c>
-      <c r="I443" s="29" t="s">
+      <c r="I443" s="29" t="str" cm="1">
+        <f t="array" ref="I443">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
+        <v>Professional</v>
+      </c>
+      <c r="J443" s="29" t="str" cm="1">
+        <f t="array" ref="J443">_xlfn.IFS(H443&gt;=90,"Very High",H443&gt;=80,"High",H443&gt;=56,"Medium",TRUE,"Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="K443" s="29" t="str" cm="1">
+        <f t="array" ref="K443">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C443)),ISNUMBER(SEARCH("health",C443)),ISNUMBER(SEARCH("medical",C443)),ISNUMBER(SEARCH("clinic",C443)),ISNUMBER(SEARCH("nursing",C443)),ISNUMBER(SEARCH("care cent",C443)),ISNUMBER(SEARCH("physician",B443)),ISNUMBER(SEARCH("doctor",B443)),ISNUMBER(SEARCH("dentist",B443)),ISNUMBER(SEARCH("surgeon",B443)),ISNUMBER(SEARCH("psychiat",B443)),ISNUMBER(SEARCH("medicine",B443))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C443)),ISNUMBER(SEARCH("lawyer",B443)),ISNUMBER(SEARCH("attorney",B443)),ISNUMBER(SEARCH("legal",C443)),ISNUMBER(SEARCH("tetrault",C443)),ISNUMBER(SEARCH("morley",C443)),ISNUMBER(SEARCH("blg",C443)),ISNUMBER(SEARCH("lowy",C443)),ISNUMBER(SEARCH("riley",C443)),ISNUMBER(SEARCH("toomath",C443))),"Law",OR(ISNUMBER(SEARCH("reit",C443)),ISNUMBER(SEARCH("properties",C443)),ISNUMBER(SEARCH("realty",C443)),ISNUMBER(SEARCH("realtor",B443)),ISNUMBER(SEARCH("colliers",C443)),ISNUMBER(SEARCH("re/max",C443)),ISNUMBER(SEARCH("quadreal",C443)),ISNUMBER(SEARCH("vic management",C443))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C443)),ISNUMBER(SEARCH("kpmg",C443)),ISNUMBER(SEARCH("pwc",C443)),ISNUMBER(SEARCH("consulting",C443)),ISNUMBER(SEARCH("consultant",B443)),ISNUMBER(SEARCH("advisory",C443)),ISNUMBER(SEARCH("philanthropic",C443)),ISNUMBER(SEARCH("argyle",C443)),ISNUMBER(SEARCH("quinn",C443))),"Consulting",OR(ISNUMBER(SEARCH("media",C443)),ISNUMBER(SEARCH("news",C443)),ISNUMBER(SEARCH("radio",C443)),ISNUMBER(SEARCH("film",C443)),ISNUMBER(SEARCH("journalist",B443)),ISNUMBER(SEARCH("columnist",B443)),ISNUMBER(SEARCH("globe",C443)),ISNUMBER(SEARCH("marketing",C443)),ISNUMBER(SEARCH("actor",B443))),"Media",OR(ISNUMBER(SEARCH("rbc",C443)),ISNUMBER(SEARCH("cibc",C443)),ISNUMBER(SEARCH("bmo",C443)),ISNUMBER(SEARCH("scotia",C443)),ISNUMBER(SEARCH("bank",C443)),ISNUMBER(SEARCH("capital",C443)),ISNUMBER(SEARCH("wealth",C443)),ISNUMBER(SEARCH("financial",C443)),ISNUMBER(SEARCH("securities",C443)),ISNUMBER(SEARCH("fidelity",C443)),ISNUMBER(SEARCH("guardian",C443)),ISNUMBER(SEARCH("wealthsimple",C443)),ISNUMBER(SEARCH("credit suisse",C443)),ISNUMBER(SEARCH("tmx",C443)),ISNUMBER(SEARCH("investors",C443)),ISNUMBER(SEARCH("trader",B443))),"Finance",OR(ISNUMBER(SEARCH("ventures",C443)),ISNUMBER(SEARCH("private equity",B443)),ISNUMBER(SEARCH("capital partners",C443))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C443)),ISNUMBER(SEARCH("ministry",C443)),ISNUMBER(SEARCH("tribunal",C443)),ISNUMBER(SEARCH("tdsb",C443)),ISNUMBER(SEARCH("public service",C443))),"Government",OR(ISNUMBER(SEARCH("association",C443)),ISNUMBER(SEARCH("institute",C443)),ISNUMBER(SEARCH("foundation",C443))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C443)),ISNUMBER(SEARCH("tech",C443)),ISNUMBER(SEARCH("systems",C443)),ISNUMBER(SEARCH("digital",C443)),ISNUMBER(SEARCH("engineering",C443)),ISNUMBER(SEARCH("solutions",C443))),"Technology",TRUE,"Other")</f>
+        <v>Media</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A444" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="B444" s="7" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C444" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="D444" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="E444" s="16">
+        <v>1000000</v>
+      </c>
+      <c r="F444" s="32">
+        <v>38908</v>
+      </c>
+      <c r="G444" s="3">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="H444" s="9">
+        <v>50</v>
+      </c>
+      <c r="I444" s="29" t="s">
         <v>1054</v>
       </c>
-      <c r="J443" s="10" t="s">
+      <c r="J444" s="10" t="s">
         <v>1060</v>
       </c>
-      <c r="K443" s="10" t="s">
+      <c r="K444" s="10" t="s">
         <v>1065</v>
       </c>
     </row>
-    <row r="444" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A444" s="25" t="s">
-        <v>1433</v>
-      </c>
-      <c r="B444" s="25" t="s">
-        <v>1434</v>
-      </c>
-      <c r="C444" s="25" t="s">
-        <v>1482</v>
-      </c>
-      <c r="D444" s="25" t="s">
-        <v>1409</v>
-      </c>
-      <c r="E444" s="30">
-        <v>1140000</v>
-      </c>
-      <c r="F444" s="26">
-        <v>37994</v>
-      </c>
-      <c r="G444" s="27">
-        <v>3.23</v>
-      </c>
-      <c r="H444" s="28" cm="1">
-        <f t="array" ref="H444">_xlfn.IFS(I444="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B444)),80,96),I444="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B444)),ISNUMBER(SEARCH("chief executive",B444))),95,91),I444="Managing Director",86,I444="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B444)),ISNUMBER(SEARCH("general partner",B444))),88,85),I444="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B444)),ISNUMBER(SEARCH("executive vice",B444))),91,ISNUMBER(SEARCH("svp",B444)),77,TRUE,73),I444="Director",IF(ISNUMBER(SEARCH("principal",B444)),72,71),I444="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B444)),ISNUMBER(SEARCH("physician",B444)),ISNUMBER(SEARCH("doctor",B444)),ISNUMBER(SEARCH("dentist",B444)),ISNUMBER(SEARCH("psychiat",B444)),ISNUMBER(SEARCH("oncolog",B444)),ISNUMBER(SEARCH("neurolog",B444)),ISNUMBER(SEARCH("patholog",B444)),ISNUMBER(SEARCH("medicine",B444)),ISNUMBER(SEARCH("obgyn",B444))),77,OR(ISNUMBER(SEARCH("portfolio manager",B444)),ISNUMBER(SEARCH("wealth advisor",B444))),81,OR(ISNUMBER(SEARCH("lawyer",B444)),ISNUMBER(SEARCH("attorney",B444))),68,ISNUMBER(SEARCH("counsel",B444)),66,ISNUMBER(SEARCH("professor",B444)),63,OR(ISNUMBER(SEARCH("engineer",B444)),ISNUMBER(SEARCH("consultant",B444))),62,ISNUMBER(SEARCH("senior manager",B444)),64,OR(ISNUMBER(SEARCH("realtor",B444)),ISNUMBER(SEARCH("broker",B444)),ISNUMBER(SEARCH("journalist",B444)),ISNUMBER(SEARCH("columnist",B444)),ISNUMBER(SEARCH("trader",B444)),ISNUMBER(SEARCH("actor",B444))),50,TRUE,60)</f>
-        <v>50</v>
-      </c>
-      <c r="I444" s="29" t="str" cm="1">
-        <f t="array" ref="I444">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
-        <v>Professional</v>
-      </c>
-      <c r="J444" s="29" t="str" cm="1">
-        <f t="array" ref="J444">_xlfn.IFS(H444&gt;=90,"Very High",H444&gt;=80,"High",H444&gt;=56,"Medium",TRUE,"Low")</f>
-        <v>Low</v>
-      </c>
-      <c r="K444" s="29" t="str" cm="1">
-        <f t="array" ref="K444">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C444)),ISNUMBER(SEARCH("health",C444)),ISNUMBER(SEARCH("medical",C444)),ISNUMBER(SEARCH("clinic",C444)),ISNUMBER(SEARCH("nursing",C444)),ISNUMBER(SEARCH("care cent",C444)),ISNUMBER(SEARCH("physician",B444)),ISNUMBER(SEARCH("doctor",B444)),ISNUMBER(SEARCH("dentist",B444)),ISNUMBER(SEARCH("surgeon",B444)),ISNUMBER(SEARCH("psychiat",B444)),ISNUMBER(SEARCH("medicine",B444))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C444)),ISNUMBER(SEARCH("lawyer",B444)),ISNUMBER(SEARCH("attorney",B444)),ISNUMBER(SEARCH("legal",C444)),ISNUMBER(SEARCH("tetrault",C444)),ISNUMBER(SEARCH("morley",C444)),ISNUMBER(SEARCH("blg",C444)),ISNUMBER(SEARCH("lowy",C444)),ISNUMBER(SEARCH("riley",C444)),ISNUMBER(SEARCH("toomath",C444))),"Law",OR(ISNUMBER(SEARCH("reit",C444)),ISNUMBER(SEARCH("properties",C444)),ISNUMBER(SEARCH("realty",C444)),ISNUMBER(SEARCH("realtor",B444)),ISNUMBER(SEARCH("colliers",C444)),ISNUMBER(SEARCH("re/max",C444)),ISNUMBER(SEARCH("quadreal",C444)),ISNUMBER(SEARCH("vic management",C444))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C444)),ISNUMBER(SEARCH("kpmg",C444)),ISNUMBER(SEARCH("pwc",C444)),ISNUMBER(SEARCH("consulting",C444)),ISNUMBER(SEARCH("consultant",B444)),ISNUMBER(SEARCH("advisory",C444)),ISNUMBER(SEARCH("philanthropic",C444)),ISNUMBER(SEARCH("argyle",C444)),ISNUMBER(SEARCH("quinn",C444))),"Consulting",OR(ISNUMBER(SEARCH("media",C444)),ISNUMBER(SEARCH("news",C444)),ISNUMBER(SEARCH("radio",C444)),ISNUMBER(SEARCH("film",C444)),ISNUMBER(SEARCH("journalist",B444)),ISNUMBER(SEARCH("columnist",B444)),ISNUMBER(SEARCH("globe",C444)),ISNUMBER(SEARCH("marketing",C444)),ISNUMBER(SEARCH("actor",B444))),"Media",OR(ISNUMBER(SEARCH("rbc",C444)),ISNUMBER(SEARCH("cibc",C444)),ISNUMBER(SEARCH("bmo",C444)),ISNUMBER(SEARCH("scotia",C444)),ISNUMBER(SEARCH("bank",C444)),ISNUMBER(SEARCH("capital",C444)),ISNUMBER(SEARCH("wealth",C444)),ISNUMBER(SEARCH("financial",C444)),ISNUMBER(SEARCH("securities",C444)),ISNUMBER(SEARCH("fidelity",C444)),ISNUMBER(SEARCH("guardian",C444)),ISNUMBER(SEARCH("wealthsimple",C444)),ISNUMBER(SEARCH("credit suisse",C444)),ISNUMBER(SEARCH("tmx",C444)),ISNUMBER(SEARCH("investors",C444)),ISNUMBER(SEARCH("trader",B444))),"Finance",OR(ISNUMBER(SEARCH("ventures",C444)),ISNUMBER(SEARCH("private equity",B444)),ISNUMBER(SEARCH("capital partners",C444))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C444)),ISNUMBER(SEARCH("ministry",C444)),ISNUMBER(SEARCH("tribunal",C444)),ISNUMBER(SEARCH("tdsb",C444)),ISNUMBER(SEARCH("public service",C444))),"Government",OR(ISNUMBER(SEARCH("association",C444)),ISNUMBER(SEARCH("institute",C444)),ISNUMBER(SEARCH("foundation",C444))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C444)),ISNUMBER(SEARCH("tech",C444)),ISNUMBER(SEARCH("systems",C444)),ISNUMBER(SEARCH("digital",C444)),ISNUMBER(SEARCH("engineering",C444)),ISNUMBER(SEARCH("solutions",C444))),"Technology",TRUE,"Other")</f>
-        <v>Media</v>
-      </c>
-    </row>
     <row r="445" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A445" s="7" t="s">
-        <v>934</v>
-      </c>
-      <c r="B445" s="7" t="s">
-        <v>1555</v>
-      </c>
-      <c r="C445" s="7" t="s">
-        <v>935</v>
-      </c>
-      <c r="D445" s="7" t="s">
-        <v>933</v>
-      </c>
-      <c r="E445" s="16">
-        <v>1000000</v>
-      </c>
-      <c r="F445" s="32">
-        <v>38908</v>
-      </c>
-      <c r="G445" s="3">
-        <v>4.1399999999999997</v>
+      <c r="A445" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B445" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C445" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E445" s="18">
+        <v>3850000</v>
+      </c>
+      <c r="F445" s="5">
+        <v>43987</v>
+      </c>
+      <c r="G445" s="6">
+        <v>3.68</v>
       </c>
       <c r="H445" s="9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I445" s="29" t="s">
         <v>1054</v>
@@ -21122,30 +21110,30 @@
         <v>1060</v>
       </c>
       <c r="K445" s="10" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="446" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>447</v>
+        <v>480</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="D446" s="4" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="E446" s="18">
-        <v>3850000</v>
+        <v>3625000</v>
       </c>
       <c r="F446" s="5">
-        <v>43987</v>
+        <v>45254</v>
       </c>
       <c r="G446" s="6">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="H446" s="9">
         <v>48</v>
@@ -21162,25 +21150,25 @@
     </row>
     <row r="447" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
-        <v>479</v>
+        <v>580</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>480</v>
+        <v>581</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>481</v>
+        <v>582</v>
       </c>
       <c r="D447" s="4" t="s">
-        <v>482</v>
+        <v>583</v>
       </c>
       <c r="E447" s="18">
-        <v>3625000</v>
+        <v>2810000</v>
       </c>
       <c r="F447" s="5">
-        <v>45254</v>
+        <v>44042</v>
       </c>
       <c r="G447" s="6">
-        <v>3.82</v>
+        <v>3.77</v>
       </c>
       <c r="H447" s="9">
         <v>48</v>
@@ -21196,26 +21184,26 @@
       </c>
     </row>
     <row r="448" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A448" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="B448" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="C448" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="D448" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="E448" s="18">
-        <v>2810000</v>
-      </c>
-      <c r="F448" s="5">
-        <v>44042</v>
-      </c>
-      <c r="G448" s="6">
-        <v>3.77</v>
+      <c r="A448" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="B448" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="C448" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="D448" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="E448" s="16">
+        <v>2261015</v>
+      </c>
+      <c r="F448" s="32">
+        <v>42359</v>
+      </c>
+      <c r="G448" s="3">
+        <v>4.1100000000000003</v>
       </c>
       <c r="H448" s="9">
         <v>48</v>
@@ -21231,25 +21219,25 @@
       </c>
     </row>
     <row r="449" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A449" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="B449" s="7" t="s">
-        <v>717</v>
-      </c>
-      <c r="C449" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="D449" s="7" t="s">
-        <v>719</v>
-      </c>
-      <c r="E449" s="16">
-        <v>2261015</v>
-      </c>
-      <c r="F449" s="32">
-        <v>42359</v>
-      </c>
-      <c r="G449" s="3">
+      <c r="A449" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C449" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E449" s="18">
+        <v>2150000</v>
+      </c>
+      <c r="F449" s="5">
+        <v>42220</v>
+      </c>
+      <c r="G449" s="6">
         <v>4.1100000000000003</v>
       </c>
       <c r="H449" s="9">
@@ -21262,30 +21250,30 @@
         <v>1060</v>
       </c>
       <c r="K449" s="10" t="s">
-        <v>1050</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="450" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
-        <v>730</v>
+        <v>811</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1540</v>
+        <v>812</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>298</v>
+        <v>813</v>
       </c>
       <c r="D450" s="4" t="s">
-        <v>731</v>
+        <v>814</v>
       </c>
       <c r="E450" s="18">
-        <v>2150000</v>
+        <v>1700000</v>
       </c>
       <c r="F450" s="5">
-        <v>42220</v>
-      </c>
-      <c r="G450" s="6">
-        <v>4.1100000000000003</v>
+        <v>42048</v>
+      </c>
+      <c r="G450" s="3">
+        <v>3.62</v>
       </c>
       <c r="H450" s="9">
         <v>48</v>
@@ -21297,30 +21285,30 @@
         <v>1060</v>
       </c>
       <c r="K450" s="10" t="s">
-        <v>1065</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="451" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
-        <v>811</v>
+        <v>133</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>812</v>
+        <v>134</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>813</v>
+        <v>298</v>
       </c>
       <c r="D451" s="4" t="s">
-        <v>814</v>
+        <v>135</v>
       </c>
       <c r="E451" s="18">
-        <v>1700000</v>
+        <v>1250000</v>
       </c>
       <c r="F451" s="5">
-        <v>42048</v>
-      </c>
-      <c r="G451" s="3">
-        <v>3.62</v>
+        <v>41271</v>
+      </c>
+      <c r="G451" s="6">
+        <v>2.871</v>
       </c>
       <c r="H451" s="9">
         <v>48</v>
@@ -21337,25 +21325,25 @@
     </row>
     <row r="452" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
-        <v>133</v>
+        <v>905</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>134</v>
+        <v>906</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>298</v>
+        <v>519</v>
       </c>
       <c r="D452" s="4" t="s">
-        <v>135</v>
+        <v>907</v>
       </c>
       <c r="E452" s="18">
-        <v>1250000</v>
+        <v>1200000</v>
       </c>
       <c r="F452" s="5">
-        <v>41271</v>
+        <v>38202</v>
       </c>
       <c r="G452" s="6">
-        <v>2.871</v>
+        <v>3.78</v>
       </c>
       <c r="H452" s="9">
         <v>48</v>
@@ -21372,28 +21360,28 @@
     </row>
     <row r="453" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
-        <v>905</v>
+        <v>552</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>906</v>
+        <v>553</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>519</v>
+        <v>554</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>907</v>
+        <v>555</v>
       </c>
       <c r="E453" s="18">
-        <v>1200000</v>
+        <v>3050000</v>
       </c>
       <c r="F453" s="5">
-        <v>38202</v>
+        <v>45806</v>
       </c>
       <c r="G453" s="6">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="H453" s="9">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I453" s="29" t="s">
         <v>1054</v>
@@ -21407,25 +21395,25 @@
     </row>
     <row r="454" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
-        <v>552</v>
+        <v>613</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>553</v>
+        <v>1554</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>554</v>
+        <v>614</v>
       </c>
       <c r="D454" s="4" t="s">
-        <v>555</v>
+        <v>612</v>
       </c>
       <c r="E454" s="18">
-        <v>3050000</v>
+        <v>2587000</v>
       </c>
       <c r="F454" s="5">
-        <v>45806</v>
+        <v>42326</v>
       </c>
       <c r="G454" s="6">
-        <v>3.84</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="H454" s="9">
         <v>45</v>
@@ -21437,30 +21425,30 @@
         <v>1060</v>
       </c>
       <c r="K454" s="10" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="455" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1558</v>
+        <v>616</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D455" s="4" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E455" s="18">
-        <v>2587000</v>
+        <v>2550000</v>
       </c>
       <c r="F455" s="5">
-        <v>42326</v>
+        <v>41739</v>
       </c>
       <c r="G455" s="6">
-        <v>4.0599999999999996</v>
+        <v>4.26</v>
       </c>
       <c r="H455" s="9">
         <v>45</v>
@@ -21472,30 +21460,30 @@
         <v>1060</v>
       </c>
       <c r="K455" s="10" t="s">
-        <v>1063</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="456" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
-        <v>615</v>
+        <v>1156</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>616</v>
+        <v>1157</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>617</v>
+        <v>1158</v>
       </c>
       <c r="D456" s="4" t="s">
-        <v>618</v>
+        <v>1159</v>
       </c>
       <c r="E456" s="18">
-        <v>2550000</v>
+        <v>2225000</v>
       </c>
       <c r="F456" s="5">
-        <v>41739</v>
+        <v>43034</v>
       </c>
       <c r="G456" s="6">
-        <v>4.26</v>
+        <v>3.4</v>
       </c>
       <c r="H456" s="9">
         <v>45</v>
@@ -21507,30 +21495,30 @@
         <v>1060</v>
       </c>
       <c r="K456" s="10" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="457" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
-        <v>1156</v>
+        <v>284</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1157</v>
+        <v>285</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>1158</v>
+        <v>1510</v>
       </c>
       <c r="D457" s="4" t="s">
-        <v>1159</v>
+        <v>286</v>
       </c>
       <c r="E457" s="18">
-        <v>2225000</v>
+        <v>1910000</v>
       </c>
       <c r="F457" s="5">
-        <v>43034</v>
+        <v>45861</v>
       </c>
       <c r="G457" s="6">
-        <v>3.4</v>
+        <v>4.5010000000000003</v>
       </c>
       <c r="H457" s="9">
         <v>45</v>
@@ -21542,30 +21530,30 @@
         <v>1060</v>
       </c>
       <c r="K457" s="10" t="s">
-        <v>1063</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="458" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A458" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B458" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C458" s="4" t="s">
-        <v>1514</v>
-      </c>
-      <c r="D458" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="E458" s="18">
-        <v>1910000</v>
-      </c>
-      <c r="F458" s="5">
-        <v>45861</v>
-      </c>
-      <c r="G458" s="6">
-        <v>4.5010000000000003</v>
+      <c r="A458" s="11" t="s">
+        <v>795</v>
+      </c>
+      <c r="B458" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C458" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="D458" s="11" t="s">
+        <v>797</v>
+      </c>
+      <c r="E458" s="17">
+        <v>1760000</v>
+      </c>
+      <c r="F458" s="31">
+        <v>41487</v>
+      </c>
+      <c r="G458" s="12">
+        <v>4</v>
       </c>
       <c r="H458" s="9">
         <v>45</v>
@@ -21581,26 +21569,26 @@
       </c>
     </row>
     <row r="459" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A459" s="11" t="s">
-        <v>795</v>
-      </c>
-      <c r="B459" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="C459" s="11" t="s">
-        <v>796</v>
-      </c>
-      <c r="D459" s="11" t="s">
-        <v>797</v>
-      </c>
-      <c r="E459" s="17">
-        <v>1760000</v>
-      </c>
-      <c r="F459" s="31">
-        <v>41487</v>
-      </c>
-      <c r="G459" s="12">
-        <v>4</v>
+      <c r="A459" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C459" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D459" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E459" s="18">
+        <v>1620000</v>
+      </c>
+      <c r="F459" s="5">
+        <v>45916</v>
+      </c>
+      <c r="G459" s="6">
+        <v>4.7530000000000001</v>
       </c>
       <c r="H459" s="9">
         <v>45</v>
@@ -21612,30 +21600,30 @@
         <v>1060</v>
       </c>
       <c r="K459" s="10" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="460" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>177</v>
+        <v>1492</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="D460" s="4" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="E460" s="18">
-        <v>1620000</v>
+        <v>1300000</v>
       </c>
       <c r="F460" s="5">
-        <v>45916</v>
+        <v>45960</v>
       </c>
       <c r="G460" s="6">
-        <v>4.7530000000000001</v>
+        <v>2.891</v>
       </c>
       <c r="H460" s="9">
         <v>45</v>
@@ -21647,30 +21635,30 @@
         <v>1060</v>
       </c>
       <c r="K460" s="10" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="461" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>1496</v>
+        <v>247</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>120</v>
+        <v>1472</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="E461" s="18">
-        <v>1300000</v>
+        <v>1190000</v>
       </c>
       <c r="F461" s="5">
-        <v>45960</v>
+        <v>45898</v>
       </c>
       <c r="G461" s="6">
-        <v>2.891</v>
+        <v>4.5919999999999996</v>
       </c>
       <c r="H461" s="9">
         <v>45</v>
@@ -21682,30 +21670,30 @@
         <v>1060</v>
       </c>
       <c r="K461" s="10" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="462" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
-        <v>246</v>
+        <v>136</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>247</v>
+        <v>1542</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>1476</v>
+        <v>137</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="E462" s="18">
-        <v>1190000</v>
+        <v>721000</v>
       </c>
       <c r="F462" s="5">
-        <v>45898</v>
-      </c>
-      <c r="G462" s="6">
-        <v>4.5919999999999996</v>
+        <v>38856</v>
+      </c>
+      <c r="G462" s="3">
+        <v>4.5060000000000002</v>
       </c>
       <c r="H462" s="9">
         <v>45</v>
@@ -21717,33 +21705,33 @@
         <v>1060</v>
       </c>
       <c r="K462" s="10" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="463" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A463" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B463" s="4" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C463" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D463" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E463" s="18">
-        <v>721000</v>
-      </c>
-      <c r="F463" s="5">
-        <v>38856</v>
-      </c>
-      <c r="G463" s="3">
-        <v>4.5060000000000002</v>
+      <c r="A463" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B463" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C463" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D463" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E463" s="17">
+        <v>2550000</v>
+      </c>
+      <c r="F463" s="31">
+        <v>45679</v>
+      </c>
+      <c r="G463" s="12">
+        <v>4.6239999999999997</v>
       </c>
       <c r="H463" s="9">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I463" s="29" t="s">
         <v>1054</v>
@@ -21752,65 +21740,65 @@
         <v>1060</v>
       </c>
       <c r="K463" s="10" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="464" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A464" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B464" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="C464" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D464" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E464" s="17">
-        <v>2550000</v>
-      </c>
-      <c r="F464" s="31">
-        <v>45679</v>
-      </c>
-      <c r="G464" s="12">
-        <v>4.6239999999999997</v>
+      <c r="A464" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="B464" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="C464" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="D464" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="E464" s="20" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F464" s="5">
+        <v>42355</v>
+      </c>
+      <c r="G464" s="6">
+        <v>4.09</v>
       </c>
       <c r="H464" s="9">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I464" s="29" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="J464" s="10" t="s">
         <v>1060</v>
       </c>
       <c r="K464" s="10" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="465" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
-        <v>985</v>
+        <v>364</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>986</v>
+        <v>365</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>677</v>
+        <v>366</v>
       </c>
       <c r="D465" s="4" t="s">
-        <v>987</v>
-      </c>
-      <c r="E465" s="20" t="s">
-        <v>1279</v>
+        <v>367</v>
+      </c>
+      <c r="E465" s="16">
+        <v>5206000</v>
       </c>
       <c r="F465" s="5">
-        <v>42355</v>
-      </c>
-      <c r="G465" s="6">
-        <v>4.09</v>
+        <v>44726</v>
+      </c>
+      <c r="G465" s="3">
+        <v>3.95</v>
       </c>
       <c r="H465" s="9">
         <v>36</v>
@@ -21822,71 +21810,71 @@
         <v>1060</v>
       </c>
       <c r="K465" s="10" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="466" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
-        <v>364</v>
+        <v>189</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>365</v>
+        <v>190</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>366</v>
+        <v>191</v>
       </c>
       <c r="D466" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="E466" s="16">
-        <v>5206000</v>
+        <v>192</v>
+      </c>
+      <c r="E466" s="18">
+        <v>2074000</v>
       </c>
       <c r="F466" s="5">
-        <v>44726</v>
-      </c>
-      <c r="G466" s="3">
-        <v>3.95</v>
+        <v>45862</v>
+      </c>
+      <c r="G466" s="6">
+        <v>4.5190000000000001</v>
       </c>
       <c r="H466" s="9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I466" s="29" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="J466" s="10" t="s">
         <v>1060</v>
       </c>
       <c r="K466" s="10" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="467" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>190</v>
+        <v>67</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>191</v>
+        <v>68</v>
       </c>
       <c r="D467" s="4" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="E467" s="18">
-        <v>2074000</v>
+        <v>1395000</v>
       </c>
       <c r="F467" s="5">
-        <v>45862</v>
+        <v>43815</v>
       </c>
       <c r="G467" s="6">
-        <v>4.5190000000000001</v>
+        <v>4.4470000000000001</v>
       </c>
       <c r="H467" s="9">
         <v>34</v>
       </c>
       <c r="I467" s="29" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="J467" s="10" t="s">
         <v>1060</v>
@@ -21896,29 +21884,29 @@
       </c>
     </row>
     <row r="468" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B468" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C468" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D468" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E468" s="18">
-        <v>1395000</v>
-      </c>
-      <c r="F468" s="5">
-        <v>43815</v>
-      </c>
-      <c r="G468" s="6">
-        <v>4.4470000000000001</v>
+      <c r="A468" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B468" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C468" s="7" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D468" s="7" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E468" s="20" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F468" s="32">
+        <v>44699</v>
+      </c>
+      <c r="G468" s="3">
+        <v>3.8</v>
       </c>
       <c r="H468" s="9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I468" s="29" t="s">
         <v>1059</v>
@@ -21927,174 +21915,174 @@
         <v>1060</v>
       </c>
       <c r="K468" s="10" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="469" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A469" s="7" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B469" s="7" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C469" s="7" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D469" s="7" t="s">
-        <v>1031</v>
+      <c r="A469" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B469" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="C469" s="4" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D469" s="4" t="s">
+        <v>1039</v>
       </c>
       <c r="E469" s="20" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F469" s="32">
-        <v>44699</v>
+        <v>1275</v>
+      </c>
+      <c r="F469" s="5">
+        <v>44782</v>
       </c>
       <c r="G469" s="3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H469" s="9">
         <v>32</v>
       </c>
       <c r="I469" s="29" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="J469" s="10" t="s">
         <v>1060</v>
       </c>
       <c r="K469" s="10" t="s">
-        <v>1056</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="470" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
-        <v>1038</v>
+        <v>343</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>779</v>
+        <v>344</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>1557</v>
+        <v>345</v>
       </c>
       <c r="D470" s="4" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E470" s="20" t="s">
-        <v>1279</v>
+        <v>346</v>
+      </c>
+      <c r="E470" s="16">
+        <v>5580000</v>
       </c>
       <c r="F470" s="5">
-        <v>44782</v>
-      </c>
-      <c r="G470" s="3">
-        <v>3.9</v>
+        <v>46112</v>
+      </c>
+      <c r="G470" s="6">
+        <v>3.82</v>
       </c>
       <c r="H470" s="9">
         <v>32</v>
       </c>
       <c r="I470" s="29" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="J470" s="10" t="s">
         <v>1060</v>
       </c>
       <c r="K470" s="10" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="471" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="B471" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="C471" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="D471" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="E471" s="16">
-        <v>5580000</v>
-      </c>
-      <c r="F471" s="5">
-        <v>46112</v>
-      </c>
-      <c r="G471" s="6">
-        <v>3.82</v>
-      </c>
-      <c r="H471" s="9">
+      <c r="A471" s="25" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B471" s="25" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C471" s="25" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D471" s="25" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E471" s="30">
+        <v>5500000</v>
+      </c>
+      <c r="F471" s="26">
+        <v>44165</v>
+      </c>
+      <c r="G471" s="27">
+        <v>2.97</v>
+      </c>
+      <c r="H471" s="28" cm="1">
+        <f t="array" ref="H471">_xlfn.IFS(I471="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B471)),80,96),I471="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B471)),ISNUMBER(SEARCH("chief executive",B471))),95,91),I471="Managing Director",86,I471="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B471)),ISNUMBER(SEARCH("general partner",B471))),88,85),I471="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B471)),ISNUMBER(SEARCH("executive vice",B471))),91,ISNUMBER(SEARCH("svp",B471)),77,TRUE,73),I471="Director",IF(ISNUMBER(SEARCH("principal",B471)),72,71),I471="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B471)),ISNUMBER(SEARCH("physician",B471)),ISNUMBER(SEARCH("doctor",B471)),ISNUMBER(SEARCH("dentist",B471)),ISNUMBER(SEARCH("psychiat",B471)),ISNUMBER(SEARCH("oncolog",B471)),ISNUMBER(SEARCH("neurolog",B471)),ISNUMBER(SEARCH("patholog",B471)),ISNUMBER(SEARCH("medicine",B471)),ISNUMBER(SEARCH("obgyn",B471))),77,OR(ISNUMBER(SEARCH("portfolio manager",B471)),ISNUMBER(SEARCH("wealth advisor",B471))),81,OR(ISNUMBER(SEARCH("lawyer",B471)),ISNUMBER(SEARCH("attorney",B471))),68,ISNUMBER(SEARCH("counsel",B471)),66,ISNUMBER(SEARCH("professor",B471)),63,OR(ISNUMBER(SEARCH("engineer",B471)),ISNUMBER(SEARCH("consultant",B471))),62,ISNUMBER(SEARCH("senior manager",B471)),64,OR(ISNUMBER(SEARCH("realtor",B471)),ISNUMBER(SEARCH("broker",B471)),ISNUMBER(SEARCH("journalist",B471)),ISNUMBER(SEARCH("columnist",B471)),ISNUMBER(SEARCH("trader",B471)),ISNUMBER(SEARCH("actor",B471))),50,TRUE,60)</f>
         <v>32</v>
       </c>
-      <c r="I471" s="29" t="s">
+      <c r="I471" s="29" t="str" cm="1">
+        <f t="array" ref="I471">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B471,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
+        <v>Individual Contributor</v>
+      </c>
+      <c r="J471" s="29" t="str" cm="1">
+        <f t="array" ref="J471">_xlfn.IFS(H471&gt;=90,"Very High",H471&gt;=80,"High",H471&gt;=56,"Medium",TRUE,"Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="K471" s="29" t="str" cm="1">
+        <f t="array" ref="K471">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C471)),ISNUMBER(SEARCH("health",C471)),ISNUMBER(SEARCH("medical",C471)),ISNUMBER(SEARCH("clinic",C471)),ISNUMBER(SEARCH("nursing",C471)),ISNUMBER(SEARCH("care cent",C471)),ISNUMBER(SEARCH("physician",B471)),ISNUMBER(SEARCH("doctor",B471)),ISNUMBER(SEARCH("dentist",B471)),ISNUMBER(SEARCH("surgeon",B471)),ISNUMBER(SEARCH("psychiat",B471)),ISNUMBER(SEARCH("medicine",B471))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C471)),ISNUMBER(SEARCH("lawyer",B471)),ISNUMBER(SEARCH("attorney",B471)),ISNUMBER(SEARCH("legal",C471)),ISNUMBER(SEARCH("tetrault",C471)),ISNUMBER(SEARCH("morley",C471)),ISNUMBER(SEARCH("blg",C471)),ISNUMBER(SEARCH("lowy",C471)),ISNUMBER(SEARCH("riley",C471)),ISNUMBER(SEARCH("toomath",C471))),"Law",OR(ISNUMBER(SEARCH("reit",C471)),ISNUMBER(SEARCH("properties",C471)),ISNUMBER(SEARCH("realty",C471)),ISNUMBER(SEARCH("realtor",B471)),ISNUMBER(SEARCH("colliers",C471)),ISNUMBER(SEARCH("re/max",C471)),ISNUMBER(SEARCH("quadreal",C471)),ISNUMBER(SEARCH("vic management",C471))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C471)),ISNUMBER(SEARCH("kpmg",C471)),ISNUMBER(SEARCH("pwc",C471)),ISNUMBER(SEARCH("consulting",C471)),ISNUMBER(SEARCH("consultant",B471)),ISNUMBER(SEARCH("advisory",C471)),ISNUMBER(SEARCH("philanthropic",C471)),ISNUMBER(SEARCH("argyle",C471)),ISNUMBER(SEARCH("quinn",C471))),"Consulting",OR(ISNUMBER(SEARCH("media",C471)),ISNUMBER(SEARCH("news",C471)),ISNUMBER(SEARCH("radio",C471)),ISNUMBER(SEARCH("film",C471)),ISNUMBER(SEARCH("journalist",B471)),ISNUMBER(SEARCH("columnist",B471)),ISNUMBER(SEARCH("globe",C471)),ISNUMBER(SEARCH("marketing",C471)),ISNUMBER(SEARCH("actor",B471))),"Media",OR(ISNUMBER(SEARCH("rbc",C471)),ISNUMBER(SEARCH("cibc",C471)),ISNUMBER(SEARCH("bmo",C471)),ISNUMBER(SEARCH("scotia",C471)),ISNUMBER(SEARCH("bank",C471)),ISNUMBER(SEARCH("capital",C471)),ISNUMBER(SEARCH("wealth",C471)),ISNUMBER(SEARCH("financial",C471)),ISNUMBER(SEARCH("securities",C471)),ISNUMBER(SEARCH("fidelity",C471)),ISNUMBER(SEARCH("guardian",C471)),ISNUMBER(SEARCH("wealthsimple",C471)),ISNUMBER(SEARCH("credit suisse",C471)),ISNUMBER(SEARCH("tmx",C471)),ISNUMBER(SEARCH("investors",C471)),ISNUMBER(SEARCH("trader",B471))),"Finance",OR(ISNUMBER(SEARCH("ventures",C471)),ISNUMBER(SEARCH("private equity",B471)),ISNUMBER(SEARCH("capital partners",C471))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C471)),ISNUMBER(SEARCH("ministry",C471)),ISNUMBER(SEARCH("tribunal",C471)),ISNUMBER(SEARCH("tdsb",C471)),ISNUMBER(SEARCH("public service",C471))),"Government",OR(ISNUMBER(SEARCH("association",C471)),ISNUMBER(SEARCH("institute",C471)),ISNUMBER(SEARCH("foundation",C471))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C471)),ISNUMBER(SEARCH("tech",C471)),ISNUMBER(SEARCH("systems",C471)),ISNUMBER(SEARCH("digital",C471)),ISNUMBER(SEARCH("engineering",C471)),ISNUMBER(SEARCH("solutions",C471))),"Technology",TRUE,"Other")</f>
+        <v>Other</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A472" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B472" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C472" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D472" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="E472" s="16">
+        <v>4550000</v>
+      </c>
+      <c r="F472" s="5">
+        <v>44693</v>
+      </c>
+      <c r="G472" s="6">
+        <v>3.85</v>
+      </c>
+      <c r="H472" s="9">
+        <v>32</v>
+      </c>
+      <c r="I472" s="29" t="s">
         <v>1059</v>
       </c>
-      <c r="J471" s="10" t="s">
+      <c r="J472" s="10" t="s">
         <v>1060</v>
       </c>
-      <c r="K471" s="10" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="472" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="25" t="s">
-        <v>1359</v>
-      </c>
-      <c r="B472" s="25" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C472" s="25" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D472" s="25" t="s">
-        <v>1319</v>
-      </c>
-      <c r="E472" s="30">
-        <v>5500000</v>
-      </c>
-      <c r="F472" s="26">
-        <v>44165</v>
-      </c>
-      <c r="G472" s="27">
-        <v>2.97</v>
-      </c>
-      <c r="H472" s="28" cm="1">
-        <f t="array" ref="H472">_xlfn.IFS(I472="Founder / Owner",IF(ISNUMBER(SEARCH("owner",B472)),80,96),I472="C-Suite",IF(OR(ISNUMBER(SEARCH("ceo",B472)),ISNUMBER(SEARCH("chief executive",B472))),95,91),I472="Managing Director",86,I472="Partner",IF(OR(ISNUMBER(SEARCH("managing partner",B472)),ISNUMBER(SEARCH("general partner",B472))),88,85),I472="VP / Head",_xlfn.IFS(OR(ISNUMBER(SEARCH("vice president",B472)),ISNUMBER(SEARCH("executive vice",B472))),91,ISNUMBER(SEARCH("svp",B472)),77,TRUE,73),I472="Director",IF(ISNUMBER(SEARCH("principal",B472)),72,71),I472="Individual Contributor",32,OR(ISNUMBER(SEARCH("surgeon",B472)),ISNUMBER(SEARCH("physician",B472)),ISNUMBER(SEARCH("doctor",B472)),ISNUMBER(SEARCH("dentist",B472)),ISNUMBER(SEARCH("psychiat",B472)),ISNUMBER(SEARCH("oncolog",B472)),ISNUMBER(SEARCH("neurolog",B472)),ISNUMBER(SEARCH("patholog",B472)),ISNUMBER(SEARCH("medicine",B472)),ISNUMBER(SEARCH("obgyn",B472))),77,OR(ISNUMBER(SEARCH("portfolio manager",B472)),ISNUMBER(SEARCH("wealth advisor",B472))),81,OR(ISNUMBER(SEARCH("lawyer",B472)),ISNUMBER(SEARCH("attorney",B472))),68,ISNUMBER(SEARCH("counsel",B472)),66,ISNUMBER(SEARCH("professor",B472)),63,OR(ISNUMBER(SEARCH("engineer",B472)),ISNUMBER(SEARCH("consultant",B472))),62,ISNUMBER(SEARCH("senior manager",B472)),64,OR(ISNUMBER(SEARCH("realtor",B472)),ISNUMBER(SEARCH("broker",B472)),ISNUMBER(SEARCH("journalist",B472)),ISNUMBER(SEARCH("columnist",B472)),ISNUMBER(SEARCH("trader",B472)),ISNUMBER(SEARCH("actor",B472))),50,TRUE,60)</f>
-        <v>32</v>
-      </c>
-      <c r="I472" s="29" t="str" cm="1">
-        <f t="array" ref="I472">_xlfn.LET(_xlpm.p," "&amp;LOWER(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B472,","," "),"-"," "),"."," "))&amp;" ",_xlfn.IFS(OR(ISNUMBER(SEARCH(" founder ",_xlpm.p)),ISNUMBER(SEARCH(" co founder ",_xlpm.p)),AND(ISNUMBER(SEARCH(" owner ",_xlpm.p)),NOT(ISNUMBER(SEARCH("product owner",_xlpm.p))))),"Founder / Owner",ISNUMBER(SEARCH("managing director",_xlpm.p)),"Managing Director",ISNUMBER(SEARCH(" partner",_xlpm.p)),"Partner",OR(ISNUMBER(SEARCH(" vice",_xlpm.p)),ISNUMBER(SEARCH(" vp ",_xlpm.p)),ISNUMBER(SEARCH(" svp ",_xlpm.p)),ISNUMBER(SEARCH(" evp ",_xlpm.p)),ISNUMBER(SEARCH(" head of ",_xlpm.p)),ISNUMBER(SEARCH("executive director",_xlpm.p))),"VP / Head",OR(ISNUMBER(SEARCH(" ceo ",_xlpm.p)),ISNUMBER(SEARCH("chief",_xlpm.p)),ISNUMBER(SEARCH("president",_xlpm.p)),ISNUMBER(SEARCH(" cfo ",_xlpm.p)),ISNUMBER(SEARCH(" coo ",_xlpm.p)),ISNUMBER(SEARCH(" cmo ",_xlpm.p)),ISNUMBER(SEARCH(" cto ",_xlpm.p)),ISNUMBER(SEARCH(" cao ",_xlpm.p)),ISNUMBER(SEARCH(" cro ",_xlpm.p)),ISNUMBER(SEARCH("chair",_xlpm.p))),"C-Suite",OR(ISNUMBER(SEARCH("director",_xlpm.p)),ISNUMBER(SEARCH("principal",_xlpm.p))),"Director",OR(ISNUMBER(SEARCH("assistant",_xlpm.p)),ISNUMBER(SEARCH("coordinator",_xlpm.p)),ISNUMBER(SEARCH("analyst",_xlpm.p)),ISNUMBER(SEARCH(" lead hand ",_xlpm.p)),ISNUMBER(SEARCH("clerk",_xlpm.p)),ISNUMBER(SEARCH("administrat",_xlpm.p))),"Individual Contributor",TRUE,"Professional"))</f>
-        <v>Individual Contributor</v>
-      </c>
-      <c r="J472" s="29" t="str" cm="1">
-        <f t="array" ref="J472">_xlfn.IFS(H472&gt;=90,"Very High",H472&gt;=80,"High",H472&gt;=56,"Medium",TRUE,"Low")</f>
-        <v>Low</v>
-      </c>
-      <c r="K472" s="29" t="str" cm="1">
-        <f t="array" ref="K472">_xlfn.IFS(OR(ISNUMBER(SEARCH("hospital",C472)),ISNUMBER(SEARCH("health",C472)),ISNUMBER(SEARCH("medical",C472)),ISNUMBER(SEARCH("clinic",C472)),ISNUMBER(SEARCH("nursing",C472)),ISNUMBER(SEARCH("care cent",C472)),ISNUMBER(SEARCH("physician",B472)),ISNUMBER(SEARCH("doctor",B472)),ISNUMBER(SEARCH("dentist",B472)),ISNUMBER(SEARCH("surgeon",B472)),ISNUMBER(SEARCH("psychiat",B472)),ISNUMBER(SEARCH("medicine",B472))),"Healthcare",OR(ISNUMBER(SEARCH("llp",C472)),ISNUMBER(SEARCH("lawyer",B472)),ISNUMBER(SEARCH("attorney",B472)),ISNUMBER(SEARCH("legal",C472)),ISNUMBER(SEARCH("tetrault",C472)),ISNUMBER(SEARCH("morley",C472)),ISNUMBER(SEARCH("blg",C472)),ISNUMBER(SEARCH("lowy",C472)),ISNUMBER(SEARCH("riley",C472)),ISNUMBER(SEARCH("toomath",C472))),"Law",OR(ISNUMBER(SEARCH("reit",C472)),ISNUMBER(SEARCH("properties",C472)),ISNUMBER(SEARCH("realty",C472)),ISNUMBER(SEARCH("realtor",B472)),ISNUMBER(SEARCH("colliers",C472)),ISNUMBER(SEARCH("re/max",C472)),ISNUMBER(SEARCH("quadreal",C472)),ISNUMBER(SEARCH("vic management",C472))),"Real Estate",OR(ISNUMBER(SEARCH("deloitte",C472)),ISNUMBER(SEARCH("kpmg",C472)),ISNUMBER(SEARCH("pwc",C472)),ISNUMBER(SEARCH("consulting",C472)),ISNUMBER(SEARCH("consultant",B472)),ISNUMBER(SEARCH("advisory",C472)),ISNUMBER(SEARCH("philanthropic",C472)),ISNUMBER(SEARCH("argyle",C472)),ISNUMBER(SEARCH("quinn",C472))),"Consulting",OR(ISNUMBER(SEARCH("media",C472)),ISNUMBER(SEARCH("news",C472)),ISNUMBER(SEARCH("radio",C472)),ISNUMBER(SEARCH("film",C472)),ISNUMBER(SEARCH("journalist",B472)),ISNUMBER(SEARCH("columnist",B472)),ISNUMBER(SEARCH("globe",C472)),ISNUMBER(SEARCH("marketing",C472)),ISNUMBER(SEARCH("actor",B472))),"Media",OR(ISNUMBER(SEARCH("rbc",C472)),ISNUMBER(SEARCH("cibc",C472)),ISNUMBER(SEARCH("bmo",C472)),ISNUMBER(SEARCH("scotia",C472)),ISNUMBER(SEARCH("bank",C472)),ISNUMBER(SEARCH("capital",C472)),ISNUMBER(SEARCH("wealth",C472)),ISNUMBER(SEARCH("financial",C472)),ISNUMBER(SEARCH("securities",C472)),ISNUMBER(SEARCH("fidelity",C472)),ISNUMBER(SEARCH("guardian",C472)),ISNUMBER(SEARCH("wealthsimple",C472)),ISNUMBER(SEARCH("credit suisse",C472)),ISNUMBER(SEARCH("tmx",C472)),ISNUMBER(SEARCH("investors",C472)),ISNUMBER(SEARCH("trader",B472))),"Finance",OR(ISNUMBER(SEARCH("ventures",C472)),ISNUMBER(SEARCH("private equity",B472)),ISNUMBER(SEARCH("capital partners",C472))),"Private Equity / VC",OR(ISNUMBER(SEARCH("government",C472)),ISNUMBER(SEARCH("ministry",C472)),ISNUMBER(SEARCH("tribunal",C472)),ISNUMBER(SEARCH("tdsb",C472)),ISNUMBER(SEARCH("public service",C472))),"Government",OR(ISNUMBER(SEARCH("association",C472)),ISNUMBER(SEARCH("institute",C472)),ISNUMBER(SEARCH("foundation",C472))),"Nonprofit",OR(ISNUMBER(SEARCH("software",C472)),ISNUMBER(SEARCH("tech",C472)),ISNUMBER(SEARCH("systems",C472)),ISNUMBER(SEARCH("digital",C472)),ISNUMBER(SEARCH("engineering",C472)),ISNUMBER(SEARCH("solutions",C472))),"Technology",TRUE,"Other")</f>
-        <v>Other</v>
+      <c r="K472" s="10" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="473" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>406</v>
+        <v>1524</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="D473" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="E473" s="16">
-        <v>4550000</v>
+        <v>458</v>
+      </c>
+      <c r="E473" s="18">
+        <v>3828000</v>
       </c>
       <c r="F473" s="5">
-        <v>44693</v>
+        <v>45461</v>
       </c>
       <c r="G473" s="6">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="H473" s="9">
         <v>32</v>
@@ -22106,30 +22094,30 @@
         <v>1060</v>
       </c>
       <c r="K473" s="10" t="s">
-        <v>1066</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="474" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
-        <v>456</v>
+        <v>602</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>1528</v>
+        <v>1480</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>457</v>
+        <v>603</v>
       </c>
       <c r="D474" s="4" t="s">
-        <v>458</v>
+        <v>604</v>
       </c>
       <c r="E474" s="18">
-        <v>3828000</v>
+        <v>2728000</v>
       </c>
       <c r="F474" s="5">
-        <v>45461</v>
+        <v>45278</v>
       </c>
       <c r="G474" s="6">
-        <v>3.74</v>
+        <v>4.09</v>
       </c>
       <c r="H474" s="9">
         <v>32</v>
@@ -22146,13 +22134,13 @@
     </row>
     <row r="475" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>1484</v>
+        <v>606</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>603</v>
+        <v>496</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>604</v>
@@ -22176,30 +22164,30 @@
         <v>1060</v>
       </c>
       <c r="K475" s="10" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="476" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
-        <v>605</v>
+        <v>657</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>606</v>
+        <v>658</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>496</v>
+        <v>659</v>
       </c>
       <c r="D476" s="4" t="s">
-        <v>604</v>
+        <v>660</v>
       </c>
       <c r="E476" s="18">
-        <v>2728000</v>
+        <v>2400000</v>
       </c>
       <c r="F476" s="5">
-        <v>45278</v>
+        <v>43928</v>
       </c>
       <c r="G476" s="6">
-        <v>4.09</v>
+        <v>4.24</v>
       </c>
       <c r="H476" s="9">
         <v>32</v>
@@ -22211,30 +22199,30 @@
         <v>1060</v>
       </c>
       <c r="K476" s="10" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="477" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
-        <v>657</v>
+        <v>720</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>658</v>
+        <v>721</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>659</v>
+        <v>722</v>
       </c>
       <c r="D477" s="4" t="s">
-        <v>660</v>
+        <v>719</v>
       </c>
       <c r="E477" s="18">
-        <v>2400000</v>
+        <v>2261015</v>
       </c>
       <c r="F477" s="5">
-        <v>43928</v>
-      </c>
-      <c r="G477" s="6">
-        <v>4.24</v>
+        <v>42359</v>
+      </c>
+      <c r="G477" s="3">
+        <v>4.1100000000000003</v>
       </c>
       <c r="H477" s="9">
         <v>32</v>
@@ -22246,30 +22234,30 @@
         <v>1060</v>
       </c>
       <c r="K477" s="10" t="s">
-        <v>1050</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="478" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A478" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="B478" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="C478" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="D478" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="E478" s="18">
-        <v>2261015</v>
-      </c>
-      <c r="F478" s="5">
-        <v>42359</v>
-      </c>
-      <c r="G478" s="3">
-        <v>4.1100000000000003</v>
+      <c r="A478" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B478" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C478" s="11" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D478" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E478" s="17">
+        <v>1939000</v>
+      </c>
+      <c r="F478" s="31">
+        <v>44019</v>
+      </c>
+      <c r="G478" s="12">
+        <v>4.8449999999999998</v>
       </c>
       <c r="H478" s="9">
         <v>32</v>
@@ -22281,100 +22269,100 @@
         <v>1060</v>
       </c>
       <c r="K478" s="10" t="s">
-        <v>1067</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="479" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A479" s="11" t="s">
-        <v>267</v>
+        <v>778</v>
       </c>
       <c r="B479" s="11" t="s">
-        <v>268</v>
+        <v>779</v>
       </c>
       <c r="C479" s="11" t="s">
-        <v>1282</v>
+        <v>780</v>
       </c>
       <c r="D479" s="11" t="s">
-        <v>269</v>
+        <v>777</v>
       </c>
       <c r="E479" s="17">
-        <v>1939000</v>
+        <v>1900000</v>
       </c>
       <c r="F479" s="31">
-        <v>44019</v>
+        <v>42891</v>
       </c>
       <c r="G479" s="12">
-        <v>4.8449999999999998</v>
+        <v>3.8</v>
       </c>
       <c r="H479" s="9">
         <v>32</v>
       </c>
       <c r="I479" s="29" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="J479" s="10" t="s">
         <v>1060</v>
       </c>
       <c r="K479" s="10" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="480" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A480" s="11" t="s">
-        <v>778</v>
-      </c>
-      <c r="B480" s="11" t="s">
-        <v>779</v>
-      </c>
-      <c r="C480" s="11" t="s">
-        <v>780</v>
-      </c>
-      <c r="D480" s="11" t="s">
-        <v>777</v>
-      </c>
-      <c r="E480" s="17">
-        <v>1900000</v>
-      </c>
-      <c r="F480" s="31">
-        <v>42891</v>
-      </c>
-      <c r="G480" s="12">
-        <v>3.8</v>
+      <c r="A480" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B480" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C480" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D480" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E480" s="16">
+        <v>1688000</v>
+      </c>
+      <c r="F480" s="32">
+        <v>45902</v>
+      </c>
+      <c r="G480" s="3">
+        <v>4.6879999999999997</v>
       </c>
       <c r="H480" s="9">
         <v>32</v>
       </c>
       <c r="I480" s="29" t="s">
-        <v>1054</v>
+        <v>1059</v>
       </c>
       <c r="J480" s="10" t="s">
         <v>1060</v>
       </c>
       <c r="K480" s="10" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="481" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A481" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B481" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C481" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D481" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="E481" s="16">
-        <v>1688000</v>
-      </c>
-      <c r="F481" s="32">
-        <v>45902</v>
-      </c>
-      <c r="G481" s="3">
-        <v>4.6879999999999997</v>
+      <c r="A481" s="11" t="s">
+        <v>845</v>
+      </c>
+      <c r="B481" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="C481" s="13" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D481" s="13" t="s">
+        <v>844</v>
+      </c>
+      <c r="E481" s="17">
+        <v>1595000</v>
+      </c>
+      <c r="F481" s="31">
+        <v>37839</v>
+      </c>
+      <c r="G481" s="14">
+        <v>3.83</v>
       </c>
       <c r="H481" s="9">
         <v>32</v>
@@ -22386,30 +22374,30 @@
         <v>1060</v>
       </c>
       <c r="K481" s="10" t="s">
-        <v>1050</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="482" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A482" s="11" t="s">
-        <v>845</v>
-      </c>
-      <c r="B482" s="11" t="s">
-        <v>846</v>
-      </c>
-      <c r="C482" s="13" t="s">
-        <v>1518</v>
-      </c>
-      <c r="D482" s="13" t="s">
-        <v>844</v>
-      </c>
-      <c r="E482" s="17">
-        <v>1595000</v>
-      </c>
-      <c r="F482" s="31">
-        <v>37839</v>
-      </c>
-      <c r="G482" s="14">
-        <v>3.83</v>
+      <c r="A482" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B482" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C482" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D482" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E482" s="18">
+        <v>1512000</v>
+      </c>
+      <c r="F482" s="5">
+        <v>44991</v>
+      </c>
+      <c r="G482" s="6">
+        <v>3.48</v>
       </c>
       <c r="H482" s="9">
         <v>32</v>
@@ -22421,30 +22409,30 @@
         <v>1060</v>
       </c>
       <c r="K482" s="10" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="483" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
-        <v>1188</v>
+        <v>49</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>1029</v>
+        <v>50</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>1189</v>
+        <v>51</v>
       </c>
       <c r="D483" s="4" t="s">
-        <v>1190</v>
+        <v>17</v>
       </c>
       <c r="E483" s="18">
-        <v>1512000</v>
+        <v>940000</v>
       </c>
       <c r="F483" s="5">
-        <v>44991</v>
+        <v>39262</v>
       </c>
       <c r="G483" s="6">
-        <v>3.48</v>
+        <v>4.84</v>
       </c>
       <c r="H483" s="9">
         <v>32</v>
@@ -22456,46 +22444,11 @@
         <v>1060</v>
       </c>
       <c r="K483" s="10" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="484" spans="1:11" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A484" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B484" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D484" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E484" s="18">
-        <v>940000</v>
-      </c>
-      <c r="F484" s="5">
-        <v>39262</v>
-      </c>
-      <c r="G484" s="6">
-        <v>4.84</v>
-      </c>
-      <c r="H484" s="9">
-        <v>32</v>
-      </c>
-      <c r="I484" s="29" t="s">
-        <v>1059</v>
-      </c>
-      <c r="J484" s="10" t="s">
-        <v>1060</v>
-      </c>
-      <c r="K484" s="10" t="s">
         <v>1050</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="I485" s="29"/>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I484" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K106" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -22503,8 +22456,8 @@
       <sortCondition descending="1" ref="H1:H106"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A415:G484">
-    <sortCondition descending="1" ref="E415:E484"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A414:G483">
+    <sortCondition descending="1" ref="E414:E483"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
